--- a/horizon-reports/horizon_rapor_latest.xlsx
+++ b/horizon-reports/horizon_rapor_latest.xlsx
@@ -12,9 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tüm Açık Çağrılar" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Yeni Açılan Çağrılar'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tüm Misyon Çağrıları'!$A$1:$E$71</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tüm Açık Çağrılar'!$A$1:$E$676</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Yeni Açılan Çağrılar'!$A$1:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tüm Misyon Çağrıları'!$A$1:$E$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tüm Açık Çağrılar'!$A$1:$E$662</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -481,94 +481,28 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Startup Europe</t>
+          <t>ODEON Open Call</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HORIZON-EIE-2027-01-CONNECT-01</t>
+          <t>HORIZON-CL5-2023-D3-01-15</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>46539</v>
+        <v>46120</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>46645</v>
+        <v>46212.70833333334</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>2000000</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Reinforcing synergies between experimentation spaces and innovation procurement</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>HORIZON-EIE-2027-01-CONNECT-02</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>46539</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>46645</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>10000000</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Enhancing the involvement of philanthropic organisations in innovation ecosystems</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>HORIZON-EIE-2027-01-CONNECT-03</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>46539</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>46645</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Ignite NEB Open call for hosts</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>HORIZON-EIT-2025-KIC-IBA-INBC</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>46104</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>46149.70833333334</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>208000</v>
+        <v>1200000</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E5"/>
+  <autoFilter ref="A1:E2"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -580,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1859,40 +1793,40 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Understanding and overcoming barriers to the scale-up of innovations supporting EU Missions</t>
+          <t>BlueActionBANOS Open Call for Community-Led Actions</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-07-CROSS-02</t>
+          <t>HORIZON-MISS-2024-OCEAN-02-01</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>46000</v>
+        <v>45989</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>46112</v>
+        <v>46171.58333333334</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>2000000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Strengthening skills and capacity for the deployment of EU Missions</t>
+          <t>BlueActionBANOS 1st Open Call for Transition Agendas</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-07-CROSS-01</t>
+          <t>HORIZON-MISS-2024-OCEAN-02-01</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>46000</v>
+        <v>45989</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>46112</v>
+        <v>46171.58333333334</v>
       </c>
       <c r="E62" s="4" t="n">
         <v>1000000</v>
@@ -1901,28 +1835,28 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Advancing lead markets and proof-of-concept for deep tech solutions contributing to EU Missions</t>
+          <t>BlueActionAA – Community Led-Pilot Action Call (BAAC-01)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-07-CROSS-03</t>
+          <t>HORIZON-MISS-2024-OCEAN-02-01</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>46000</v>
+        <v>45989</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>46112</v>
+        <v>46171.58333333334</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>4000000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>BlueActionBANOS Open Call for Community-Led Actions</t>
+          <t xml:space="preserve">TASC-RestoreMed Open Call Type B: Transition Agenda Development (TAD) </t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1931,19 +1865,19 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>45989</v>
+        <v>45988</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>46171.58333333334</v>
+        <v>46169.70833333334</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>7000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>BlueActionBANOS 1st Open Call for Transition Agendas</t>
+          <t xml:space="preserve">TASC-RestoreMed Open Call Type A: Community-Led Actions (CLA) </t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1952,140 +1886,56 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>45989</v>
+        <v>45988</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>46171.58333333334</v>
+        <v>46169.70833333334</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>1000000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>BlueActionAA – Community Led-Pilot Action Call (BAAC-01)</t>
+          <t>Call for MRV providers to test solutions under the LILAS4SOILS Project</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-OCEAN-02-01</t>
+          <t>HORIZON-MISS-2023-SOIL-01-09</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>45989</v>
+        <v>45985</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>46171.58333333334</v>
+        <v>46046.99930555555</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>7000000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TASC-RestoreMed Open Call Type B: Transition Agenda Development (TAD) </t>
+          <t>Call for marine biodiversity (monitoring) data</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-OCEAN-02-01</t>
+          <t>HORIZON-MISS-2022-OCEAN-01-07</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>45988</v>
+        <v>45644</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>46169.70833333334</v>
-      </c>
-      <c r="E67" s="4" t="n">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>SoS2LearnDBS’s Open call for Community-Led Actions to restore Danube-Black Sea Waters (OC-CLed-SoS2LearnDBS-2025)</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>HORIZON-MISS-2024-OCEAN-02-01</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="n">
-        <v>45988</v>
-      </c>
-      <c r="D68" s="3" t="n">
-        <v>46111.5</v>
-      </c>
-      <c r="E68" s="4" t="n">
-        <v>7000000</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TASC-RestoreMed Open Call Type A: Community-Led Actions (CLA) </t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>HORIZON-MISS-2024-OCEAN-02-01</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="n">
-        <v>45988</v>
-      </c>
-      <c r="D69" s="3" t="n">
-        <v>46169.70833333334</v>
-      </c>
-      <c r="E69" s="4" t="n">
-        <v>7000000</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Call for MRV providers to test solutions under the LILAS4SOILS Project</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>HORIZON-MISS-2023-SOIL-01-09</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="n">
-        <v>45985</v>
-      </c>
-      <c r="D70" s="3" t="n">
-        <v>46046.99930555555</v>
-      </c>
-      <c r="E70" s="4" t="n">
-        <v>60000</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>Call for marine biodiversity (monitoring) data</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>HORIZON-MISS-2022-OCEAN-01-07</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="n">
-        <v>45644</v>
-      </c>
-      <c r="D71" s="3" t="n">
         <v>45716.99930555555</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E71"/>
+  <autoFilter ref="A1:E67"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId2"/>
@@ -2153,10 +2003,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2168,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E676"/>
+  <dimension ref="A1:E662"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -9948,120 +9794,138 @@
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>Superconducting motor windings for a fully electric hydrogen fuel cell powered aircraft</t>
+          <t>ODEON Open Call</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-FTA-06</t>
+          <t>HORIZON-CL5-2023-D3-01-15</t>
         </is>
       </c>
       <c r="C372" s="3" t="n">
-        <v>46112</v>
+        <v>46120</v>
       </c>
       <c r="D372" s="3" t="n">
-        <v>46161</v>
+        <v>46212.70833333334</v>
+      </c>
+      <c r="E372" s="4" t="n">
+        <v>1200000</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>Demonstration of advanced FC propulsion techno-bricks for a fully electric hydrogen fuel cell powered aircraft</t>
+          <t>JARVIS Open Call #2 - Co-development Track</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-HPA-01</t>
+          <t>HORIZON-CL4-2023-DIGITAL-EMERGING-01-02</t>
         </is>
       </c>
       <c r="C373" s="3" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="D373" s="3" t="n">
-        <v>46161</v>
+        <v>46174.875</v>
+      </c>
+      <c r="E373" s="4" t="n">
+        <v>800000</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>Demonstration and Validation of icing Certification Methodologies compatible with EIS2035 for the SMR and REG Aircraft</t>
+          <t>JARVIS Open Call #2 - External Pilots Track</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-TRA-01</t>
+          <t>HORIZON-CL4-2023-DIGITAL-EMERGING-01-02</t>
         </is>
       </c>
       <c r="C374" s="3" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="D374" s="3" t="n">
-        <v>46161</v>
+        <v>46213.875</v>
+      </c>
+      <c r="E374" s="4" t="n">
+        <v>650000</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>Demonstration of advanced airframe for ultra-efficient regional aircraft</t>
+          <t>NGI Fediversity open call (2026-06F)</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-REG-01</t>
+          <t>HORIZON-CL4-2023-HUMAN-01-12</t>
         </is>
       </c>
       <c r="C375" s="3" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="D375" s="3" t="n">
-        <v>46161</v>
+        <v>46174.5</v>
+      </c>
+      <c r="E375" s="4" t="n">
+        <v>365000</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>Demonstration of an integrated hydrogen fuel system for a fully electric hydrogen fuel cell powered aircraft</t>
+          <t>NGI Zero Commons Fund (2026-06Z)</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-HPA-02</t>
+          <t>HORIZON-CL4-2023-HUMAN-01-11</t>
         </is>
       </c>
       <c r="C376" s="3" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="D376" s="3" t="n">
-        <v>46161</v>
+        <v>46174.5</v>
+      </c>
+      <c r="E376" s="4" t="n">
+        <v>6100000</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>Cryo-cooled power electronics for a fully electric hydrogen fuel cell powered aircraft</t>
+          <t>NGI TALER open call (2026-06T)</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-FTA-05</t>
+          <t>HORIZON-CL4-2023-HUMAN-01-12</t>
         </is>
       </c>
       <c r="C377" s="3" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="D377" s="3" t="n">
-        <v>46161</v>
+        <v>46174.5</v>
+      </c>
+      <c r="E377" s="4" t="n">
+        <v>269173</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>Innovative light weight and reliable liquid hydrogen tank</t>
+          <t>Demonstration of low power Ice Protection System technology</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-FTA-07</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-FTA-01</t>
         </is>
       </c>
       <c r="C378" s="3" t="n">
@@ -10074,12 +9938,12 @@
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>Operational stakeholders’ group to support the deployment of Clean Aviation aircraft concepts and technologies</t>
+          <t>Demonstration of an Ultra-Efficient Rear Fuselage and Empennage and Its Integrated Industrial System enabling EIS2035 for the SMR Aircraft</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-CSA-01</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-SMR-02</t>
         </is>
       </c>
       <c r="C379" s="3" t="n">
@@ -10092,12 +9956,12 @@
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>Demonstration of low power Ice Protection System technology</t>
+          <t>Demonstration and Validation of icing Certification Methodologies compatible with EIS2035 for the SMR and REG Aircraft</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-FTA-01</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-TRA-01</t>
         </is>
       </c>
       <c r="C380" s="3" t="n">
@@ -10110,12 +9974,12 @@
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Key Technologies for Loads Control Lidar for Ultra-efficient SMR aircraft </t>
+          <t>Demonstration of an Optimized System Platform for Ultra-efficient SMR Aircraft</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-FTA-04</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-SMR-01</t>
         </is>
       </c>
       <c r="C381" s="3" t="n">
@@ -10128,12 +9992,12 @@
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>Demonstration of Advanced Low NOx H2C Propulsion System for a direct hydrogen combustion aircraft</t>
+          <t>Demonstration of an integrated hydrogen fuel system for a fully electric hydrogen fuel cell powered aircraft</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-HPA-03</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-HPA-02</t>
         </is>
       </c>
       <c r="C382" s="3" t="n">
@@ -10146,12 +10010,12 @@
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>Demonstration of an Ultra-Efficient Rear Fuselage and Empennage and Its Integrated Industrial System enabling EIS2035 for the SMR Aircraft</t>
+          <t>Demonstration of a hydrogen distribution system for a direct hydrogen combustion propulsion aircraft</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-SMR-02</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-HPA-04</t>
         </is>
       </c>
       <c r="C383" s="3" t="n">
@@ -10164,12 +10028,12 @@
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>Advanced noise-reducing technologies for propulsion systems of next generation Ultra-efficient SMR aircraft</t>
+          <t>Demonstration of Advanced Low NOx H2C Propulsion System for a direct hydrogen combustion aircraft</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-FTA-03</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-HPA-03</t>
         </is>
       </c>
       <c r="C384" s="3" t="n">
@@ -10182,12 +10046,12 @@
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>Demonstration of a hydrogen distribution system for a direct hydrogen combustion propulsion aircraft</t>
+          <t>Advanced noise-reducing technologies for propulsion systems of next generation Ultra-efficient SMR aircraft</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-HPA-04</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-FTA-03</t>
         </is>
       </c>
       <c r="C385" s="3" t="n">
@@ -10200,12 +10064,12 @@
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>Ground Demonstration of Hybrid-Electric Propulsion Architectures for the Ultra-efficient SMR aircraft</t>
+          <t>Demonstration of cabin acoustic optimization technology</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-SMR-03</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-FTA-02</t>
         </is>
       </c>
       <c r="C386" s="3" t="n">
@@ -10236,12 +10100,12 @@
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>Demonstration of an Optimized System Platform for Ultra-efficient SMR Aircraft</t>
+          <t>Superconducting motor windings for a fully electric hydrogen fuel cell powered aircraft</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-SMR-01</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-FTA-06</t>
         </is>
       </c>
       <c r="C388" s="3" t="n">
@@ -10254,12 +10118,12 @@
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>Demonstration of cabin acoustic optimization technology</t>
+          <t>Demonstration of advanced FC propulsion techno-bricks for a fully electric hydrogen fuel cell powered aircraft</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-FTA-02</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-HPA-01</t>
         </is>
       </c>
       <c r="C389" s="3" t="n">
@@ -10272,222 +10136,204 @@
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>Scaleups Promotion Open Call</t>
+          <t xml:space="preserve">Key Technologies for Loads Control Lidar for Ultra-efficient SMR aircraft </t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>HORIZON-EIT-2025-KIC-IBA-UM</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-FTA-04</t>
         </is>
       </c>
       <c r="C390" s="3" t="n">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="D390" s="3" t="n">
-        <v>46169.70833333334</v>
-      </c>
-      <c r="E390" s="4" t="n">
-        <v>415000</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>Ignite NEB Open call for hosts</t>
+          <t>Demonstration of advanced airframe for ultra-efficient regional aircraft</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>HORIZON-EIT-2025-KIC-IBA-INBC</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-REG-01</t>
         </is>
       </c>
       <c r="C391" s="3" t="n">
-        <v>46104</v>
+        <v>46112</v>
       </c>
       <c r="D391" s="3" t="n">
-        <v>46149.70833333334</v>
-      </c>
-      <c r="E391" s="4" t="n">
-        <v>208000</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>PERIFORMANCE OPEN CALL FOR BOTTOM-UP STAKEHOLDER ENGAGEMENT INITIATIVES IN CANCER RESEARCH &amp; CARE</t>
+          <t>Operational stakeholders’ group to support the deployment of Clean Aviation aircraft concepts and technologies</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-CROSS-02-01</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-CSA-01</t>
         </is>
       </c>
       <c r="C392" s="3" t="n">
-        <v>46103</v>
+        <v>46112</v>
       </c>
       <c r="D392" s="3" t="n">
-        <v>46173.70833333334</v>
-      </c>
-      <c r="E392" s="4" t="n">
-        <v>150000</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>Risk management, mitigation and contingency for ESFRI/ERIC and other world-class research infrastructures</t>
+          <t>Cryo-cooled power electronics for a fully electric hydrogen fuel cell powered aircraft</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>HORIZON-INFRA-2026-DEV-01-07</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-FTA-05</t>
         </is>
       </c>
       <c r="C393" s="3" t="n">
-        <v>46091</v>
+        <v>46112</v>
       </c>
       <c r="D393" s="3" t="n">
-        <v>46189</v>
-      </c>
-      <c r="E393" s="4" t="n">
-        <v>1000000</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>R&amp;D for the next generation of scientific instrumentation, tools, methods, digitalisation and solutions for research infrastructure upgrades</t>
+          <t>Innovative light weight and reliable liquid hydrogen tank</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>HORIZON-INFRA-2026-TECH-01-01</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-FTA-07</t>
         </is>
       </c>
       <c r="C394" s="3" t="n">
-        <v>46091</v>
+        <v>46112</v>
       </c>
       <c r="D394" s="3" t="n">
-        <v>46189</v>
-      </c>
-      <c r="E394" s="4" t="n">
-        <v>5000000</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>Uptake of FAIR data management practices and of EOSC by research communities and research infrastructures (EOSC Partnership)</t>
+          <t>Ground Demonstration of Hybrid-Electric Propulsion Architectures for the Ultra-efficient SMR aircraft</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>HORIZON-INFRA-2026-01-EOSC-01</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-SMR-03</t>
         </is>
       </c>
       <c r="C395" s="3" t="n">
-        <v>46091</v>
+        <v>46112</v>
       </c>
       <c r="D395" s="3" t="n">
-        <v>46189</v>
-      </c>
-      <c r="E395" s="4" t="n">
-        <v>40000000</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>Implementing digital services to empower neuroscience research for health and brain inspired technology via EBRAINS</t>
+          <t>Student Entrepreneur Grant Scheme (SEGS)</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>HORIZON-INFRA-2026-SERV-01-01</t>
+          <t>HORIZON-EIT-2025-KIC-IBA-UM</t>
         </is>
       </c>
       <c r="C396" s="3" t="n">
-        <v>46091</v>
+        <v>46111</v>
       </c>
       <c r="D396" s="3" t="n">
-        <v>46189</v>
+        <v>46307.70833333334</v>
       </c>
       <c r="E396" s="4" t="n">
-        <v>32000000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>Strengthening the human capital managing research infrastructures, including in international context</t>
+          <t>Scaleups Promotion Open Call</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>HORIZON-INFRA-2026-DEV-01-04</t>
+          <t>HORIZON-EIT-2025-KIC-IBA-UM</t>
         </is>
       </c>
       <c r="C397" s="3" t="n">
-        <v>46091</v>
+        <v>46108</v>
       </c>
       <c r="D397" s="3" t="n">
-        <v>46189</v>
+        <v>46169.70833333334</v>
       </c>
       <c r="E397" s="4" t="n">
-        <v>2000000</v>
+        <v>415000</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>Consolidation of the research infrastructure landscape – pilots for strategic coordination, synergies and simplified access pathways, by large thematic clusters of pan-European research infrastructures</t>
+          <t>Ignite NEB Open call for hosts</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>HORIZON-INFRA-2026-DEV-01-02</t>
+          <t>HORIZON-EIT-2025-KIC-IBA-INBC</t>
         </is>
       </c>
       <c r="C398" s="3" t="n">
-        <v>46091</v>
+        <v>46104</v>
       </c>
       <c r="D398" s="3" t="n">
-        <v>46189</v>
+        <v>46149.70833333334</v>
       </c>
       <c r="E398" s="4" t="n">
-        <v>4000000</v>
+        <v>208000</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>Digital twins and/or their major components for environment, climate and security</t>
+          <t>PERIFORMANCE OPEN CALL FOR BOTTOM-UP STAKEHOLDER ENGAGEMENT INITIATIVES IN CANCER RESEARCH &amp; CARE</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>HORIZON-INFRA-2026-TECH-01-02</t>
+          <t>HORIZON-MISS-2024-CROSS-02-01</t>
         </is>
       </c>
       <c r="C399" s="3" t="n">
-        <v>46091</v>
+        <v>46103</v>
       </c>
       <c r="D399" s="3" t="n">
-        <v>46189</v>
+        <v>46173.70833333334</v>
       </c>
       <c r="E399" s="4" t="n">
-        <v>5000000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>Strengthening the international dimension of ESFRI and/or ERIC research infrastructures</t>
+          <t>Risk management, mitigation and contingency for ESFRI/ERIC and other world-class research infrastructures</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>HORIZON-INFRA-2026-DEV-01-06</t>
+          <t>HORIZON-INFRA-2026-DEV-01-07</t>
         </is>
       </c>
       <c r="C400" s="3" t="n">
@@ -10503,12 +10349,12 @@
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>Research infrastructures as accelerators of the integration of Ukraine in the European Research Area</t>
+          <t>R&amp;D for the next generation of scientific instrumentation, tools, methods, digitalisation and solutions for research infrastructure upgrades</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>HORIZON-INFRA-2026-DEV-01-05</t>
+          <t>HORIZON-INFRA-2026-TECH-01-01</t>
         </is>
       </c>
       <c r="C401" s="3" t="n">
@@ -10518,18 +10364,18 @@
         <v>46189</v>
       </c>
       <c r="E401" s="4" t="n">
-        <v>8000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>Trusted frameworks for secure and efficient data sharing in EOSC (EOSC Partnership)</t>
+          <t>Uptake of FAIR data management practices and of EOSC by research communities and research infrastructures (EOSC Partnership)</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>HORIZON-INFRA-2026-01-EOSC-02</t>
+          <t>HORIZON-INFRA-2026-01-EOSC-01</t>
         </is>
       </c>
       <c r="C402" s="3" t="n">
@@ -10539,18 +10385,18 @@
         <v>46189</v>
       </c>
       <c r="E402" s="4" t="n">
-        <v>3000000</v>
+        <v>40000000</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>Consolidation of the research infrastructure landscape – individual support for evolution, long-term sustainability and emerging needs of pan-European research infrastructures</t>
+          <t>Implementing digital services to empower neuroscience research for health and brain inspired technology via EBRAINS</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>HORIZON-INFRA-2026-DEV-01-03</t>
+          <t>HORIZON-INFRA-2026-SERV-01-01</t>
         </is>
       </c>
       <c r="C403" s="3" t="n">
@@ -10560,18 +10406,18 @@
         <v>46189</v>
       </c>
       <c r="E403" s="4" t="n">
-        <v>3000000</v>
+        <v>32000000</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>Research infrastructure concept development including major upgrades or extensions of existing infrastructures</t>
+          <t>Strengthening the human capital managing research infrastructures, including in international context</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>HORIZON-INFRA-2026-DEV-01-01</t>
+          <t>HORIZON-INFRA-2026-DEV-01-04</t>
         </is>
       </c>
       <c r="C404" s="3" t="n">
@@ -10587,159 +10433,159 @@
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>Preparing demonstration missions for Earth Observation and Satellite telecommunication for Space solutions (Space Partnership)</t>
+          <t>Consolidation of the research infrastructure landscape – pilots for strategic coordination, synergies and simplified access pathways, by large thematic clusters of pan-European research infrastructures</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-SPACE-03-32</t>
+          <t>HORIZON-INFRA-2026-DEV-01-02</t>
         </is>
       </c>
       <c r="C405" s="3" t="n">
         <v>46091</v>
       </c>
       <c r="D405" s="3" t="n">
-        <v>46268</v>
+        <v>46189</v>
       </c>
       <c r="E405" s="4" t="n">
-        <v>5000000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>Digital enablers and building-blocks for Earth Observation and Satellite telecommunication for Space solutions (Space Partnership)</t>
+          <t>Digital twins and/or their major components for environment, climate and security</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-SPACE-03-31</t>
+          <t>HORIZON-INFRA-2026-TECH-01-02</t>
         </is>
       </c>
       <c r="C406" s="3" t="n">
         <v>46091</v>
       </c>
       <c r="D406" s="3" t="n">
-        <v>46268</v>
+        <v>46189</v>
       </c>
       <c r="E406" s="4" t="n">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>Space critical EEE components for EU non-dependence – GaN MMICs mm-Wave Foundations (Phase A): Development and Industrialization of Semi-insulating SiC Substrate Capabilities</t>
+          <t>Strengthening the international dimension of ESFRI and/or ERIC research infrastructures</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-SPACE-03-82</t>
+          <t>HORIZON-INFRA-2026-DEV-01-06</t>
         </is>
       </c>
       <c r="C407" s="3" t="n">
         <v>46091</v>
       </c>
       <c r="D407" s="3" t="n">
-        <v>46268</v>
+        <v>46189</v>
       </c>
       <c r="E407" s="4" t="n">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>Reinforcing EU autonomous access to space through EU-based spaceports</t>
+          <t>Research infrastructures as accelerators of the integration of Ukraine in the European Research Area</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-SPACE-03-11</t>
+          <t>HORIZON-INFRA-2026-DEV-01-05</t>
         </is>
       </c>
       <c r="C408" s="3" t="n">
         <v>46091</v>
       </c>
       <c r="D408" s="3" t="n">
-        <v>46268</v>
+        <v>46189</v>
       </c>
       <c r="E408" s="4" t="n">
-        <v>10000000</v>
+        <v>8000000</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>Space critical EEE components for EU non-dependence – Radiation Hard FPGA on 7nm</t>
+          <t>Trusted frameworks for secure and efficient data sharing in EOSC (EOSC Partnership)</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-SPACE-03-81</t>
+          <t>HORIZON-INFRA-2026-01-EOSC-02</t>
         </is>
       </c>
       <c r="C409" s="3" t="n">
         <v>46091</v>
       </c>
       <c r="D409" s="3" t="n">
-        <v>46268</v>
+        <v>46189</v>
       </c>
       <c r="E409" s="4" t="n">
-        <v>12000000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>Space critical Equipment for EU non-dependence – Space Refuelling Interface</t>
+          <t>Consolidation of the research infrastructure landscape – individual support for evolution, long-term sustainability and emerging needs of pan-European research infrastructures</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-SPACE-03-86</t>
+          <t>HORIZON-INFRA-2026-DEV-01-03</t>
         </is>
       </c>
       <c r="C410" s="3" t="n">
         <v>46091</v>
       </c>
       <c r="D410" s="3" t="n">
-        <v>46268</v>
+        <v>46189</v>
       </c>
       <c r="E410" s="4" t="n">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>Critical Facilities Serving Space EEE components for EU non-dependence – High and Very High Energy Irradiation Test Facility Market Deployment</t>
+          <t>Research infrastructure concept development including major upgrades or extensions of existing infrastructures</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-SPACE-03-85</t>
+          <t>HORIZON-INFRA-2026-DEV-01-01</t>
         </is>
       </c>
       <c r="C411" s="3" t="n">
         <v>46091</v>
       </c>
       <c r="D411" s="3" t="n">
-        <v>46268</v>
+        <v>46189</v>
       </c>
       <c r="E411" s="4" t="n">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>Scientific analysis and exploitation of space data</t>
+          <t>Preparing demonstration missions for Earth Observation and Satellite telecommunication for Space solutions (Space Partnership)</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-SPACE-03-61</t>
+          <t>HORIZON-CL4-2026-SPACE-03-32</t>
         </is>
       </c>
       <c r="C412" s="3" t="n">
@@ -10749,109 +10595,109 @@
         <v>46268</v>
       </c>
       <c r="E412" s="4" t="n">
-        <v>1500000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">INTEGRATION OF EXISTING APPLICATIONS, MODELS AND DATA INTO EDITO </t>
+          <t>Digital enablers and building-blocks for Earth Observation and Satellite telecommunication for Space solutions (Space Partnership)</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-OCEAN-IBA</t>
+          <t>HORIZON-CL4-2026-SPACE-03-31</t>
         </is>
       </c>
       <c r="C413" s="3" t="n">
         <v>46091</v>
       </c>
       <c r="D413" s="3" t="n">
-        <v>46148.5</v>
+        <v>46268</v>
       </c>
       <c r="E413" s="4" t="n">
-        <v>600000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>Open Call for Financial Support to Third parties as a mechanism to test, promote, validate, replicate PRIMARY business model blueprints and develop new value chains</t>
+          <t>Space critical EEE components for EU non-dependence – GaN MMICs mm-Wave Foundations (Phase A): Development and Industrialization of Semi-insulating SiC Substrate Capabilities</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2024-CircBio-02-6-two-stage</t>
+          <t>HORIZON-CL4-2026-SPACE-03-82</t>
         </is>
       </c>
       <c r="C414" s="3" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="D414" s="3" t="n">
-        <v>46181.70833333334</v>
+        <v>46268</v>
       </c>
       <c r="E414" s="4" t="n">
-        <v>900000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">COP-PILOT Open Call 1 </t>
+          <t>Reinforcing EU autonomous access to space through EU-based spaceports</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2024-DATA-01-03</t>
+          <t>HORIZON-CL4-2026-SPACE-03-11</t>
         </is>
       </c>
       <c r="C415" s="3" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D415" s="3" t="n">
-        <v>46146.91666666666</v>
+        <v>46268</v>
       </c>
       <c r="E415" s="4" t="n">
-        <v>1600000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>Approaches and tools for security in software and hardware development and assessment</t>
+          <t>Space critical EEE components for EU non-dependence – Radiation Hard FPGA on 7nm</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>HORIZON-CL3-2026-02-CS-ECCC-01</t>
+          <t>HORIZON-CL4-2026-SPACE-03-81</t>
         </is>
       </c>
       <c r="C416" s="3" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D416" s="3" t="n">
-        <v>46280</v>
+        <v>46268</v>
       </c>
       <c r="E416" s="4" t="n">
-        <v>3000000</v>
+        <v>12000000</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>Advanced cryptographic schemes and High-Assurance high-speed cryptographic implementations</t>
+          <t>Space critical Equipment for EU non-dependence – Space Refuelling Interface</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>HORIZON-CL3-2026-02-CS-ECCC-03</t>
+          <t>HORIZON-CL4-2026-SPACE-03-86</t>
         </is>
       </c>
       <c r="C417" s="3" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D417" s="3" t="n">
-        <v>46280</v>
+        <v>46268</v>
       </c>
       <c r="E417" s="4" t="n">
         <v>2000000</v>
@@ -10860,19 +10706,19 @@
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>Enhancing the Security, Privacy and Robustness of AI Models and Systems (SecureAI)</t>
+          <t>Critical Facilities Serving Space EEE components for EU non-dependence – High and Very High Energy Irradiation Test Facility Market Deployment</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>HORIZON-CL3-2026-02-CS-ECCC-02</t>
+          <t>HORIZON-CL4-2026-SPACE-03-85</t>
         </is>
       </c>
       <c r="C418" s="3" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D418" s="3" t="n">
-        <v>46280</v>
+        <v>46268</v>
       </c>
       <c r="E418" s="4" t="n">
         <v>3000000</v>
@@ -10881,352 +10727,352 @@
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
         <is>
-          <t>HORIZON-EIC-2026-BAS-02-SCLATEUP</t>
+          <t>Scientific analysis and exploitation of space data</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>HORIZON-EIC-2026-BAS-02-SCALEUP</t>
+          <t>HORIZON-CL4-2026-SPACE-03-61</t>
         </is>
       </c>
       <c r="C419" s="3" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D419" s="3" t="n">
-        <v>46176</v>
+        <v>46268</v>
       </c>
       <c r="E419" s="4" t="n">
-        <v>4000000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>AUTOASSESS Open Call #2 for Tech Innovators</t>
+          <t xml:space="preserve">INTEGRATION OF EXISTING APPLICATIONS, MODELS AND DATA INTO EDITO </t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2022-DIGITAL-EMERGING-02-07</t>
+          <t>HORIZON-MISS-2024-OCEAN-IBA</t>
         </is>
       </c>
       <c r="C420" s="3" t="n">
-        <v>46083</v>
+        <v>46091</v>
       </c>
       <c r="D420" s="3" t="n">
-        <v>46147.70833333334</v>
+        <v>46148.5</v>
       </c>
       <c r="E420" s="4" t="n">
-        <v>1350000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>Open Horizons Open Call #3</t>
+          <t>Open Call for Financial Support to Third parties as a mechanism to test, promote, validate, replicate PRIMARY business model blueprints and develop new value chains</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>HORIZON-EIE-2024-CONNECT-01-02</t>
+          <t>HORIZON-CL6-2024-CircBio-02-6-two-stage</t>
         </is>
       </c>
       <c r="C421" s="3" t="n">
-        <v>46083</v>
+        <v>46090</v>
       </c>
       <c r="D421" s="3" t="n">
-        <v>46161.70833333334</v>
+        <v>46181.70833333334</v>
       </c>
       <c r="E421" s="4" t="n">
-        <v>475000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>First FIDELIS Open Call for Mentors and Peer-to-Peer Support Programme</t>
+          <t xml:space="preserve">COP-PILOT Open Call 1 </t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>HORIZON-INFRA-2024-EOSC-01-03</t>
+          <t>HORIZON-CL4-2024-DATA-01-03</t>
         </is>
       </c>
       <c r="C422" s="3" t="n">
-        <v>46080</v>
+        <v>46084</v>
       </c>
       <c r="D422" s="3" t="n">
-        <v>46142.70833333334</v>
+        <v>46146.91666666666</v>
       </c>
       <c r="E422" s="4" t="n">
-        <v>120000</v>
+        <v>1600000</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
         <is>
-          <t>Call for applications: FRONTIERS Science Journalism Residency Program (Call 4)</t>
+          <t>Approaches and tools for security in software and hardware development and assessment</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>ERC-2023-SJI-1</t>
+          <t>HORIZON-CL3-2026-02-CS-ECCC-01</t>
         </is>
       </c>
       <c r="C423" s="3" t="n">
-        <v>46078</v>
+        <v>46084</v>
       </c>
       <c r="D423" s="3" t="n">
-        <v>46167.79166666666</v>
+        <v>46280</v>
       </c>
       <c r="E423" s="4" t="n">
-        <v>600000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>Open Call 2 - Short Term and Long Term Funding to support ICT standardisation</t>
+          <t>Advanced cryptographic schemes and High-Assurance high-speed cryptographic implementations</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2024-HUMAN-03-04</t>
+          <t>HORIZON-CL3-2026-02-CS-ECCC-03</t>
         </is>
       </c>
       <c r="C424" s="3" t="n">
-        <v>46076</v>
+        <v>46084</v>
       </c>
       <c r="D424" s="3" t="n">
-        <v>46136.70833333334</v>
+        <v>46280</v>
       </c>
       <c r="E424" s="4" t="n">
-        <v>650000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
         <is>
-          <t>InnoMatch project - Open call 2 for EIC Awardees</t>
+          <t>Enhancing the Security, Privacy and Robustness of AI Models and Systems (SecureAI)</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>HORIZON-EIC-2023-INNOVPRO-01-01</t>
+          <t>HORIZON-CL3-2026-02-CS-ECCC-02</t>
         </is>
       </c>
       <c r="C425" s="3" t="n">
-        <v>46069</v>
+        <v>46084</v>
       </c>
       <c r="D425" s="3" t="n">
-        <v>46129.70833333334</v>
+        <v>46280</v>
+      </c>
+      <c r="E425" s="4" t="n">
+        <v>3000000</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>Living labs to enhance soil health in managed forests and in natural/semi-natural lands</t>
+          <t>HORIZON-EIC-2026-BAS-02-SCLATEUP</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-05-SOIL-02-two-stage</t>
+          <t>HORIZON-EIC-2026-BAS-02-SCALEUP</t>
         </is>
       </c>
       <c r="C426" s="3" t="n">
-        <v>46065</v>
+        <v>46084</v>
       </c>
       <c r="D426" s="3" t="n">
-        <v>46280</v>
+        <v>46198</v>
       </c>
       <c r="E426" s="4" t="n">
-        <v>12000000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>Open topic: Uncovering the causes of specific species’ rapid decline and exploring actionable solutions</t>
+          <t>AUTOASSESS Open Call #2 for Tech Innovators</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-01-BIODIV-02-two-stage</t>
+          <t>HORIZON-CL4-2022-DIGITAL-EMERGING-02-07</t>
         </is>
       </c>
       <c r="C427" s="3" t="n">
-        <v>46065</v>
+        <v>46083</v>
       </c>
       <c r="D427" s="3" t="n">
-        <v>46288</v>
+        <v>46147.70833333334</v>
       </c>
       <c r="E427" s="4" t="n">
-        <v>3000000</v>
+        <v>1350000</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>Open topic: Using the Circular Cities and Regions Initiative to strengthen urban manufacturing in support of the Clean Industrial Deal</t>
+          <t>Open Horizons Open Call #3</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-01-CIRCBIO-02-two-stage</t>
+          <t>HORIZON-EIE-2024-CONNECT-01-02</t>
         </is>
       </c>
       <c r="C428" s="3" t="n">
-        <v>46065</v>
+        <v>46083</v>
       </c>
       <c r="D428" s="3" t="n">
-        <v>46288</v>
+        <v>46161.70833333334</v>
       </c>
       <c r="E428" s="4" t="n">
-        <v>6000000</v>
+        <v>475000</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>Deploying circular systemic solutions through living labs in cities and regions (Circular Cities and Regions Initiative topic)</t>
+          <t>First FIDELIS Open Call for Mentors and Peer-to-Peer Support Programme</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-01-CIRCBIO-01-two-stage</t>
+          <t>HORIZON-INFRA-2024-EOSC-01-03</t>
         </is>
       </c>
       <c r="C429" s="3" t="n">
-        <v>46065</v>
+        <v>46080</v>
       </c>
       <c r="D429" s="3" t="n">
-        <v>46288</v>
+        <v>46142.70833333334</v>
       </c>
       <c r="E429" s="4" t="n">
-        <v>5000000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>Unlocking the potential of citizen action for nature protection and restoration</t>
+          <t>Call for applications: FRONTIERS Science Journalism Residency Program (Call 4)</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-01-BIODIV-03-two-stage</t>
+          <t>ERC-2023-SJI-1</t>
         </is>
       </c>
       <c r="C430" s="3" t="n">
-        <v>46065</v>
+        <v>46078</v>
       </c>
       <c r="D430" s="3" t="n">
-        <v>46288</v>
+        <v>46167.79166666666</v>
       </c>
       <c r="E430" s="4" t="n">
-        <v>5000000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>Living labs for co-creating solutions for the restoration of ecosystems</t>
+          <t>Open Call 2 - Short Term and Long Term Funding to support ICT standardisation</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-01-BIODIV-01-two-stage</t>
+          <t>HORIZON-CL4-2024-HUMAN-03-04</t>
         </is>
       </c>
       <c r="C431" s="3" t="n">
-        <v>46065</v>
+        <v>46076</v>
       </c>
       <c r="D431" s="3" t="n">
-        <v>46288</v>
+        <v>46136.70833333334</v>
       </c>
       <c r="E431" s="4" t="n">
-        <v>7000000</v>
+        <v>650000</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>Decontaminate and bioremediate aquatic pollution</t>
+          <t>InnoMatch project - Open call 2 for EIC Awardees</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-01-ZEROPOLLUTION-01-two-stage</t>
+          <t>HORIZON-EIC-2023-INNOVPRO-01-01</t>
         </is>
       </c>
       <c r="C432" s="3" t="n">
-        <v>46065</v>
+        <v>46069</v>
       </c>
       <c r="D432" s="3" t="n">
-        <v>46288</v>
-      </c>
-      <c r="E432" s="4" t="n">
-        <v>7000000</v>
+        <v>46129.70833333334</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
         <is>
-          <t>Mainstreaming and scaling-up evidence-based Nature-Based Solutions towards a nature positive and climate-resilient economy</t>
+          <t>Living labs to enhance soil health in managed forests and in natural/semi-natural lands</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-01-BIODIV-04-two-stage</t>
+          <t>HORIZON-MISS-2026-05-SOIL-02-two-stage</t>
         </is>
       </c>
       <c r="C433" s="3" t="n">
         <v>46065</v>
       </c>
       <c r="D433" s="3" t="n">
-        <v>46288</v>
+        <v>46280</v>
       </c>
       <c r="E433" s="4" t="n">
-        <v>6000000</v>
+        <v>12000000</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>Open topic: Improving the competitiveness of the agricultural sector by enhancing the efficient and sustainable use of agricultural production factors</t>
+          <t>Open topic: Uncovering the causes of specific species’ rapid decline and exploring actionable solutions</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-FARM2FORK-01-two-stage</t>
+          <t>HORIZON-CL6-2026-01-BIODIV-02-two-stage</t>
         </is>
       </c>
       <c r="C434" s="3" t="n">
         <v>46065</v>
       </c>
       <c r="D434" s="3" t="n">
-        <v>46280</v>
+        <v>46288</v>
       </c>
       <c r="E434" s="4" t="n">
-        <v>4500000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
         <is>
-          <t>Open topic: Develop Earth Intelligence solutions using environmental observations and state-of-the-art AI for sustainable competitiveness and policy making</t>
+          <t>Open topic: Using the Circular Cities and Regions Initiative to strengthen urban manufacturing in support of the Clean Industrial Deal</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-03-GOVERNANCE-01-two-stage</t>
+          <t>HORIZON-CL6-2026-01-CIRCBIO-02-two-stage</t>
         </is>
       </c>
       <c r="C435" s="3" t="n">
         <v>46065</v>
       </c>
       <c r="D435" s="3" t="n">
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="E435" s="4" t="n">
         <v>6000000</v>
@@ -11235,201 +11081,201 @@
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>Living labs to enhance soil health in Alpine and Atlantic biogeographical regions</t>
+          <t>Deploying circular systemic solutions through living labs in cities and regions (Circular Cities and Regions Initiative topic)</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-05-SOIL-01-two-stage</t>
+          <t>HORIZON-CL6-2026-01-CIRCBIO-01-two-stage</t>
         </is>
       </c>
       <c r="C436" s="3" t="n">
         <v>46065</v>
       </c>
       <c r="D436" s="3" t="n">
-        <v>46280</v>
+        <v>46288</v>
       </c>
       <c r="E436" s="4" t="n">
-        <v>12000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
         <is>
-          <t>Open topic: Boosting organic farming for a competitive, sustainable and resilient farming sector</t>
+          <t>Unlocking the potential of citizen action for nature protection and restoration</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-FARM2FORK-02-two-stage</t>
+          <t>HORIZON-CL6-2026-01-BIODIV-03-two-stage</t>
         </is>
       </c>
       <c r="C437" s="3" t="n">
         <v>46065</v>
       </c>
       <c r="D437" s="3" t="n">
-        <v>46280</v>
+        <v>46288</v>
       </c>
       <c r="E437" s="4" t="n">
-        <v>6000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>Innovative interventions to prevent the harmful effects of using digital technologies on the mental health of children and young adults</t>
+          <t>Living labs for co-creating solutions for the restoration of ecosystems</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-DISEASE-02</t>
+          <t>HORIZON-CL6-2026-01-BIODIV-01-two-stage</t>
         </is>
       </c>
       <c r="C438" s="3" t="n">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="D438" s="3" t="n">
-        <v>46128</v>
+        <v>46288</v>
       </c>
       <c r="E438" s="4" t="n">
-        <v>8000000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
         <is>
-          <t>Advancing research on the prevention, diagnosis, and management of post-infection long-term conditions</t>
+          <t>Decontaminate and bioremediate aquatic pollution</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-DISEASE-03</t>
+          <t>HORIZON-CL6-2026-01-ZEROPOLLUTION-01-two-stage</t>
         </is>
       </c>
       <c r="C439" s="3" t="n">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="D439" s="3" t="n">
-        <v>46128</v>
+        <v>46288</v>
       </c>
       <c r="E439" s="4" t="n">
-        <v>6000000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>Identifying and addressing low-value care in health and care systems</t>
+          <t>Mainstreaming and scaling-up evidence-based Nature-Based Solutions towards a nature positive and climate-resilient economy</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-CARE-03</t>
+          <t>HORIZON-CL6-2026-01-BIODIV-04-two-stage</t>
         </is>
       </c>
       <c r="C440" s="3" t="n">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="D440" s="3" t="n">
-        <v>46128</v>
+        <v>46288</v>
       </c>
       <c r="E440" s="4" t="n">
-        <v>10000000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
         <is>
-          <t>Regulatory science to support translational development of patient-centred health technologies</t>
+          <t>Open topic: Improving the competitiveness of the agricultural sector by enhancing the efficient and sustainable use of agricultural production factors</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-IND-03</t>
+          <t>HORIZON-CL6-2026-02-FARM2FORK-01-two-stage</t>
         </is>
       </c>
       <c r="C441" s="3" t="n">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="D441" s="3" t="n">
-        <v>46128</v>
+        <v>46280</v>
       </c>
       <c r="E441" s="4" t="n">
-        <v>4000000</v>
+        <v>4500000</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>Towards a better understanding and anticipation of the impacts of climate change on health</t>
+          <t>Open topic: Develop Earth Intelligence solutions using environmental observations and state-of-the-art AI for sustainable competitiveness and policy making</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-ENVHLTH-01</t>
+          <t>HORIZON-CL6-2026-03-GOVERNANCE-01-two-stage</t>
         </is>
       </c>
       <c r="C442" s="3" t="n">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="D442" s="3" t="n">
-        <v>46128</v>
+        <v>46295</v>
       </c>
       <c r="E442" s="4" t="n">
-        <v>7000000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
         <is>
-          <t>Public procurement of innovative solutions for improving citizens' access to healthcare through integrated or personalised approaches</t>
+          <t>Living labs to enhance soil health in Alpine and Atlantic biogeographical regions</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-CARE-01</t>
+          <t>HORIZON-MISS-2026-05-SOIL-01-two-stage</t>
         </is>
       </c>
       <c r="C443" s="3" t="n">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="D443" s="3" t="n">
-        <v>46128</v>
+        <v>46280</v>
       </c>
       <c r="E443" s="4" t="n">
-        <v>3000000</v>
+        <v>12000000</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>Establishing a European network of Centres of Excellence (CoEs) for Advanced Therapies Medicinal Products (ATMPs)</t>
+          <t>Open topic: Boosting organic farming for a competitive, sustainable and resilient farming sector</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-TOOL-07</t>
+          <t>HORIZON-CL6-2026-02-FARM2FORK-02-two-stage</t>
         </is>
       </c>
       <c r="C444" s="3" t="n">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="D444" s="3" t="n">
-        <v>46128</v>
+        <v>46280</v>
       </c>
       <c r="E444" s="4" t="n">
-        <v>3900000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
         <is>
-          <t>Development of novel vaccines for viral pathogens with epidemic potential</t>
+          <t>Innovative interventions to prevent the harmful effects of using digital technologies on the mental health of children and young adults</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-DISEASE-04</t>
+          <t>HORIZON-HLTH-2026-01-DISEASE-02</t>
         </is>
       </c>
       <c r="C445" s="3" t="n">
@@ -11439,18 +11285,18 @@
         <v>46128</v>
       </c>
       <c r="E445" s="4" t="n">
-        <v>9000000</v>
+        <v>8000000</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>Towards climate resilient, prepared and carbon neutral populations and healthcare systems</t>
+          <t>Advancing research on the prevention, diagnosis, and management of post-infection long-term conditions</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-ENVHLTH-04</t>
+          <t>HORIZON-HLTH-2026-01-DISEASE-03</t>
         </is>
       </c>
       <c r="C446" s="3" t="n">
@@ -11460,18 +11306,18 @@
         <v>46128</v>
       </c>
       <c r="E446" s="4" t="n">
-        <v>7000000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
         <is>
-          <t>Support for a multilateral initiative on climate change and health research</t>
+          <t>Identifying and addressing low-value care in health and care systems</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-ENVHLTH-05</t>
+          <t>HORIZON-HLTH-2026-01-CARE-03</t>
         </is>
       </c>
       <c r="C447" s="3" t="n">
@@ -11481,18 +11327,18 @@
         <v>46128</v>
       </c>
       <c r="E447" s="4" t="n">
-        <v>3000000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
         <is>
-          <t>Enhancing and enlarging the European Partnership on Personalised Medicine (EP PerMEd) (Top-up)</t>
+          <t>Regulatory science to support translational development of patient-centred health technologies</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-04-CARE-04</t>
+          <t>HORIZON-HLTH-2026-01-IND-03</t>
         </is>
       </c>
       <c r="C448" s="3" t="n">
@@ -11502,18 +11348,18 @@
         <v>46128</v>
       </c>
       <c r="E448" s="4" t="n">
-        <v>9800000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
         <is>
-          <t>Multisectoral approach to tackle chronic non-communicable diseases: implementation research maximising collaboration and coordination with sectors and in settings beyond the healthcare system (GACD)</t>
+          <t>Towards a better understanding and anticipation of the impacts of climate change on health</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-DISEASE-09</t>
+          <t>HORIZON-HLTH-2026-01-ENVHLTH-01</t>
         </is>
       </c>
       <c r="C449" s="3" t="n">
@@ -11523,18 +11369,18 @@
         <v>46128</v>
       </c>
       <c r="E449" s="4" t="n">
-        <v>3000000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>Scaling up innovation in cardiovascular health</t>
+          <t>Public procurement of innovative solutions for improving citizens' access to healthcare through integrated or personalised approaches</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-DISEASE-15</t>
+          <t>HORIZON-HLTH-2026-01-CARE-01</t>
         </is>
       </c>
       <c r="C450" s="3" t="n">
@@ -11544,18 +11390,18 @@
         <v>46128</v>
       </c>
       <c r="E450" s="4" t="n">
-        <v>1900000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
         <is>
-          <t>Understanding of sex and/or gender-specific mechanisms of cardiovascular diseases: determinants, risk factors and pathways</t>
+          <t>Establishing a European network of Centres of Excellence (CoEs) for Advanced Therapies Medicinal Products (ATMPs)</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-DISEASE-11</t>
+          <t>HORIZON-HLTH-2026-01-TOOL-07</t>
         </is>
       </c>
       <c r="C451" s="3" t="n">
@@ -11565,39 +11411,39 @@
         <v>46128</v>
       </c>
       <c r="E451" s="4" t="n">
-        <v>6000000</v>
+        <v>3900000</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
         <is>
-          <t>European Partnership on Rare Diseases (ERDERA) (Phase 2)</t>
+          <t>Development of novel vaccines for viral pathogens with epidemic potential</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-02-DISEASE-12</t>
+          <t>HORIZON-HLTH-2026-01-DISEASE-04</t>
         </is>
       </c>
       <c r="C452" s="3" t="n">
         <v>46063</v>
       </c>
       <c r="D452" s="3" t="n">
-        <v>46280</v>
+        <v>46128</v>
       </c>
       <c r="E452" s="4" t="n">
-        <v>91300000</v>
+        <v>9000000</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
         <is>
-          <t>Support to European Research Area (ERA) action on accelerating New Approach Methodologies (NAMs) to advance biomedical research and testing of medicinal products and medical devices</t>
+          <t>Towards climate resilient, prepared and carbon neutral populations and healthcare systems</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-TOOL-06</t>
+          <t>HORIZON-HLTH-2026-01-ENVHLTH-04</t>
         </is>
       </c>
       <c r="C453" s="3" t="n">
@@ -11607,18 +11453,18 @@
         <v>46128</v>
       </c>
       <c r="E453" s="4" t="n">
-        <v>2900000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>Building public trust and outreach in the life sciences</t>
+          <t>Support for a multilateral initiative on climate change and health research</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-STAYHLTH-03</t>
+          <t>HORIZON-HLTH-2026-01-ENVHLTH-05</t>
         </is>
       </c>
       <c r="C454" s="3" t="n">
@@ -11628,18 +11474,18 @@
         <v>46128</v>
       </c>
       <c r="E454" s="4" t="n">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
         <is>
-          <t>Behavioural interventions as primary prevention for Non-Communicable Diseases (NCDs) among young people</t>
+          <t>Enhancing and enlarging the European Partnership on Personalised Medicine (EP PerMEd) (Top-up)</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-STAYHLTH-02</t>
+          <t>HORIZON-HLTH-2026-04-CARE-04</t>
         </is>
       </c>
       <c r="C455" s="3" t="n">
@@ -11649,18 +11495,18 @@
         <v>46128</v>
       </c>
       <c r="E455" s="4" t="n">
-        <v>9000000</v>
+        <v>9800000</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
         <is>
-          <t>Integrating New Approach Methodologies (NAMs) to advance biomedical research and regulatory testing</t>
+          <t>Multisectoral approach to tackle chronic non-communicable diseases: implementation research maximising collaboration and coordination with sectors and in settings beyond the healthcare system (GACD)</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-TOOL-03</t>
+          <t>HORIZON-HLTH-2026-01-DISEASE-09</t>
         </is>
       </c>
       <c r="C456" s="3" t="n">
@@ -11670,60 +11516,60 @@
         <v>46128</v>
       </c>
       <c r="E456" s="4" t="n">
-        <v>5000000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
         <is>
-          <t>Earlier and more precise palliative care</t>
+          <t>Scaling up innovation in cardiovascular health</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-02-CANCER-04</t>
+          <t>HORIZON-HLTH-2026-01-DISEASE-15</t>
         </is>
       </c>
       <c r="C457" s="3" t="n">
         <v>46063</v>
       </c>
       <c r="D457" s="3" t="n">
-        <v>46280</v>
+        <v>46128</v>
       </c>
       <c r="E457" s="4" t="n">
-        <v>5000000</v>
+        <v>1900000</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
         <is>
-          <t>Virtual Human Twin (VHT) Models for Cancer Research</t>
+          <t>Understanding of sex and/or gender-specific mechanisms of cardiovascular diseases: determinants, risk factors and pathways</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-02-CANCER-01</t>
+          <t>HORIZON-HLTH-2026-01-DISEASE-11</t>
         </is>
       </c>
       <c r="C458" s="3" t="n">
         <v>46063</v>
       </c>
       <c r="D458" s="3" t="n">
-        <v>46280</v>
+        <v>46128</v>
       </c>
       <c r="E458" s="4" t="n">
-        <v>8000000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
         <is>
-          <t>Improve the Quality of Life of older cancer patients</t>
+          <t>European Partnership on Rare Diseases (ERDERA) (Phase 2)</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-02-CANCER-07</t>
+          <t>HORIZON-HLTH-2026-02-DISEASE-12</t>
         </is>
       </c>
       <c r="C459" s="3" t="n">
@@ -11733,60 +11579,60 @@
         <v>46280</v>
       </c>
       <c r="E459" s="4" t="n">
-        <v>5000000</v>
+        <v>91300000</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
         <is>
-          <t>Pragmatic clinical trials to optimise immunotherapeutic interventions for patients with refractory cancers</t>
+          <t>Support to European Research Area (ERA) action on accelerating New Approach Methodologies (NAMs) to advance biomedical research and testing of medicinal products and medical devices</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-02-CANCER-03</t>
+          <t>HORIZON-HLTH-2026-01-TOOL-06</t>
         </is>
       </c>
       <c r="C460" s="3" t="n">
         <v>46063</v>
       </c>
       <c r="D460" s="3" t="n">
-        <v>46280</v>
+        <v>46128</v>
       </c>
       <c r="E460" s="4" t="n">
-        <v>7000000</v>
+        <v>2900000</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
         <is>
-          <t>Microbiome for early cancer prediction before the onset of disease</t>
+          <t>Building public trust and outreach in the life sciences</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-02-CANCER-02</t>
+          <t>HORIZON-HLTH-2026-01-STAYHLTH-03</t>
         </is>
       </c>
       <c r="C461" s="3" t="n">
         <v>46063</v>
       </c>
       <c r="D461" s="3" t="n">
-        <v>46280</v>
+        <v>46128</v>
       </c>
       <c r="E461" s="4" t="n">
-        <v>15000000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
         <is>
-          <t>Pilot actions for follow-on funding: Leveraging EU-funded collaborative research in regenerative medicine</t>
+          <t>Behavioural interventions as primary prevention for Non-Communicable Diseases (NCDs) among young people</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-TOOL-05</t>
+          <t>HORIZON-HLTH-2026-01-STAYHLTH-02</t>
         </is>
       </c>
       <c r="C462" s="3" t="n">
@@ -11796,39 +11642,39 @@
         <v>46128</v>
       </c>
       <c r="E462" s="4" t="n">
-        <v>6000000</v>
+        <v>9000000</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
         <is>
-          <t>Boosting mental health of young cancer survivors through the European Cancer Patient Digital Centre (ECPDC)</t>
+          <t>Integrating New Approach Methodologies (NAMs) to advance biomedical research and regulatory testing</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-02-CANCER-05</t>
+          <t>HORIZON-HLTH-2026-01-TOOL-03</t>
         </is>
       </c>
       <c r="C463" s="3" t="n">
         <v>46063</v>
       </c>
       <c r="D463" s="3" t="n">
-        <v>46280</v>
+        <v>46128</v>
       </c>
       <c r="E463" s="4" t="n">
-        <v>7000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
         <is>
-          <t>Development of a research capacity building programme on cancer with and for Ukraine</t>
+          <t>Earlier and more precise palliative care</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-02-CANCER-06</t>
+          <t>HORIZON-MISS-2026-02-CANCER-04</t>
         </is>
       </c>
       <c r="C464" s="3" t="n">
@@ -11844,19 +11690,19 @@
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
         <is>
-          <t>Components Development and Experimental Testing for an Onboard Liquid Hydrogen Supply and Conditioning System in High-Power Fuel Cell Aviation Applications</t>
+          <t>Virtual Human Twin (VHT) Models for Cancer Research</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-03-02</t>
+          <t>HORIZON-MISS-2026-02-CANCER-01</t>
         </is>
       </c>
       <c r="C465" s="3" t="n">
         <v>46063</v>
       </c>
       <c r="D465" s="3" t="n">
-        <v>46127</v>
+        <v>46280</v>
       </c>
       <c r="E465" s="4" t="n">
         <v>8000000</v>
@@ -11865,138 +11711,138 @@
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
         <is>
-          <t>Improved components and tools to increase the safety of electrolysers</t>
+          <t>Improve the Quality of Life of older cancer patients</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-01-03</t>
+          <t>HORIZON-MISS-2026-02-CANCER-07</t>
         </is>
       </c>
       <c r="C466" s="3" t="n">
         <v>46063</v>
       </c>
       <c r="D466" s="3" t="n">
-        <v>46127</v>
+        <v>46280</v>
       </c>
       <c r="E466" s="4" t="n">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
         <is>
-          <t>Demonstration of rSOC operation for local grid-connected hydrogen production and utilisation</t>
+          <t>Pragmatic clinical trials to optimise immunotherapeutic interventions for patients with refractory cancers</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-04-02</t>
+          <t>HORIZON-MISS-2026-02-CANCER-03</t>
         </is>
       </c>
       <c r="C467" s="3" t="n">
         <v>46063</v>
       </c>
       <c r="D467" s="3" t="n">
-        <v>46127</v>
+        <v>46280</v>
       </c>
       <c r="E467" s="4" t="n">
-        <v>8000000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
         <is>
-          <t>Multi-fuel SOFC powertrain for maritime transport</t>
+          <t>Microbiome for early cancer prediction before the onset of disease</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-03-04</t>
+          <t>HORIZON-MISS-2026-02-CANCER-02</t>
         </is>
       </c>
       <c r="C468" s="3" t="n">
         <v>46063</v>
       </c>
       <c r="D468" s="3" t="n">
-        <v>46127</v>
+        <v>46280</v>
       </c>
       <c r="E468" s="4" t="n">
-        <v>8000000</v>
+        <v>15000000</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="inlineStr">
         <is>
-          <t>Cost-efficient and reliable designs towards gigawatt-scale electrolytic hydrogen production plants</t>
+          <t>Pilot actions for follow-on funding: Leveraging EU-funded collaborative research in regenerative medicine</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-01-02</t>
+          <t>HORIZON-HLTH-2026-01-TOOL-05</t>
         </is>
       </c>
       <c r="C469" s="3" t="n">
         <v>46063</v>
       </c>
       <c r="D469" s="3" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="E469" s="4" t="n">
-        <v>2500000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
         <is>
-          <t>Demonstrating in-line inspection (ILI) to monitor cracks assuring compatibility for operation with hydrogen in new and re-purposed offshore natural gas pipelines</t>
+          <t>Boosting mental health of young cancer survivors through the European Cancer Patient Digital Centre (ECPDC)</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-02-02</t>
+          <t>HORIZON-MISS-2026-02-CANCER-05</t>
         </is>
       </c>
       <c r="C470" s="3" t="n">
         <v>46063</v>
       </c>
       <c r="D470" s="3" t="n">
-        <v>46127</v>
+        <v>46280</v>
       </c>
       <c r="E470" s="4" t="n">
-        <v>3500000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
         <is>
-          <t>Integration of control &amp; monitoring tools and strategies for improved Fuel Cell System durability &amp; reliability</t>
+          <t>Development of a research capacity building programme on cancer with and for Ukraine</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-03-01</t>
+          <t>HORIZON-MISS-2026-02-CANCER-06</t>
         </is>
       </c>
       <c r="C471" s="3" t="n">
         <v>46063</v>
       </c>
       <c r="D471" s="3" t="n">
-        <v>46127</v>
+        <v>46280</v>
       </c>
       <c r="E471" s="4" t="n">
-        <v>4000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
         <is>
-          <t>Flexible and standardised hydrogen storage system</t>
+          <t>Components Development and Experimental Testing for an Onboard Liquid Hydrogen Supply and Conditioning System in High-Power Fuel Cell Aviation Applications</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-03-03</t>
+          <t>HORIZON-JU-CLEANH2-2026-03-02</t>
         </is>
       </c>
       <c r="C472" s="3" t="n">
@@ -12006,18 +11852,18 @@
         <v>46127</v>
       </c>
       <c r="E472" s="4" t="n">
-        <v>5000000</v>
+        <v>8000000</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
         <is>
-          <t>Pre-Normative Research on hydrogen odorisation: enhancing safety and detection along the hydrogen value chain</t>
+          <t>Improved components and tools to increase the safety of electrolysers</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-05-02</t>
+          <t>HORIZON-JU-CLEANH2-2026-01-03</t>
         </is>
       </c>
       <c r="C473" s="3" t="n">
@@ -12033,12 +11879,12 @@
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
         <is>
-          <t>Next generation of reversible proton conducting ceramic cells and stacks for efficient energy applications at ≥1 kW scale</t>
+          <t>Demonstration of rSOC operation for local grid-connected hydrogen production and utilisation</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-04-01</t>
+          <t>HORIZON-JU-CLEANH2-2026-04-02</t>
         </is>
       </c>
       <c r="C474" s="3" t="n">
@@ -12048,18 +11894,18 @@
         <v>46127</v>
       </c>
       <c r="E474" s="4" t="n">
-        <v>3000000</v>
+        <v>8000000</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
         <is>
-          <t>Innovative business models advancing renewable electrolysis integration in industry</t>
+          <t>Multi-fuel SOFC powertrain for maritime transport</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-01-04</t>
+          <t>HORIZON-JU-CLEANH2-2026-03-04</t>
         </is>
       </c>
       <c r="C475" s="3" t="n">
@@ -12069,18 +11915,18 @@
         <v>46127</v>
       </c>
       <c r="E475" s="4" t="n">
-        <v>1500000</v>
+        <v>8000000</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
         <is>
-          <t>Affordable, Safe and Sustainable aboveground medium to large GH2 storage</t>
+          <t>Cost-efficient and reliable designs towards gigawatt-scale electrolytic hydrogen production plants</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-02-01</t>
+          <t>HORIZON-JU-CLEANH2-2026-01-02</t>
         </is>
       </c>
       <c r="C476" s="3" t="n">
@@ -12090,18 +11936,18 @@
         <v>46127</v>
       </c>
       <c r="E476" s="4" t="n">
-        <v>4000000</v>
+        <v>2500000</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="inlineStr">
         <is>
-          <t>New thermal insulation concepts for bulk liquid hydrogen shipping</t>
+          <t>Demonstrating in-line inspection (ILI) to monitor cracks assuring compatibility for operation with hydrogen in new and re-purposed offshore natural gas pipelines</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-02-03</t>
+          <t>HORIZON-JU-CLEANH2-2026-02-02</t>
         </is>
       </c>
       <c r="C477" s="3" t="n">
@@ -12111,18 +11957,18 @@
         <v>46127</v>
       </c>
       <c r="E477" s="4" t="n">
-        <v>4000000</v>
+        <v>3500000</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
         <is>
-          <t>Fuel-flexible gas turbine combustion technology for clean and efficient ammonia firing</t>
+          <t>Integration of control &amp; monitoring tools and strategies for improved Fuel Cell System durability &amp; reliability</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-04-03</t>
+          <t>HORIZON-JU-CLEANH2-2026-03-01</t>
         </is>
       </c>
       <c r="C478" s="3" t="n">
@@ -12132,18 +11978,18 @@
         <v>46127</v>
       </c>
       <c r="E478" s="4" t="n">
-        <v>5000000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
         <is>
-          <t>Scalable and high efficiency materials and reactors for direct solar hydrogen production</t>
+          <t>Flexible and standardised hydrogen storage system</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-01-06</t>
+          <t>HORIZON-JU-CLEANH2-2026-03-03</t>
         </is>
       </c>
       <c r="C479" s="3" t="n">
@@ -12153,18 +11999,18 @@
         <v>46127</v>
       </c>
       <c r="E479" s="4" t="n">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
         <is>
-          <t>Small-scale Hydrogen Valley</t>
+          <t>Pre-Normative Research on hydrogen odorisation: enhancing safety and detection along the hydrogen value chain</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-06-02</t>
+          <t>HORIZON-JU-CLEANH2-2026-05-02</t>
         </is>
       </c>
       <c r="C480" s="3" t="n">
@@ -12174,18 +12020,18 @@
         <v>46127</v>
       </c>
       <c r="E480" s="4" t="n">
-        <v>8000000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
         <is>
-          <t>Public datasets of technologies along the hydrogen value chain for life cycle (sustainability) assessment</t>
+          <t>Next generation of reversible proton conducting ceramic cells and stacks for efficient energy applications at ≥1 kW scale</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-05-01</t>
+          <t>HORIZON-JU-CLEANH2-2026-04-01</t>
         </is>
       </c>
       <c r="C481" s="3" t="n">
@@ -12195,18 +12041,18 @@
         <v>46127</v>
       </c>
       <c r="E481" s="4" t="n">
-        <v>2500000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
         <is>
-          <t>Development and validation of innovative approaches, catalysts, electrolytes and components for electrolysis technologies based on low-quality water</t>
+          <t>Innovative business models advancing renewable electrolysis integration in industry</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-01-01</t>
+          <t>HORIZON-JU-CLEANH2-2026-01-04</t>
         </is>
       </c>
       <c r="C482" s="3" t="n">
@@ -12216,18 +12062,18 @@
         <v>46127</v>
       </c>
       <c r="E482" s="4" t="n">
-        <v>3000000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
         <is>
-          <t>Cost-efficient small scale hydrogen liquefaction</t>
+          <t>Affordable, Safe and Sustainable aboveground medium to large GH2 storage</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-02-04</t>
+          <t>HORIZON-JU-CLEANH2-2026-02-01</t>
         </is>
       </c>
       <c r="C483" s="3" t="n">
@@ -12237,18 +12083,18 @@
         <v>46127</v>
       </c>
       <c r="E483" s="4" t="n">
-        <v>6000000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
         <is>
-          <t>Large-scale Hydrogen Valley</t>
+          <t>New thermal insulation concepts for bulk liquid hydrogen shipping</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-06-01</t>
+          <t>HORIZON-JU-CLEANH2-2026-02-03</t>
         </is>
       </c>
       <c r="C484" s="3" t="n">
@@ -12258,18 +12104,18 @@
         <v>46127</v>
       </c>
       <c r="E484" s="4" t="n">
-        <v>17000000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
         <is>
-          <t>Sustainable hydrogen production from renewable gases and biogenic waste sources through innovative modular reactor design, process intensification and integration</t>
+          <t>Fuel-flexible gas turbine combustion technology for clean and efficient ammonia firing</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-01-05</t>
+          <t>HORIZON-JU-CLEANH2-2026-04-03</t>
         </is>
       </c>
       <c r="C485" s="3" t="n">
@@ -12279,207 +12125,207 @@
         <v>46127</v>
       </c>
       <c r="E485" s="4" t="n">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
         <is>
-          <t>EIC 2026 Pathfinder Open</t>
+          <t>Scalable and high efficiency materials and reactors for direct solar hydrogen production</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>HORIZON-EIC-2026-PATHFINDEROPEN</t>
+          <t>HORIZON-JU-CLEANH2-2026-01-06</t>
         </is>
       </c>
       <c r="C486" s="3" t="n">
-        <v>46058</v>
+        <v>46063</v>
       </c>
       <c r="D486" s="3" t="n">
-        <v>46154</v>
+        <v>46127</v>
       </c>
       <c r="E486" s="4" t="n">
-        <v>1000000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
         <is>
-          <t>ROB4GREEN Open Call #1</t>
+          <t>Small-scale Hydrogen Valley</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2024-DIGITAL-EMERGING-01-04</t>
+          <t>HORIZON-JU-CLEANH2-2026-06-02</t>
         </is>
       </c>
       <c r="C487" s="3" t="n">
-        <v>46057</v>
+        <v>46063</v>
       </c>
       <c r="D487" s="3" t="n">
-        <v>46120.70833333334</v>
+        <v>46127</v>
       </c>
       <c r="E487" s="4" t="n">
-        <v>2400000</v>
+        <v>8000000</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
         <is>
-          <t>Standardising and supporting climate services for  climate adaptation</t>
+          <t>Public datasets of technologies along the hydrogen value chain for life cycle (sustainability) assessment</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-01-CLIMA-03</t>
+          <t>HORIZON-JU-CLEANH2-2026-05-01</t>
         </is>
       </c>
       <c r="C488" s="3" t="n">
-        <v>46057</v>
+        <v>46063</v>
       </c>
       <c r="D488" s="3" t="n">
-        <v>46288</v>
+        <v>46127</v>
       </c>
       <c r="E488" s="4" t="n">
-        <v>9000000</v>
+        <v>2500000</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
         <is>
-          <t>National Adaptation Hubs - Bringing together the national level with the engaged regional and local levels (multi-level governance)</t>
+          <t>Development and validation of innovative approaches, catalysts, electrolytes and components for electrolysis technologies based on low-quality water</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-01-CLIMA-01</t>
+          <t>HORIZON-JU-CLEANH2-2026-01-01</t>
         </is>
       </c>
       <c r="C489" s="3" t="n">
-        <v>46057</v>
+        <v>46063</v>
       </c>
       <c r="D489" s="3" t="n">
-        <v>46288</v>
+        <v>46127</v>
       </c>
       <c r="E489" s="4" t="n">
-        <v>10000000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
         <is>
-          <t>Bridging the gap between disaster risk management and climate adaptation</t>
+          <t>Cost-efficient small scale hydrogen liquefaction</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-01-CLIMA-04</t>
+          <t>HORIZON-JU-CLEANH2-2026-02-04</t>
         </is>
       </c>
       <c r="C490" s="3" t="n">
-        <v>46057</v>
+        <v>46063</v>
       </c>
       <c r="D490" s="3" t="n">
-        <v>46288</v>
+        <v>46127</v>
       </c>
       <c r="E490" s="4" t="n">
-        <v>5000000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
         <is>
-          <t>Supporting financing of local adaptation actions with combination of public funding and private financing</t>
+          <t>Large-scale Hydrogen Valley</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-01-CLIMA-07</t>
+          <t>HORIZON-JU-CLEANH2-2026-06-01</t>
         </is>
       </c>
       <c r="C491" s="3" t="n">
-        <v>46057</v>
+        <v>46063</v>
       </c>
       <c r="D491" s="3" t="n">
-        <v>46288</v>
+        <v>46127</v>
       </c>
       <c r="E491" s="4" t="n">
-        <v>20000000</v>
+        <v>17000000</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
         <is>
-          <t>Demonstrating solutions to protect and preserve cultural heritage from the impacts of climate change</t>
+          <t>Sustainable hydrogen production from renewable gases and biogenic waste sources through innovative modular reactor design, process intensification and integration</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-01-CLIMA-05</t>
+          <t>HORIZON-JU-CLEANH2-2026-01-05</t>
         </is>
       </c>
       <c r="C492" s="3" t="n">
-        <v>46057</v>
+        <v>46063</v>
       </c>
       <c r="D492" s="3" t="n">
-        <v>46288</v>
+        <v>46127</v>
       </c>
       <c r="E492" s="4" t="n">
-        <v>7000000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joint demonstration of solutions to build soil resilience to extreme weather events and support food security </t>
+          <t>EIC 2026 Pathfinder Open</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-06-CLIMA-SOIL</t>
+          <t>HORIZON-EIC-2026-PATHFINDEROPEN</t>
         </is>
       </c>
       <c r="C493" s="3" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="D493" s="3" t="n">
-        <v>46288</v>
+        <v>46154</v>
       </c>
       <c r="E493" s="4" t="n">
-        <v>10000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
         <is>
-          <t>Improving climate resilience of navigable inland waterways, their surroundings and related water infrastructure</t>
+          <t>ROB4GREEN Open Call #1</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-01-CLIMA-06</t>
+          <t>HORIZON-CL4-2024-DIGITAL-EMERGING-01-04</t>
         </is>
       </c>
       <c r="C494" s="3" t="n">
         <v>46057</v>
       </c>
       <c r="D494" s="3" t="n">
-        <v>46288</v>
+        <v>46120.70833333334</v>
       </c>
       <c r="E494" s="4" t="n">
-        <v>6000000</v>
+        <v>2400000</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="inlineStr">
         <is>
-          <t>Facilitating implementation of actionable solutions for climate adaptation of regions and local authorities</t>
+          <t>Standardising and supporting climate services for  climate adaptation</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-01-CLIMA-02</t>
+          <t>HORIZON-MISS-2026-01-CLIMA-03</t>
         </is>
       </c>
       <c r="C495" s="3" t="n">
@@ -12489,18 +12335,18 @@
         <v>46288</v>
       </c>
       <c r="E495" s="4" t="n">
-        <v>5000000</v>
+        <v>9000000</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
         <is>
-          <t>Leveraging long-term field experiments and other datasets to develop AI-ready decision support systems for sustainable soil management</t>
+          <t>National Adaptation Hubs - Bringing together the national level with the engaged regional and local levels (multi-level governance)</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-05-SOIL-04</t>
+          <t>HORIZON-MISS-2026-01-CLIMA-01</t>
         </is>
       </c>
       <c r="C496" s="3" t="n">
@@ -12510,18 +12356,18 @@
         <v>46288</v>
       </c>
       <c r="E496" s="4" t="n">
-        <v>9000000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="2" t="inlineStr">
         <is>
-          <t>Antimicrobial resistance and antibiotic biosynthesis in soils: developing key understanding and counteractive strategies using a One-Health approach</t>
+          <t>Bridging the gap between disaster risk management and climate adaptation</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-05-SOIL-02</t>
+          <t>HORIZON-MISS-2026-01-CLIMA-04</t>
         </is>
       </c>
       <c r="C497" s="3" t="n">
@@ -12531,18 +12377,18 @@
         <v>46288</v>
       </c>
       <c r="E497" s="4" t="n">
-        <v>7000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
         <is>
-          <t>Monitoring soil health in practice: equipping stakeholders to sample, analyse, and interpret soil health indicators</t>
+          <t>Supporting financing of local adaptation actions with combination of public funding and private financing</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-05-SOIL-01</t>
+          <t>HORIZON-MISS-2026-01-CLIMA-07</t>
         </is>
       </c>
       <c r="C498" s="3" t="n">
@@ -12552,18 +12398,18 @@
         <v>46288</v>
       </c>
       <c r="E498" s="4" t="n">
-        <v>5000000</v>
+        <v>20000000</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="inlineStr">
         <is>
-          <t>Enabling user-centred and open innovation initiatives to enhance soil health in Ukraine</t>
+          <t>Demonstrating solutions to protect and preserve cultural heritage from the impacts of climate change</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-05-SOIL-03</t>
+          <t>HORIZON-MISS-2026-01-CLIMA-05</t>
         </is>
       </c>
       <c r="C499" s="3" t="n">
@@ -12573,81 +12419,81 @@
         <v>46288</v>
       </c>
       <c r="E499" s="4" t="n">
-        <v>5000000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
         <is>
-          <t>Introducing circular economy models in the construction sector, from buildings to city scale</t>
+          <t xml:space="preserve">Joint demonstration of solutions to build soil resilience to extreme weather events and support food security </t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-04-CIT-NEB-B4P-CCRI-03</t>
+          <t>HORIZON-MISS-2026-06-CLIMA-SOIL</t>
         </is>
       </c>
       <c r="C500" s="3" t="n">
         <v>46057</v>
       </c>
       <c r="D500" s="3" t="n">
-        <v>46303</v>
+        <v>46288</v>
       </c>
       <c r="E500" s="4" t="n">
-        <v>9500000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="inlineStr">
         <is>
-          <t>Energy efficient urban and sub-urban public transport, complemented by shared mobility</t>
+          <t>Improving climate resilience of navigable inland waterways, their surroundings and related water infrastructure</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-04-CIT-01</t>
+          <t>HORIZON-MISS-2026-01-CLIMA-06</t>
         </is>
       </c>
       <c r="C501" s="3" t="n">
         <v>46057</v>
       </c>
       <c r="D501" s="3" t="n">
-        <v>46303</v>
+        <v>46288</v>
       </c>
       <c r="E501" s="4" t="n">
-        <v>10000000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
         <is>
-          <t>Transition to low-temperature heating solutions in multi-apartment buildings</t>
+          <t>Facilitating implementation of actionable solutions for climate adaptation of regions and local authorities</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-04-CIT-02</t>
+          <t>HORIZON-MISS-2026-01-CLIMA-02</t>
         </is>
       </c>
       <c r="C502" s="3" t="n">
         <v>46057</v>
       </c>
       <c r="D502" s="3" t="n">
-        <v>46303</v>
+        <v>46288</v>
       </c>
       <c r="E502" s="4" t="n">
-        <v>6000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="2" t="inlineStr">
         <is>
-          <t>Regional  (sea-basins) components of the EU Digital Twin Ocean</t>
+          <t>Leveraging long-term field experiments and other datasets to develop AI-ready decision support systems for sustainable soil management</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-03-OCEAN-05</t>
+          <t>HORIZON-MISS-2026-05-SOIL-04</t>
         </is>
       </c>
       <c r="C503" s="3" t="n">
@@ -12657,18 +12503,18 @@
         <v>46288</v>
       </c>
       <c r="E503" s="4" t="n">
-        <v>4000000</v>
+        <v>9000000</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
         <is>
-          <t>By fishers, for fishers: co-management of marine and freshwaters ecosystems and resources</t>
+          <t>Antimicrobial resistance and antibiotic biosynthesis in soils: developing key understanding and counteractive strategies using a One-Health approach</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-03-OCEAN-03</t>
+          <t>HORIZON-MISS-2026-05-SOIL-02</t>
         </is>
       </c>
       <c r="C504" s="3" t="n">
@@ -12684,12 +12530,12 @@
     <row r="505">
       <c r="A505" s="2" t="inlineStr">
         <is>
-          <t>Large-scale demonstration for mapping the distribution and condition of marine habitats to implement the Nature Restoration Regulation</t>
+          <t>Monitoring soil health in practice: equipping stakeholders to sample, analyse, and interpret soil health indicators</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-03-OCEAN-01</t>
+          <t>HORIZON-MISS-2026-05-SOIL-01</t>
         </is>
       </c>
       <c r="C505" s="3" t="n">
@@ -12699,18 +12545,18 @@
         <v>46288</v>
       </c>
       <c r="E505" s="4" t="n">
-        <v>7000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
         <is>
-          <t>Towards a European network of ocean technology testing sites</t>
+          <t>Enabling user-centred and open innovation initiatives to enhance soil health in Ukraine</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-03-OCEAN-04</t>
+          <t>HORIZON-MISS-2026-05-SOIL-03</t>
         </is>
       </c>
       <c r="C506" s="3" t="n">
@@ -12720,256 +12566,256 @@
         <v>46288</v>
       </c>
       <c r="E506" s="4" t="n">
-        <v>2500000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="2" t="inlineStr">
         <is>
-          <t>Addressing aquatic pollution and biodiversity loss through nature positive solutions from source to sea</t>
+          <t>Introducing circular economy models in the construction sector, from buildings to city scale</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-03-OCEAN-02</t>
+          <t>HORIZON-MISS-2026-04-CIT-NEB-B4P-CCRI-03</t>
         </is>
       </c>
       <c r="C507" s="3" t="n">
         <v>46057</v>
       </c>
       <c r="D507" s="3" t="n">
-        <v>46288</v>
+        <v>46303</v>
       </c>
       <c r="E507" s="4" t="n">
-        <v>7000000</v>
+        <v>9500000</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
         <is>
-          <t>Innovation for regional rail services and new guided transport systems</t>
+          <t>Energy efficient urban and sub-urban public transport, complemented by shared mobility</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>HORIZON-JU-ER-2026-FA6FA7-01</t>
+          <t>HORIZON-MISS-2026-04-CIT-01</t>
         </is>
       </c>
       <c r="C508" s="3" t="n">
         <v>46057</v>
       </c>
       <c r="D508" s="3" t="n">
-        <v>46149</v>
+        <v>46303</v>
       </c>
       <c r="E508" s="4" t="n">
-        <v>3100000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" s="2" t="inlineStr">
         <is>
-          <t>Safety and certification guidelines and demonstration of safety components for hyperloop</t>
+          <t>Transition to low-temperature heating solutions in multi-apartment buildings</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>HORIZON-JU-ER-2026-FA7-01</t>
+          <t>HORIZON-MISS-2026-04-CIT-02</t>
         </is>
       </c>
       <c r="C509" s="3" t="n">
         <v>46057</v>
       </c>
       <c r="D509" s="3" t="n">
-        <v>46149</v>
+        <v>46303</v>
       </c>
       <c r="E509" s="4" t="n">
-        <v>3000000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="2" t="inlineStr">
         <is>
-          <t>Knowledge to Practice: Develop applications and AI solutions utilizing the ForestWard Observatory</t>
+          <t>Regional  (sea-basins) components of the EU Digital Twin Ocean</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2022-CLIMATE-01-05</t>
+          <t>HORIZON-MISS-2026-03-OCEAN-05</t>
         </is>
       </c>
       <c r="C510" s="3" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="D510" s="3" t="n">
-        <v>46115.95833333334</v>
+        <v>46288</v>
       </c>
       <c r="E510" s="4" t="n">
-        <v>300000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" s="2" t="inlineStr">
         <is>
-          <t>RIA Global call according to SRIA 2026</t>
+          <t>By fishers, for fishers: co-management of marine and freshwaters ecosystems and resources</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CHIPS-2026-1-RIA</t>
+          <t>HORIZON-MISS-2026-03-OCEAN-03</t>
         </is>
       </c>
       <c r="C511" s="3" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="D511" s="3" t="n">
-        <v>46282</v>
+        <v>46288</v>
       </c>
       <c r="E511" s="4" t="n">
-        <v>1000000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" s="2" t="inlineStr">
         <is>
-          <t>IA Global call according to SRIA 2026</t>
+          <t>Large-scale demonstration for mapping the distribution and condition of marine habitats to implement the Nature Restoration Regulation</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CHIPS-2026-1-IA</t>
+          <t>HORIZON-MISS-2026-03-OCEAN-01</t>
         </is>
       </c>
       <c r="C512" s="3" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="D512" s="3" t="n">
-        <v>46282</v>
+        <v>46288</v>
       </c>
       <c r="E512" s="4" t="n">
-        <v>1000000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" s="2" t="inlineStr">
         <is>
-          <t>NGI Zero Commons Fund (2026-04Z)</t>
+          <t>Towards a European network of ocean technology testing sites</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2023-HUMAN-01-11</t>
+          <t>HORIZON-MISS-2026-03-OCEAN-04</t>
         </is>
       </c>
       <c r="C513" s="3" t="n">
-        <v>46054</v>
+        <v>46057</v>
       </c>
       <c r="D513" s="3" t="n">
-        <v>46113.5</v>
+        <v>46288</v>
       </c>
       <c r="E513" s="4" t="n">
-        <v>14000000</v>
+        <v>2500000</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" s="2" t="inlineStr">
         <is>
-          <t>BlueActionAA – Transition Agenda Call (BAAT-01)</t>
+          <t>Addressing aquatic pollution and biodiversity loss through nature positive solutions from source to sea</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-OCEAN-02-01</t>
+          <t>HORIZON-MISS-2026-03-OCEAN-02</t>
         </is>
       </c>
       <c r="C514" s="3" t="n">
-        <v>46052</v>
+        <v>46057</v>
       </c>
       <c r="D514" s="3" t="n">
-        <v>46171.58333333334</v>
+        <v>46288</v>
       </c>
       <c r="E514" s="4" t="n">
-        <v>1000000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" s="2" t="inlineStr">
         <is>
-          <t>SNS Operations and Output optimisation</t>
+          <t>Innovation for regional rail services and new guided transport systems</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>HORIZON-JU-SNS-2026-STREAM-CSA-01</t>
+          <t>HORIZON-JU-ER-2026-FA6FA7-01</t>
         </is>
       </c>
       <c r="C515" s="3" t="n">
-        <v>46051</v>
+        <v>46057</v>
       </c>
       <c r="D515" s="3" t="n">
-        <v>46141</v>
+        <v>46149</v>
       </c>
       <c r="E515" s="4" t="n">
-        <v>3000000</v>
+        <v>3100000</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" s="2" t="inlineStr">
         <is>
-          <t>6G Devices</t>
+          <t>Safety and certification guidelines and demonstration of safety components for hyperloop</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>HORIZON-JU-SNS-2026-STREAM-CSA-02</t>
+          <t>HORIZON-JU-ER-2026-FA7-01</t>
         </is>
       </c>
       <c r="C516" s="3" t="n">
-        <v>46051</v>
+        <v>46057</v>
       </c>
       <c r="D516" s="3" t="n">
-        <v>46141</v>
+        <v>46149</v>
       </c>
       <c r="E516" s="4" t="n">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" s="2" t="inlineStr">
         <is>
-          <t>Collection, Generation and Validation of Datasets  suitable for training AI Models for 6G Networks and for AIaaS</t>
+          <t>RIA Global call according to SRIA 2026</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>HORIZON-JU-SNS-2026-STREAM-B-01</t>
+          <t>HORIZON-JU-CHIPS-2026-1-RIA</t>
         </is>
       </c>
       <c r="C517" s="3" t="n">
-        <v>46051</v>
+        <v>46056</v>
       </c>
       <c r="D517" s="3" t="n">
-        <v>46141</v>
+        <v>46282</v>
       </c>
       <c r="E517" s="4" t="n">
-        <v>8000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" s="2" t="inlineStr">
         <is>
-          <t>EU-India International Collaboration</t>
+          <t>IA Global call according to SRIA 2026</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>HORIZON-JU-SNS-2026-STREAM-CSA-03</t>
+          <t>HORIZON-JU-CHIPS-2026-1-IA</t>
         </is>
       </c>
       <c r="C518" s="3" t="n">
-        <v>46051</v>
+        <v>46056</v>
       </c>
       <c r="D518" s="3" t="n">
-        <v>46141</v>
+        <v>46282</v>
       </c>
       <c r="E518" s="4" t="n">
         <v>1000000</v>
@@ -12978,216 +12824,219 @@
     <row r="519">
       <c r="A519" s="2" t="inlineStr">
         <is>
-          <t>SNS experimental infrastructure</t>
+          <t>BlueActionAA – Transition Agenda Call (BAAT-01)</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>HORIZON-JU-SNS-2026-STREAM-C-01</t>
+          <t>HORIZON-MISS-2024-OCEAN-02-01</t>
         </is>
       </c>
       <c r="C519" s="3" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="D519" s="3" t="n">
-        <v>46141</v>
+        <v>46171.58333333334</v>
       </c>
       <c r="E519" s="4" t="n">
-        <v>8000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" s="2" t="inlineStr">
         <is>
-          <t>Excel4Pro Open Call</t>
+          <t>SNS Operations and Output optimisation</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>HORIZON-WIDERA-2023-ACCESS-07-01</t>
+          <t>HORIZON-JU-SNS-2026-STREAM-CSA-01</t>
         </is>
       </c>
       <c r="C520" s="3" t="n">
-        <v>46048</v>
+        <v>46051</v>
       </c>
       <c r="D520" s="3" t="n">
-        <v>46139.70833333334</v>
+        <v>46141</v>
       </c>
       <c r="E520" s="4" t="n">
-        <v>360000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" s="2" t="inlineStr">
         <is>
-          <t>Shaping the Future of Animal Health and Welfare</t>
+          <t>6G Devices</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2023-FARM2FORK-01-2</t>
+          <t>HORIZON-JU-SNS-2026-STREAM-CSA-02</t>
         </is>
       </c>
       <c r="C521" s="3" t="n">
-        <v>46048</v>
+        <v>46051</v>
       </c>
       <c r="D521" s="3" t="n">
-        <v>46111.5</v>
+        <v>46141</v>
+      </c>
+      <c r="E521" s="4" t="n">
+        <v>2000000</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" s="2" t="inlineStr">
         <is>
-          <t>Renewable energy technology (RET) solutions in energy communities</t>
+          <t>Collection, Generation and Validation of Datasets  suitable for training AI Models for 6G Networks and for AIaaS</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2026-2-PRIZE</t>
+          <t>HORIZON-JU-SNS-2026-STREAM-B-01</t>
         </is>
       </c>
       <c r="C522" s="3" t="n">
-        <v>46042</v>
+        <v>46051</v>
       </c>
       <c r="D522" s="3" t="n">
-        <v>46198</v>
+        <v>46141</v>
+      </c>
+      <c r="E522" s="4" t="n">
+        <v>8000000</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" s="2" t="inlineStr">
         <is>
-          <t>ERC PROOF OF CONCEPT GRANTS</t>
+          <t>EU-India International Collaboration</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>ERC-2026-POC</t>
+          <t>HORIZON-JU-SNS-2026-STREAM-CSA-03</t>
         </is>
       </c>
       <c r="C523" s="3" t="n">
-        <v>46042</v>
+        <v>46051</v>
       </c>
       <c r="D523" s="3" t="n">
-        <v>46282</v>
+        <v>46141</v>
       </c>
       <c r="E523" s="4" t="n">
-        <v>150000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" s="2" t="inlineStr">
         <is>
-          <t>Joint Transnational Call 2026 for the BE READY Partnership: Advancing knowledge of host and pathogens dynamics to better combat emerging diseases</t>
+          <t>SNS experimental infrastructure</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2024-DISEASE-12-01</t>
+          <t>HORIZON-JU-SNS-2026-STREAM-C-01</t>
         </is>
       </c>
       <c r="C524" s="3" t="n">
-        <v>46041</v>
+        <v>46051</v>
       </c>
       <c r="D524" s="3" t="n">
-        <v>46254.54166666666</v>
+        <v>46141</v>
       </c>
       <c r="E524" s="4" t="n">
-        <v>16400000</v>
+        <v>8000000</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="2" t="inlineStr">
         <is>
-          <t>Developing and demonstrating core technologies for Virtual Worlds and Web 4.0 (IA) (Virtual worlds Partnership)</t>
+          <t>Excel4Pro Open Call</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-04-HUMAN-01</t>
+          <t>HORIZON-WIDERA-2023-ACCESS-07-01</t>
         </is>
       </c>
       <c r="C525" s="3" t="n">
-        <v>46037</v>
+        <v>46048</v>
       </c>
       <c r="D525" s="3" t="n">
-        <v>46127</v>
+        <v>46139.70833333334</v>
       </c>
       <c r="E525" s="4" t="n">
-        <v>4000000</v>
+        <v>360000</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" s="2" t="inlineStr">
         <is>
-          <t>Networking and Future Photonics Strategy  (CSA) (Photonics Partnership)</t>
+          <t>Renewable energy technology (RET) solutions in energy communities</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-14</t>
+          <t>HORIZON-CL5-2026-2-PRIZE</t>
         </is>
       </c>
       <c r="C526" s="3" t="n">
-        <v>46037</v>
+        <v>46042</v>
       </c>
       <c r="D526" s="3" t="n">
-        <v>46127</v>
-      </c>
-      <c r="E526" s="4" t="n">
-        <v>3000000</v>
+        <v>46198</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" s="2" t="inlineStr">
         <is>
-          <t>Fostering 2-Dimensional Materials (2DM) based emerging and enabling technologies (CSA)</t>
+          <t>ERC PROOF OF CONCEPT GRANTS</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-17</t>
+          <t>ERC-2026-POC</t>
         </is>
       </c>
       <c r="C527" s="3" t="n">
-        <v>46037</v>
+        <v>46042</v>
       </c>
       <c r="D527" s="3" t="n">
-        <v>46127</v>
+        <v>46282</v>
       </c>
       <c r="E527" s="4" t="n">
-        <v>1000000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" s="2" t="inlineStr">
         <is>
-          <t>Apply AI: Robotics for Manufacturing: Advancing Core Skills through Technical Challenges (RIA) (Partnership in AI, Data and Robotics)</t>
+          <t>Joint Transnational Call 2026 for the BE READY Partnership: Advancing knowledge of host and pathogens dynamics to better combat emerging diseases</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-08</t>
+          <t>HORIZON-HLTH-2024-DISEASE-12-01</t>
         </is>
       </c>
       <c r="C528" s="3" t="n">
-        <v>46037</v>
+        <v>46041</v>
       </c>
       <c r="D528" s="3" t="n">
-        <v>46127</v>
+        <v>46254.54166666666</v>
       </c>
       <c r="E528" s="4" t="n">
-        <v>18000000</v>
+        <v>16400000</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" s="2" t="inlineStr">
         <is>
-          <t>Strengthening the cooperation of semiconductor-intensive EU regions (CSA)</t>
+          <t>Developing and demonstrating core technologies for Virtual Worlds and Web 4.0 (IA) (Virtual worlds Partnership)</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-15</t>
+          <t>HORIZON-CL4-2026-04-HUMAN-01</t>
         </is>
       </c>
       <c r="C529" s="3" t="n">
@@ -13197,39 +13046,39 @@
         <v>46127</v>
       </c>
       <c r="E529" s="4" t="n">
-        <v>1000000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="2" t="inlineStr">
         <is>
-          <t>Boosting innovation for a better understanding of the determinants of health</t>
+          <t>Networking and Future Photonics Strategy  (CSA) (Photonics Partnership)</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>HORIZON-JU-IHI-2026-12-SINGLE-STAGE-01</t>
+          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-14</t>
         </is>
       </c>
       <c r="C530" s="3" t="n">
         <v>46037</v>
       </c>
       <c r="D530" s="3" t="n">
-        <v>46133</v>
+        <v>46127</v>
       </c>
       <c r="E530" s="4" t="n">
-        <v>8000000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" s="2" t="inlineStr">
         <is>
-          <t>Advanced Local Digital Twins using AI for Early Warning and Preparedness (IA)</t>
+          <t>Fostering 2-Dimensional Materials (2DM) based emerging and enabling technologies (CSA)</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-09</t>
+          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-17</t>
         </is>
       </c>
       <c r="C531" s="3" t="n">
@@ -13239,18 +13088,18 @@
         <v>46127</v>
       </c>
       <c r="E531" s="4" t="n">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" s="2" t="inlineStr">
         <is>
-          <t>Apply AI: Pilot of the “Science for AI” Pillar of RAISE (“Resource for AI science in Europe”) (RIA)</t>
+          <t>Apply AI: Robotics for Manufacturing: Advancing Core Skills through Technical Challenges (RIA) (Partnership in AI, Data and Robotics)</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-01</t>
+          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-08</t>
         </is>
       </c>
       <c r="C532" s="3" t="n">
@@ -13260,18 +13109,18 @@
         <v>46127</v>
       </c>
       <c r="E532" s="4" t="n">
-        <v>17000000</v>
+        <v>18000000</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" s="2" t="inlineStr">
         <is>
-          <t>Grand Challenge on Quantum Sensors for Inertial Navigation</t>
+          <t>Strengthening the cooperation of semiconductor-intensive EU regions (CSA)</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-11</t>
+          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-15</t>
         </is>
       </c>
       <c r="C533" s="3" t="n">
@@ -13281,18 +13130,18 @@
         <v>46127</v>
       </c>
       <c r="E533" s="4" t="n">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" s="2" t="inlineStr">
         <is>
-          <t>Boosting innovation through better integration of fragmented health R&amp;I efforts</t>
+          <t>Boosting innovation for a better understanding of the determinants of health</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>HORIZON-JU-IHI-2026-12-SINGLE-STAGE-02</t>
+          <t>HORIZON-JU-IHI-2026-12-SINGLE-STAGE-01</t>
         </is>
       </c>
       <c r="C534" s="3" t="n">
@@ -13302,165 +13151,165 @@
         <v>46133</v>
       </c>
       <c r="E534" s="4" t="n">
-        <v>15000000</v>
+        <v>8000000</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="2" t="inlineStr">
         <is>
-          <t>Boosting innovation through exploitation of digitalisation and data exchange in healthcare</t>
+          <t>Advanced Local Digital Twins using AI for Early Warning and Preparedness (IA)</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>HORIZON-JU-IHI-2026-12-SINGLE-STAGE-04</t>
+          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-09</t>
         </is>
       </c>
       <c r="C535" s="3" t="n">
         <v>46037</v>
       </c>
       <c r="D535" s="3" t="n">
-        <v>46133</v>
+        <v>46127</v>
       </c>
       <c r="E535" s="4" t="n">
-        <v>8000000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" s="2" t="inlineStr">
         <is>
-          <t>Boosting innovation for better assessment of the added value of innovative integrated healthcare solutions</t>
+          <t>Apply AI: Pilot of the “Science for AI” Pillar of RAISE (“Resource for AI science in Europe”) (RIA)</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>HORIZON-JU-IHI-2026-12-SINGLE-STAGE-05</t>
+          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-01</t>
         </is>
       </c>
       <c r="C536" s="3" t="n">
         <v>46037</v>
       </c>
       <c r="D536" s="3" t="n">
-        <v>46133</v>
+        <v>46127</v>
       </c>
       <c r="E536" s="4" t="n">
-        <v>5000000</v>
+        <v>17000000</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" s="2" t="inlineStr">
         <is>
-          <t>Boosting innovation for people-centred integrated healthcare solutions</t>
+          <t>Grand Challenge on Quantum Sensors for Inertial Navigation</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>HORIZON-JU-IHI-2026-12-SINGLE-STAGE-03</t>
+          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-11</t>
         </is>
       </c>
       <c r="C537" s="3" t="n">
         <v>46037</v>
       </c>
       <c r="D537" s="3" t="n">
-        <v>46133</v>
+        <v>46127</v>
       </c>
       <c r="E537" s="4" t="n">
-        <v>8000000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" s="2" t="inlineStr">
         <is>
-          <t>Efficient and compliant access to and use of data (IA) (AI, Data and Robotics partnership)</t>
+          <t>Boosting innovation through better integration of fragmented health R&amp;I efforts</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-04-DATA-06</t>
+          <t>HORIZON-JU-IHI-2026-12-SINGLE-STAGE-02</t>
         </is>
       </c>
       <c r="C538" s="3" t="n">
         <v>46037</v>
       </c>
       <c r="D538" s="3" t="n">
-        <v>46127</v>
+        <v>46133</v>
       </c>
       <c r="E538" s="4" t="n">
-        <v>11500000</v>
+        <v>15000000</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" s="2" t="inlineStr">
         <is>
-          <t>Large-Scale Photonic Quantum Computing Platform Technologies (RIA)</t>
+          <t>Boosting innovation through exploitation of digitalisation and data exchange in healthcare</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-18</t>
+          <t>HORIZON-JU-IHI-2026-12-SINGLE-STAGE-04</t>
         </is>
       </c>
       <c r="C539" s="3" t="n">
         <v>46037</v>
       </c>
       <c r="D539" s="3" t="n">
-        <v>46127</v>
+        <v>46133</v>
       </c>
       <c r="E539" s="4" t="n">
-        <v>10000000</v>
+        <v>8000000</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" s="2" t="inlineStr">
         <is>
-          <t>Challenge-Driven GenAI4EU Booster in Apply AI prioritised sectors (RIA) (AI/Data/Robotics Partnership)</t>
+          <t>Boosting innovation for better assessment of the added value of innovative integrated healthcare solutions</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-19</t>
+          <t>HORIZON-JU-IHI-2026-12-SINGLE-STAGE-05</t>
         </is>
       </c>
       <c r="C540" s="3" t="n">
         <v>46037</v>
       </c>
       <c r="D540" s="3" t="n">
-        <v>46127</v>
+        <v>46133</v>
       </c>
       <c r="E540" s="4" t="n">
-        <v>15000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" s="2" t="inlineStr">
         <is>
-          <t>Web 4.0 architectural framework and Open Internet Stack applications for virtual worlds (RIA)</t>
+          <t>Boosting innovation for people-centred integrated healthcare solutions</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-04-HUMAN-02</t>
+          <t>HORIZON-JU-IHI-2026-12-SINGLE-STAGE-03</t>
         </is>
       </c>
       <c r="C541" s="3" t="n">
         <v>46037</v>
       </c>
       <c r="D541" s="3" t="n">
-        <v>46127</v>
+        <v>46133</v>
       </c>
       <c r="E541" s="4" t="n">
-        <v>2800000</v>
+        <v>8000000</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" s="2" t="inlineStr">
         <is>
-          <t>Open Internet Stack Sovereign Solutions (RIA)</t>
+          <t>Efficient and compliant access to and use of data (IA) (AI, Data and Robotics partnership)</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-04-DATA-02</t>
+          <t>HORIZON-CL4-2026-04-DATA-06</t>
         </is>
       </c>
       <c r="C542" s="3" t="n">
@@ -13470,18 +13319,18 @@
         <v>46127</v>
       </c>
       <c r="E542" s="4" t="n">
-        <v>7000000</v>
+        <v>11500000</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" s="2" t="inlineStr">
         <is>
-          <t>Open Internet Stack Support for Scale (CSA)</t>
+          <t>Large-Scale Photonic Quantum Computing Platform Technologies (RIA)</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-04-DATA-03</t>
+          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-18</t>
         </is>
       </c>
       <c r="C543" s="3" t="n">
@@ -13491,18 +13340,18 @@
         <v>46127</v>
       </c>
       <c r="E543" s="4" t="n">
-        <v>4000000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" s="2" t="inlineStr">
         <is>
-          <t>Standards for Quantum Technologies – Coordination and Support Action (CSA)</t>
+          <t>Challenge-Driven GenAI4EU Booster in Apply AI prioritised sectors (RIA) (AI/Data/Robotics Partnership)</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-12</t>
+          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-19</t>
         </is>
       </c>
       <c r="C544" s="3" t="n">
@@ -13512,18 +13361,18 @@
         <v>46127</v>
       </c>
       <c r="E544" s="4" t="n">
-        <v>1000000</v>
+        <v>15000000</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" s="2" t="inlineStr">
         <is>
-          <t>New or enhanced Innovative Advanced Materials (IAM) enabled sensing functionality (RIA)</t>
+          <t>Web 4.0 architectural framework and Open Internet Stack applications for virtual worlds (RIA)</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-05-MAT-PROD-25</t>
+          <t>HORIZON-CL4-2026-04-HUMAN-02</t>
         </is>
       </c>
       <c r="C545" s="3" t="n">
@@ -13533,18 +13382,18 @@
         <v>46127</v>
       </c>
       <c r="E545" s="4" t="n">
-        <v>7500000</v>
+        <v>2800000</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" s="2" t="inlineStr">
         <is>
-          <t>Apply AI: Next-Generation Agile and Intelligent Robotics Platforms for Industrial and Service Applications (Partnership in AI, Data and Robotics) (RIA)</t>
+          <t>Open Internet Stack Sovereign Solutions (RIA)</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-05-DIGITAL-EMERGING-03</t>
+          <t>HORIZON-CL4-2026-04-DATA-02</t>
         </is>
       </c>
       <c r="C546" s="3" t="n">
@@ -13554,18 +13403,18 @@
         <v>46127</v>
       </c>
       <c r="E546" s="4" t="n">
-        <v>12000000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" s="2" t="inlineStr">
         <is>
-          <t>Next-Generation AI Agents for Real-World Applications in the Apply AI sectors (RIA) (Partnership in AI, Data and Robotics)</t>
+          <t>Open Internet Stack Support for Scale (CSA)</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-05-DIGITAL-EMERGING-02</t>
+          <t>HORIZON-CL4-2026-04-DATA-03</t>
         </is>
       </c>
       <c r="C547" s="3" t="n">
@@ -13575,144 +13424,144 @@
         <v>46127</v>
       </c>
       <c r="E547" s="4" t="n">
-        <v>19000000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" s="2" t="inlineStr">
         <is>
-          <t>Enhancing integrated research and healthcare in sub-Saharan Africa through digital innovation and Artificial Intelligence</t>
+          <t>Standards for Quantum Technologies – Coordination and Support Action (CSA)</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>HORIZON-JU-GH-EDCTP3-2026-03-DIGIT-02</t>
+          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-12</t>
         </is>
       </c>
       <c r="C548" s="3" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="D548" s="3" t="n">
-        <v>46267</v>
+        <v>46127</v>
       </c>
       <c r="E548" s="4" t="n">
-        <v>2250000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" s="2" t="inlineStr">
         <is>
-          <t>Training and innovation networks for sustained capacity development related to ethics, regulatory, pharmacovigilance, and related digital regulatory platforms</t>
+          <t>New or enhanced Innovative Advanced Materials (IAM) enabled sensing functionality (RIA)</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>HORIZON-JU-GH-EDCTP3-2026-03-SERP-01</t>
+          <t>HORIZON-CL4-2026-05-MAT-PROD-25</t>
         </is>
       </c>
       <c r="C549" s="3" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="D549" s="3" t="n">
-        <v>46267</v>
+        <v>46127</v>
       </c>
       <c r="E549" s="4" t="n">
-        <v>1500000</v>
+        <v>7500000</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" s="2" t="inlineStr">
         <is>
-          <t>Strengthening the EU plant protection ecosystem for a future-proof agriculture</t>
+          <t>Apply AI: Next-Generation Agile and Intelligent Robotics Platforms for Industrial and Service Applications (Partnership in AI, Data and Robotics) (RIA)</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-FARM2FORK-07</t>
+          <t>HORIZON-CL4-2026-05-DIGITAL-EMERGING-03</t>
         </is>
       </c>
       <c r="C550" s="3" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="D550" s="3" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="E550" s="4" t="n">
-        <v>3000000</v>
+        <v>12000000</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" s="2" t="inlineStr">
         <is>
-          <t>Developing innovative phytosanitary treatments for regulated plant pests to support safe international trade</t>
+          <t>Next-Generation AI Agents for Real-World Applications in the Apply AI sectors (RIA) (Partnership in AI, Data and Robotics)</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-FARM2FORK-01</t>
+          <t>HORIZON-CL4-2026-05-DIGITAL-EMERGING-02</t>
         </is>
       </c>
       <c r="C551" s="3" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="D551" s="3" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="E551" s="4" t="n">
-        <v>5900000</v>
+        <v>19000000</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" s="2" t="inlineStr">
         <is>
-          <t>Leveraging R&amp;I knowledge on microbiome</t>
+          <t>Enhancing integrated research and healthcare in sub-Saharan Africa through digital innovation and Artificial Intelligence</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-FARM2FORK-12</t>
+          <t>HORIZON-JU-GH-EDCTP3-2026-03-DIGIT-02</t>
         </is>
       </c>
       <c r="C552" s="3" t="n">
         <v>46036</v>
       </c>
       <c r="D552" s="3" t="n">
-        <v>46126</v>
+        <v>46267</v>
       </c>
       <c r="E552" s="4" t="n">
-        <v>2000000</v>
+        <v>2250000</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" s="2" t="inlineStr">
         <is>
-          <t>Advancing basic knowledge and developing tools for sustainable management of key migratory fish species</t>
+          <t>Training and innovation networks for sustained capacity development related to ethics, regulatory, pharmacovigilance, and related digital regulatory platforms</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-FARM2FORK-08</t>
+          <t>HORIZON-JU-GH-EDCTP3-2026-03-SERP-01</t>
         </is>
       </c>
       <c r="C553" s="3" t="n">
         <v>46036</v>
       </c>
       <c r="D553" s="3" t="n">
-        <v>46126</v>
+        <v>46267</v>
       </c>
       <c r="E553" s="4" t="n">
-        <v>7000000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" s="2" t="inlineStr">
         <is>
-          <t>Boosting sustainable competitiveness in rural areas through innovation</t>
+          <t>Strengthening the EU plant protection ecosystem for a future-proof agriculture</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-COMMUNITIES-01</t>
+          <t>HORIZON-CL6-2026-02-FARM2FORK-07</t>
         </is>
       </c>
       <c r="C554" s="3" t="n">
@@ -13722,18 +13571,18 @@
         <v>46126</v>
       </c>
       <c r="E554" s="4" t="n">
-        <v>5000000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" s="2" t="inlineStr">
         <is>
-          <t>Boosting the competitiveness of protein crops in Europe</t>
+          <t>Developing innovative phytosanitary treatments for regulated plant pests to support safe international trade</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-FARM2FORK-03</t>
+          <t>HORIZON-CL6-2026-02-FARM2FORK-01</t>
         </is>
       </c>
       <c r="C555" s="3" t="n">
@@ -13743,18 +13592,18 @@
         <v>46126</v>
       </c>
       <c r="E555" s="4" t="n">
-        <v>6000000</v>
+        <v>5900000</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" s="2" t="inlineStr">
         <is>
-          <t>Integrating a holistic perspective in microbiome research for resilient, competitive and sustainable food systems</t>
+          <t>Leveraging R&amp;I knowledge on microbiome</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-FARM2FORK-11</t>
+          <t>HORIZON-CL6-2026-02-FARM2FORK-12</t>
         </is>
       </c>
       <c r="C556" s="3" t="n">
@@ -13764,18 +13613,18 @@
         <v>46126</v>
       </c>
       <c r="E556" s="4" t="n">
-        <v>5000000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" s="2" t="inlineStr">
         <is>
-          <t>Tackling pesticide resistance: early detection, management strategies, and foresight</t>
+          <t>Advancing basic knowledge and developing tools for sustainable management of key migratory fish species</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-FARM2FORK-02</t>
+          <t>HORIZON-CL6-2026-02-FARM2FORK-08</t>
         </is>
       </c>
       <c r="C557" s="3" t="n">
@@ -13785,18 +13634,18 @@
         <v>46126</v>
       </c>
       <c r="E557" s="4" t="n">
-        <v>6000000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" s="2" t="inlineStr">
         <is>
-          <t>Boosting plant health and reducing losses on farm and during storage for sustainable growth in Africa (FNSSA)</t>
+          <t>Boosting sustainable competitiveness in rural areas through innovation</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-FARM2FORK-13</t>
+          <t>HORIZON-CL6-2026-02-COMMUNITIES-01</t>
         </is>
       </c>
       <c r="C558" s="3" t="n">
@@ -13806,18 +13655,18 @@
         <v>46126</v>
       </c>
       <c r="E558" s="4" t="n">
-        <v>6000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" s="2" t="inlineStr">
         <is>
-          <t>Advanced innovative solutions for improved competitiveness and sustainability in controlled environment agriculture (CEA)</t>
+          <t>Boosting the competitiveness of protein crops in Europe</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-FARM2FORK-06</t>
+          <t>HORIZON-CL6-2026-02-FARM2FORK-03</t>
         </is>
       </c>
       <c r="C559" s="3" t="n">
@@ -13833,82 +13682,82 @@
     <row r="560">
       <c r="A560" s="2" t="inlineStr">
         <is>
-          <t>Additional activities for the Sustainable Blue Economy Partnership (SBEP)</t>
+          <t>Integrating a holistic perspective in microbiome research for resilient, competitive and sustainable food systems</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-03-GOVERNANCE-01</t>
+          <t>HORIZON-CL6-2026-02-FARM2FORK-11</t>
         </is>
       </c>
       <c r="C560" s="3" t="n">
         <v>46036</v>
       </c>
       <c r="D560" s="3" t="n">
-        <v>46127</v>
+        <v>46126</v>
       </c>
       <c r="E560" s="4" t="n">
-        <v>38000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" s="2" t="inlineStr">
         <is>
-          <t>Interconnect Earth Observation research for addressing environmental policies</t>
+          <t>Tackling pesticide resistance: early detection, management strategies, and foresight</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-03-GOVERNANCE-07</t>
+          <t>HORIZON-CL6-2026-02-FARM2FORK-02</t>
         </is>
       </c>
       <c r="C561" s="3" t="n">
         <v>46036</v>
       </c>
       <c r="D561" s="3" t="n">
-        <v>46127</v>
+        <v>46126</v>
       </c>
       <c r="E561" s="4" t="n">
-        <v>5400000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" s="2" t="inlineStr">
         <is>
-          <t>Boosting data availability and AI solutions in food for consumers and food service professionals</t>
+          <t>Boosting plant health and reducing losses on farm and during storage for sustainable growth in Africa (FNSSA)</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-03-GOVERNANCE-08</t>
+          <t>HORIZON-CL6-2026-02-FARM2FORK-13</t>
         </is>
       </c>
       <c r="C562" s="3" t="n">
         <v>46036</v>
       </c>
       <c r="D562" s="3" t="n">
-        <v>46127</v>
+        <v>46126</v>
       </c>
       <c r="E562" s="4" t="n">
-        <v>7500000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" s="2" t="inlineStr">
         <is>
-          <t>A services and business incubator for geospatial open-source developments</t>
+          <t>Advanced innovative solutions for improved competitiveness and sustainability in controlled environment agriculture (CEA)</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-03-GOVERNANCE-06</t>
+          <t>HORIZON-CL6-2026-02-FARM2FORK-06</t>
         </is>
       </c>
       <c r="C563" s="3" t="n">
         <v>46036</v>
       </c>
       <c r="D563" s="3" t="n">
-        <v>46127</v>
+        <v>46126</v>
       </c>
       <c r="E563" s="4" t="n">
         <v>6000000</v>
@@ -13917,33 +13766,33 @@
     <row r="564">
       <c r="A564" s="2" t="inlineStr">
         <is>
-          <t>Towards more effective, fair and coherent policies for climate change mitigation and adaptation in agriculture and forestry</t>
+          <t>Additional activities for the Sustainable Blue Economy Partnership (SBEP)</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-CLIMATE-01</t>
+          <t>HORIZON-CL6-2026-03-GOVERNANCE-01</t>
         </is>
       </c>
       <c r="C564" s="3" t="n">
         <v>46036</v>
       </c>
       <c r="D564" s="3" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="E564" s="4" t="n">
-        <v>6000000</v>
+        <v>38000000</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" s="2" t="inlineStr">
         <is>
-          <t>Empowering the UN Decade of Ocean Science for Sustainable Development</t>
+          <t>Interconnect Earth Observation research for addressing environmental policies</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-03-GOVERNANCE-03</t>
+          <t>HORIZON-CL6-2026-03-GOVERNANCE-07</t>
         </is>
       </c>
       <c r="C565" s="3" t="n">
@@ -13953,18 +13802,18 @@
         <v>46127</v>
       </c>
       <c r="E565" s="4" t="n">
-        <v>3000000</v>
+        <v>5400000</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" s="2" t="inlineStr">
         <is>
-          <t>Supporting All-Atlantic Ocean Research and Innovation Alliance</t>
+          <t>Boosting data availability and AI solutions in food for consumers and food service professionals</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-03-GOVERNANCE-04</t>
+          <t>HORIZON-CL6-2026-03-GOVERNANCE-08</t>
         </is>
       </c>
       <c r="C566" s="3" t="n">
@@ -13974,18 +13823,18 @@
         <v>46127</v>
       </c>
       <c r="E566" s="4" t="n">
-        <v>4500000</v>
+        <v>7500000</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" s="2" t="inlineStr">
         <is>
-          <t>Coordinated European contribution to the WMO Global Greenhouse Gas Watch and its international governance</t>
+          <t>A services and business incubator for geospatial open-source developments</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-03-GOVERNANCE-05</t>
+          <t>HORIZON-CL6-2026-03-GOVERNANCE-06</t>
         </is>
       </c>
       <c r="C567" s="3" t="n">
@@ -13995,18 +13844,18 @@
         <v>46127</v>
       </c>
       <c r="E567" s="4" t="n">
-        <v>7000000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" s="2" t="inlineStr">
         <is>
-          <t>Sustainable and healthy diets for cardiovascular diseases prevention with the support of digital applications</t>
+          <t>Towards more effective, fair and coherent policies for climate change mitigation and adaptation in agriculture and forestry</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-FARM2FORK-09</t>
+          <t>HORIZON-CL6-2026-02-CLIMATE-01</t>
         </is>
       </c>
       <c r="C568" s="3" t="n">
@@ -14016,39 +13865,39 @@
         <v>46126</v>
       </c>
       <c r="E568" s="4" t="n">
-        <v>5000000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" s="2" t="inlineStr">
         <is>
-          <t>Boosting circularity and diversification strategies of terrestrial livestock production systems</t>
+          <t>Empowering the UN Decade of Ocean Science for Sustainable Development</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-FARM2FORK-05</t>
+          <t>HORIZON-CL6-2026-03-GOVERNANCE-03</t>
         </is>
       </c>
       <c r="C569" s="3" t="n">
         <v>46036</v>
       </c>
       <c r="D569" s="3" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="E569" s="4" t="n">
-        <v>6000000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" s="2" t="inlineStr">
         <is>
-          <t>Embracing innovation in agriculture by peer-to-peer learning via on farm-demonstrations and cost-benefit analysis</t>
+          <t>Supporting All-Atlantic Ocean Research and Innovation Alliance</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-03-GOVERNANCE-10</t>
+          <t>HORIZON-CL6-2026-03-GOVERNANCE-04</t>
         </is>
       </c>
       <c r="C570" s="3" t="n">
@@ -14058,18 +13907,18 @@
         <v>46127</v>
       </c>
       <c r="E570" s="4" t="n">
-        <v>4000000</v>
+        <v>4500000</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" s="2" t="inlineStr">
         <is>
-          <t>Improving analytical capacity and understanding of social drivers in agriculture to better assess social sustainability in the sector</t>
+          <t>Coordinated European contribution to the WMO Global Greenhouse Gas Watch and its international governance</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-03-GOVERNANCE-02</t>
+          <t>HORIZON-CL6-2026-03-GOVERNANCE-05</t>
         </is>
       </c>
       <c r="C571" s="3" t="n">
@@ -14079,18 +13928,18 @@
         <v>46127</v>
       </c>
       <c r="E571" s="4" t="n">
-        <v>5000000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" s="2" t="inlineStr">
         <is>
-          <t>Sustainable and healthy diets based on health status and socio-economic risk factors of ageing population</t>
+          <t>Sustainable and healthy diets for cardiovascular diseases prevention with the support of digital applications</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-FARM2FORK-10</t>
+          <t>HORIZON-CL6-2026-02-FARM2FORK-09</t>
         </is>
       </c>
       <c r="C572" s="3" t="n">
@@ -14100,18 +13949,18 @@
         <v>46126</v>
       </c>
       <c r="E572" s="4" t="n">
-        <v>2000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" s="2" t="inlineStr">
         <is>
-          <t>Green Transition Food Processing Africa</t>
+          <t>Boosting circularity and diversification strategies of terrestrial livestock production systems</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-FARM2FORK-14</t>
+          <t>HORIZON-CL6-2026-02-FARM2FORK-05</t>
         </is>
       </c>
       <c r="C573" s="3" t="n">
@@ -14121,46 +13970,46 @@
         <v>46126</v>
       </c>
       <c r="E573" s="4" t="n">
-        <v>5000000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" s="2" t="inlineStr">
         <is>
-          <t>Accelerating the development of breeding tools for perennial crops, specifically fruits and nuts</t>
+          <t>Embracing innovation in agriculture by peer-to-peer learning via on farm-demonstrations and cost-benefit analysis</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-FARM2FORK-04</t>
+          <t>HORIZON-CL6-2026-03-GOVERNANCE-10</t>
         </is>
       </c>
       <c r="C574" s="3" t="n">
         <v>46036</v>
       </c>
       <c r="D574" s="3" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="E574" s="4" t="n">
-        <v>6000000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" s="2" t="inlineStr">
         <is>
-          <t>Towards the water infrastructures of the future</t>
+          <t>Improving analytical capacity and understanding of social drivers in agriculture to better assess social sustainability in the sector</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-CLIMATE-02</t>
+          <t>HORIZON-CL6-2026-03-GOVERNANCE-02</t>
         </is>
       </c>
       <c r="C575" s="3" t="n">
         <v>46036</v>
       </c>
       <c r="D575" s="3" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="E575" s="4" t="n">
         <v>5000000</v>
@@ -14169,201 +14018,201 @@
     <row r="576">
       <c r="A576" s="2" t="inlineStr">
         <is>
-          <t>Increasing knowledge flows to practice within AKIS via EU thematic knowledge hubs</t>
+          <t>Sustainable and healthy diets based on health status and socio-economic risk factors of ageing population</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-03-GOVERNANCE-09</t>
+          <t>HORIZON-CL6-2026-02-FARM2FORK-10</t>
         </is>
       </c>
       <c r="C576" s="3" t="n">
         <v>46036</v>
       </c>
       <c r="D576" s="3" t="n">
-        <v>46127</v>
+        <v>46126</v>
       </c>
       <c r="E576" s="4" t="n">
-        <v>3500000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" s="2" t="inlineStr">
         <is>
-          <t>Hop-On Facility</t>
+          <t>Green Transition Food Processing Africa</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>HORIZON-WIDERA-2026-03-WIDENING-01</t>
+          <t>HORIZON-CL6-2026-02-FARM2FORK-14</t>
         </is>
       </c>
       <c r="C577" s="3" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="D577" s="3" t="n">
-        <v>46289</v>
+        <v>46126</v>
       </c>
       <c r="E577" s="4" t="n">
-        <v>200000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" s="2" t="inlineStr">
         <is>
-          <t>FIERCE 1st Open Call for the Financial Support Program</t>
+          <t>Accelerating the development of breeding tools for perennial crops, specifically fruits and nuts</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2024-RESILIENCE-01-41</t>
+          <t>HORIZON-CL6-2026-02-FARM2FORK-04</t>
         </is>
       </c>
       <c r="C578" s="3" t="n">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="D578" s="3" t="n">
-        <v>46112.99930555555</v>
+        <v>46126</v>
       </c>
       <c r="E578" s="4" t="n">
-        <v>1250000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" s="2" t="inlineStr">
         <is>
-          <t>EP BrainHealth Call 1 | Biological, social and environmental factors that impact the trajectory of brain health across the lifespan – in the field of neurological, mental and sensory disorders</t>
+          <t>Towards the water infrastructures of the future</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2025-02-DISEASE-01</t>
+          <t>HORIZON-CL6-2026-02-CLIMATE-02</t>
         </is>
       </c>
       <c r="C579" s="3" t="n">
-        <v>46030</v>
+        <v>46036</v>
       </c>
       <c r="D579" s="3" t="n">
-        <v>46203.58333333334</v>
+        <v>46126</v>
       </c>
       <c r="E579" s="4" t="n">
-        <v>26260000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" s="2" t="inlineStr">
         <is>
-          <t>EP BrainHealth Call 2 | Biological, social and environmental factors that impact the trajectory of brain health across the lifespan – in the field of neurodegeneration</t>
+          <t>Increasing knowledge flows to practice within AKIS via EU thematic knowledge hubs</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2025-02-DISEASE-01</t>
+          <t>HORIZON-CL6-2026-03-GOVERNANCE-09</t>
         </is>
       </c>
       <c r="C580" s="3" t="n">
-        <v>46030</v>
+        <v>46036</v>
       </c>
       <c r="D580" s="3" t="n">
-        <v>46203.58333333334</v>
+        <v>46127</v>
       </c>
       <c r="E580" s="4" t="n">
-        <v>27540000</v>
+        <v>3500000</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" s="2" t="inlineStr">
         <is>
-          <t>Twinning</t>
+          <t>Hop-On Facility</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>HORIZON-WIDERA-2026-02-WIDENING-01</t>
+          <t>HORIZON-WIDERA-2026-03-WIDENING-01</t>
         </is>
       </c>
       <c r="C581" s="3" t="n">
-        <v>46030</v>
+        <v>46035</v>
       </c>
       <c r="D581" s="3" t="n">
-        <v>46121</v>
+        <v>46289</v>
       </c>
       <c r="E581" s="4" t="n">
-        <v>800000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" s="2" t="inlineStr">
         <is>
-          <t>Optimise the usage of resources in a circular economy (RIA) (Processes4Planet and Clean Steel partnerships)</t>
+          <t>EP BrainHealth Call 1 | Biological, social and environmental factors that impact the trajectory of brain health across the lifespan – in the field of neurological, mental and sensory disorders</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-01-MAT-PROD-04</t>
+          <t>HORIZON-HLTH-2025-02-DISEASE-01</t>
         </is>
       </c>
       <c r="C582" s="3" t="n">
-        <v>46028</v>
+        <v>46030</v>
       </c>
       <c r="D582" s="3" t="n">
-        <v>46133</v>
+        <v>46203.58333333334</v>
       </c>
       <c r="E582" s="4" t="n">
-        <v>5000000</v>
+        <v>26260000</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" s="2" t="inlineStr">
         <is>
-          <t>Attracting management talent for capacity building for Technology Infrastructures staff members (CSA)</t>
+          <t>EP BrainHealth Call 2 | Biological, social and environmental factors that impact the trajectory of brain health across the lifespan – in the field of neurodegeneration</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-01-MAT-PROD-44</t>
+          <t>HORIZON-HLTH-2025-02-DISEASE-01</t>
         </is>
       </c>
       <c r="C583" s="3" t="n">
-        <v>46028</v>
+        <v>46030</v>
       </c>
       <c r="D583" s="3" t="n">
-        <v>46133</v>
+        <v>46203.58333333334</v>
       </c>
       <c r="E583" s="4" t="n">
-        <v>2500000</v>
+        <v>27540000</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
         <is>
-          <t>‘Proof of market’ to improve valorisation and commercialisation of Horizon generated R&amp;I results (IA)</t>
+          <t>Twinning</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-01-MAT-PROD-48</t>
+          <t>HORIZON-WIDERA-2026-02-WIDENING-01</t>
         </is>
       </c>
       <c r="C584" s="3" t="n">
-        <v>46028</v>
+        <v>46030</v>
       </c>
       <c r="D584" s="3" t="n">
-        <v>46133</v>
+        <v>46121</v>
       </c>
       <c r="E584" s="4" t="n">
-        <v>200000</v>
+        <v>800000</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" s="2" t="inlineStr">
         <is>
-          <t>Efficient capture / purification / utilisation of CO2 for the production of competitive products (RIA) (Processes4Planet partnership)</t>
+          <t>Optimise the usage of resources in a circular economy (RIA) (Processes4Planet and Clean Steel partnerships)</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-01-MAT-PROD-31</t>
+          <t>HORIZON-CL4-2026-01-MAT-PROD-04</t>
         </is>
       </c>
       <c r="C585" s="3" t="n">
@@ -14379,12 +14228,12 @@
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>Mapping and service finder for Technology Infrastructures (CSA)</t>
+          <t>Attracting management talent for capacity building for Technology Infrastructures staff members (CSA)</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-01-MAT-PROD-46</t>
+          <t>HORIZON-CL4-2026-01-MAT-PROD-44</t>
         </is>
       </c>
       <c r="C586" s="3" t="n">
@@ -14394,18 +14243,18 @@
         <v>46133</v>
       </c>
       <c r="E586" s="4" t="n">
-        <v>2000000</v>
+        <v>2500000</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" s="2" t="inlineStr">
         <is>
-          <t>Improving availability of secondary raw materials through recycling (IA)</t>
+          <t>‘Proof of market’ to improve valorisation and commercialisation of Horizon generated R&amp;I results (IA)</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-01-MAT-PROD-14</t>
+          <t>HORIZON-CL4-2026-01-MAT-PROD-48</t>
         </is>
       </c>
       <c r="C587" s="3" t="n">
@@ -14415,18 +14264,18 @@
         <v>46133</v>
       </c>
       <c r="E587" s="4" t="n">
-        <v>7500000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>Advanced manufacturing for key products (IA) (Made in Europe partnership)</t>
+          <t>Efficient capture / purification / utilisation of CO2 for the production of competitive products (RIA) (Processes4Planet partnership)</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-01-MAT-PROD-01</t>
+          <t>HORIZON-CL4-2026-01-MAT-PROD-31</t>
         </is>
       </c>
       <c r="C588" s="3" t="n">
@@ -14436,18 +14285,18 @@
         <v>46133</v>
       </c>
       <c r="E588" s="4" t="n">
-        <v>6000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" s="2" t="inlineStr">
         <is>
-          <t>Cooperation on innovative advanced materials with Japan (CSA)</t>
+          <t>Mapping and service finder for Technology Infrastructures (CSA)</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-01-MAT-PROD-24</t>
+          <t>HORIZON-CL4-2026-01-MAT-PROD-46</t>
         </is>
       </c>
       <c r="C589" s="3" t="n">
@@ -14457,18 +14306,18 @@
         <v>46133</v>
       </c>
       <c r="E589" s="4" t="n">
-        <v>800000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>Enhancing industry-academia knowledge exchange in Social Sciences and Humanities (SSH) (CSA)</t>
+          <t>Improving availability of secondary raw materials through recycling (IA)</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-01-MAT-PROD-41</t>
+          <t>HORIZON-CL4-2026-01-MAT-PROD-14</t>
         </is>
       </c>
       <c r="C590" s="3" t="n">
@@ -14478,18 +14327,18 @@
         <v>46133</v>
       </c>
       <c r="E590" s="4" t="n">
-        <v>1000000</v>
+        <v>7500000</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" s="2" t="inlineStr">
         <is>
-          <t>Technologies for innovative extraction of critical raw materials (RIA)</t>
+          <t>Advanced manufacturing for key products (IA) (Made in Europe partnership)</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-01-MAT-PROD-12</t>
+          <t>HORIZON-CL4-2026-01-MAT-PROD-01</t>
         </is>
       </c>
       <c r="C591" s="3" t="n">
@@ -14499,18 +14348,18 @@
         <v>46133</v>
       </c>
       <c r="E591" s="4" t="n">
-        <v>5000000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
         <is>
-          <t>Accelerating the discovery and development of chemicals and innovative advanced materials through digitalisation and artificial intelligence (IA) (Innovative Advanced Materials for the EU partnership)</t>
+          <t>Cooperation on innovative advanced materials with Japan (CSA)</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-01-MAT-PROD-23</t>
+          <t>HORIZON-CL4-2026-01-MAT-PROD-24</t>
         </is>
       </c>
       <c r="C592" s="3" t="n">
@@ -14520,18 +14369,18 @@
         <v>46133</v>
       </c>
       <c r="E592" s="4" t="n">
-        <v>13000000</v>
+        <v>800000</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" s="2" t="inlineStr">
         <is>
-          <t>Innovative technologies and tools for exploration and data modelling of raw materials (RIA)</t>
+          <t>Enhancing industry-academia knowledge exchange in Social Sciences and Humanities (SSH) (CSA)</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-01-MAT-PROD-11</t>
+          <t>HORIZON-CL4-2026-01-MAT-PROD-41</t>
         </is>
       </c>
       <c r="C593" s="3" t="n">
@@ -14541,18 +14390,18 @@
         <v>46133</v>
       </c>
       <c r="E593" s="4" t="n">
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
         <is>
-          <t>Monitoring of secondary raw materials (CSA)</t>
+          <t>Technologies for innovative extraction of critical raw materials (RIA)</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-01-MAT-PROD-13</t>
+          <t>HORIZON-CL4-2026-01-MAT-PROD-12</t>
         </is>
       </c>
       <c r="C594" s="3" t="n">
@@ -14562,18 +14411,18 @@
         <v>46133</v>
       </c>
       <c r="E594" s="4" t="n">
-        <v>4000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" s="2" t="inlineStr">
         <is>
-          <t>Circular innovative advanced materials: facilitating the transition from design to markets (RIA) (Innovative Advanced Materials for the EU and Made in Europe partnerships)</t>
+          <t>Accelerating the discovery and development of chemicals and innovative advanced materials through digitalisation and artificial intelligence (IA) (Innovative Advanced Materials for the EU partnership)</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-01-MAT-PROD-05</t>
+          <t>HORIZON-CL4-2026-01-MAT-PROD-23</t>
         </is>
       </c>
       <c r="C595" s="3" t="n">
@@ -14583,18 +14432,18 @@
         <v>46133</v>
       </c>
       <c r="E595" s="4" t="n">
-        <v>5000000</v>
+        <v>13000000</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>Pilot access schemes to Technology Infrastructures for European startups, scaleups and innovative SMEs (CSA)</t>
+          <t>Innovative technologies and tools for exploration and data modelling of raw materials (RIA)</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-01-MAT-PROD-45</t>
+          <t>HORIZON-CL4-2026-01-MAT-PROD-11</t>
         </is>
       </c>
       <c r="C596" s="3" t="n">
@@ -14604,18 +14453,18 @@
         <v>46133</v>
       </c>
       <c r="E596" s="4" t="n">
-        <v>1500000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" s="2" t="inlineStr">
         <is>
-          <t>Thematic Networks of Excellence for AI in Science (RAISE pilot) (RIA)</t>
+          <t>Monitoring of secondary raw materials (CSA)</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>HORIZON-RAISE-2026-01-01</t>
+          <t>HORIZON-CL4-2026-01-MAT-PROD-13</t>
         </is>
       </c>
       <c r="C597" s="3" t="n">
@@ -14625,18 +14474,18 @@
         <v>46133</v>
       </c>
       <c r="E597" s="4" t="n">
-        <v>15000000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>Thematic Networks of Excellence for AI in Science – Agriculture and Environmental Pollution (RAISE pilot)</t>
+          <t>Circular innovative advanced materials: facilitating the transition from design to markets (RIA) (Innovative Advanced Materials for the EU and Made in Europe partnerships)</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>HORIZON-RAISE-2026-01-02</t>
+          <t>HORIZON-CL4-2026-01-MAT-PROD-05</t>
         </is>
       </c>
       <c r="C598" s="3" t="n">
@@ -14646,46 +14495,46 @@
         <v>46133</v>
       </c>
       <c r="E598" s="4" t="n">
-        <v>12800000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" s="2" t="inlineStr">
         <is>
-          <t>Financial support to startups Open Call</t>
+          <t>Pilot access schemes to Technology Infrastructures for European startups, scaleups and innovative SMEs (CSA)</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>HORIZON-EIT-2025-KIC-IBA-UM</t>
+          <t>HORIZON-CL4-2026-01-MAT-PROD-45</t>
         </is>
       </c>
       <c r="C599" s="3" t="n">
-        <v>46014</v>
+        <v>46028</v>
       </c>
       <c r="D599" s="3" t="n">
-        <v>46160.70833333334</v>
+        <v>46133</v>
       </c>
       <c r="E599" s="4" t="n">
-        <v>14000000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>R&amp;I in Support of the Clean Industrial Deal: Decarbonisation of energy intensive industries (IA) (Processes4Planet and Clean Steel partnerships)</t>
+          <t>Thematic Networks of Excellence for AI in Science (RAISE pilot) (RIA)</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>HORIZON-CID-2026-01-01</t>
+          <t>HORIZON-RAISE-2026-01-01</t>
         </is>
       </c>
       <c r="C600" s="3" t="n">
-        <v>46009</v>
+        <v>46028</v>
       </c>
       <c r="D600" s="3" t="n">
-        <v>46280</v>
+        <v>46133</v>
       </c>
       <c r="E600" s="4" t="n">
         <v>15000000</v>
@@ -14694,208 +14543,208 @@
     <row r="601">
       <c r="A601" s="2" t="inlineStr">
         <is>
-          <t>Development of direct recycling processes (BATT4EU Partnership)</t>
+          <t>Thematic Networks of Excellence for AI in Science – Agriculture and Environmental Pollution (RAISE pilot)</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2026-03-D2-02</t>
+          <t>HORIZON-RAISE-2026-01-02</t>
         </is>
       </c>
       <c r="C601" s="3" t="n">
-        <v>46009</v>
+        <v>46028</v>
       </c>
       <c r="D601" s="3" t="n">
-        <v>46112</v>
+        <v>46133</v>
       </c>
       <c r="E601" s="4" t="n">
-        <v>4700000</v>
+        <v>12800000</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>R&amp;I in Support of the Clean Industrial Deal: Clean Technologies for Climate Action</t>
+          <t>Financial support to startups Open Call</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>HORIZON-CID-2026-01-02</t>
+          <t>HORIZON-EIT-2025-KIC-IBA-UM</t>
         </is>
       </c>
       <c r="C602" s="3" t="n">
-        <v>46009</v>
+        <v>46014</v>
       </c>
       <c r="D602" s="3" t="n">
-        <v>46280</v>
+        <v>46160.70833333334</v>
       </c>
       <c r="E602" s="4" t="n">
-        <v>15000000</v>
+        <v>14000000</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" s="2" t="inlineStr">
         <is>
-          <t>Industrial scale up and circularity pathway for IPV technologies (EUPI-PV Partnership)</t>
+          <t>R&amp;I in Support of the Clean Industrial Deal: Decarbonisation of energy intensive industries (IA) (Processes4Planet and Clean Steel partnerships)</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2026-03-D3-13</t>
+          <t>HORIZON-CID-2026-01-01</t>
         </is>
       </c>
       <c r="C603" s="3" t="n">
         <v>46009</v>
       </c>
       <c r="D603" s="3" t="n">
-        <v>46112</v>
+        <v>46280</v>
       </c>
       <c r="E603" s="4" t="n">
-        <v>10500000</v>
+        <v>15000000</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>AI-driven forecasting algorithms for Grid and Consumer friendly Energy Sharing – Societal Readiness pilot</t>
+          <t>R&amp;I in Support of the Clean Industrial Deal: Clean Technologies for Climate Action</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2026-03-D3-22</t>
+          <t>HORIZON-CID-2026-01-02</t>
         </is>
       </c>
       <c r="C604" s="3" t="n">
         <v>46009</v>
       </c>
       <c r="D604" s="3" t="n">
-        <v>46112</v>
+        <v>46280</v>
       </c>
       <c r="E604" s="4" t="n">
-        <v>6000000</v>
+        <v>15000000</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" s="2" t="inlineStr">
         <is>
-          <t>Hybrid AI-Control Framework for a next-generation grid-scale energy storage and system integration</t>
+          <t>Closing knowledge gaps on Earth system science in support of global and regional assessments and climate policy</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2026-03-D3-20</t>
+          <t>HORIZON-CL5-2026-08-Two-Stage-D1-06</t>
         </is>
       </c>
       <c r="C605" s="3" t="n">
         <v>46009</v>
       </c>
       <c r="D605" s="3" t="n">
-        <v>46112</v>
+        <v>46303</v>
       </c>
       <c r="E605" s="4" t="n">
-        <v>7000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>Long-lifetime and optimised use of materials in recyclable Ag and In-free Si PV modules (EUPI-PV Partnership)</t>
+          <t>Improving climate and weather models for Africa</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2026-03-D3-12</t>
+          <t>HORIZON-CL5-2026-07-D1-05</t>
         </is>
       </c>
       <c r="C606" s="3" t="n">
         <v>46009</v>
       </c>
       <c r="D606" s="3" t="n">
-        <v>46112</v>
+        <v>46127</v>
       </c>
       <c r="E606" s="4" t="n">
-        <v>5000000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" s="2" t="inlineStr">
         <is>
-          <t>Targeting key value chain components for increasing the competitiveness of renewable energy technologies in Europe</t>
+          <t>Disruptive Technologies and Innovative Concepts for Energy Saving Onboard of long-distance ships (ZEWT Partnership)</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2026-03-D3-01</t>
+          <t>HORIZON-CL5-2026-06-Two-Stage-D5-10</t>
         </is>
       </c>
       <c r="C607" s="3" t="n">
         <v>46009</v>
       </c>
       <c r="D607" s="3" t="n">
-        <v>46112</v>
+        <v>46303</v>
       </c>
       <c r="E607" s="4" t="n">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" s="2" t="inlineStr">
         <is>
-          <t>Pre-commercial appraisal for CO2 aquifer storage</t>
+          <t>Non-exhaust emissions in road and railway transport</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2026-03-D3-29</t>
+          <t>HORIZON-CL5-2026-06-Two-Stage-D5-19</t>
         </is>
       </c>
       <c r="C608" s="3" t="n">
         <v>46009</v>
       </c>
       <c r="D608" s="3" t="n">
-        <v>46112</v>
+        <v>46303</v>
       </c>
       <c r="E608" s="4" t="n">
-        <v>5000000</v>
+        <v>3500000</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" s="2" t="inlineStr">
         <is>
-          <t>Grid-forming capabilities for more resilient and RES-based electricity grids</t>
+          <t>Advancing European climate risk assessments</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2026-03-D3-18</t>
+          <t>HORIZON-CL5-2026-07-D1-02</t>
         </is>
       </c>
       <c r="C609" s="3" t="n">
         <v>46009</v>
       </c>
       <c r="D609" s="3" t="n">
-        <v>46112</v>
+        <v>46127</v>
       </c>
       <c r="E609" s="4" t="n">
-        <v>10000000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" s="2" t="inlineStr">
         <is>
-          <t>Closing knowledge gaps on Earth system science in support of global and regional assessments and climate policy</t>
+          <t>Next generation climate monitoring and related capabilities</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2026-08-Two-Stage-D1-06</t>
+          <t>HORIZON-CL5-2026-07-D1-01</t>
         </is>
       </c>
       <c r="C610" s="3" t="n">
         <v>46009</v>
       </c>
       <c r="D610" s="3" t="n">
-        <v>46303</v>
+        <v>46127</v>
       </c>
       <c r="E610" s="4" t="n">
         <v>5000000</v>
@@ -14904,12 +14753,12 @@
     <row r="611">
       <c r="A611" s="2" t="inlineStr">
         <is>
-          <t>Improving climate and weather models for Africa</t>
+          <t>Economics of climate change and cost of inaction</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2026-07-D1-05</t>
+          <t>HORIZON-CL5-2026-07-D1-03</t>
         </is>
       </c>
       <c r="C611" s="3" t="n">
@@ -14919,25 +14768,25 @@
         <v>46127</v>
       </c>
       <c r="E611" s="4" t="n">
-        <v>7000000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" s="2" t="inlineStr">
         <is>
-          <t>Next generation of renewable energy technologies</t>
+          <t>Fighting disinformation and effectively communicating on climate change</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2026-04-Two-Stage-D3-02</t>
+          <t>HORIZON-CL5-2026-07-D1-04</t>
         </is>
       </c>
       <c r="C612" s="3" t="n">
         <v>46009</v>
       </c>
       <c r="D612" s="3" t="n">
-        <v>46315</v>
+        <v>46127</v>
       </c>
       <c r="E612" s="4" t="n">
         <v>4000000</v>
@@ -14946,1334 +14795,1040 @@
     <row r="613">
       <c r="A613" s="2" t="inlineStr">
         <is>
-          <t>Disruptive Technologies and Innovative Concepts for Energy Saving Onboard of long-distance ships (ZEWT Partnership)</t>
+          <t>Safety of renewable low and zero-carbon waterborne fuels in port areas: risk assessment, regulatory framework, and guidelines for safe bunkering, handling and storage (ZEWT partnership)</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2026-06-Two-Stage-D5-10</t>
+          <t>HORIZON-CL5-2026-05-D5-13</t>
         </is>
       </c>
       <c r="C613" s="3" t="n">
         <v>46009</v>
       </c>
       <c r="D613" s="3" t="n">
-        <v>46303</v>
+        <v>46126</v>
       </c>
       <c r="E613" s="4" t="n">
-        <v>5000000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" s="2" t="inlineStr">
         <is>
-          <t>Non-exhaust emissions in road and railway transport</t>
+          <t>Shipyards of the future (ZEWT Partnership)</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2026-06-Two-Stage-D5-19</t>
+          <t>HORIZON-CL5-2026-05-D5-12</t>
         </is>
       </c>
       <c r="C614" s="3" t="n">
         <v>46009</v>
       </c>
       <c r="D614" s="3" t="n">
-        <v>46303</v>
+        <v>46126</v>
       </c>
       <c r="E614" s="4" t="n">
-        <v>3500000</v>
+        <v>10500000</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" s="2" t="inlineStr">
         <is>
-          <t>Affordable and sustainable primary equipment for Future-Ready multi-terminal HVDC Systems</t>
+          <t>AI-assisted digital aircraft design, manufacturing and MRO, towards a competitive aviation</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2026-03-D3-19</t>
+          <t>HORIZON-CL5-2026-05-D5-07</t>
         </is>
       </c>
       <c r="C615" s="3" t="n">
         <v>46009</v>
       </c>
       <c r="D615" s="3" t="n">
-        <v>46112</v>
+        <v>46126</v>
       </c>
       <c r="E615" s="4" t="n">
-        <v>4000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" s="2" t="inlineStr">
         <is>
-          <t>Novel solutions for off-grid storage of renewable energy for critical infrastructures</t>
+          <t>Energy-efficient software-defined EVs (2ZERO Partnership)</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2026-03-D3-21</t>
+          <t>HORIZON-CL5-2026-05-D5-02</t>
         </is>
       </c>
       <c r="C616" s="3" t="n">
         <v>46009</v>
       </c>
       <c r="D616" s="3" t="n">
-        <v>46112</v>
+        <v>46126</v>
       </c>
       <c r="E616" s="4" t="n">
-        <v>4000000</v>
+        <v>16000000</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" s="2" t="inlineStr">
         <is>
-          <t>Advancing European climate risk assessments</t>
+          <t>Large-scale demonstration of Heavy-Duty Battery Electric Vehicles (HD BEV) towards long-haul logistics operations (2ZERO Partnership)</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2026-07-D1-02</t>
+          <t>HORIZON-CL5-2026-05-D5-01</t>
         </is>
       </c>
       <c r="C617" s="3" t="n">
         <v>46009</v>
       </c>
       <c r="D617" s="3" t="n">
-        <v>46127</v>
+        <v>46126</v>
       </c>
       <c r="E617" s="4" t="n">
-        <v>4000000</v>
+        <v>34000000</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" s="2" t="inlineStr">
         <is>
-          <t>Next generation climate monitoring and related capabilities</t>
+          <t>Ports of the future (ZEWT Partnership)</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2026-07-D1-01</t>
+          <t>HORIZON-CL5-2026-05-D5-11</t>
         </is>
       </c>
       <c r="C618" s="3" t="n">
         <v>46009</v>
       </c>
       <c r="D618" s="3" t="n">
-        <v>46127</v>
+        <v>46126</v>
       </c>
       <c r="E618" s="4" t="n">
-        <v>5000000</v>
+        <v>10500000</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" s="2" t="inlineStr">
         <is>
-          <t>Economics of climate change and cost of inaction</t>
+          <t>MSCA Staff Exchanges 2026</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2026-07-D1-03</t>
+          <t>HORIZON-MSCA-2026-SE-01-01</t>
         </is>
       </c>
       <c r="C619" s="3" t="n">
-        <v>46009</v>
+        <v>46007</v>
       </c>
       <c r="D619" s="3" t="n">
-        <v>46127</v>
-      </c>
-      <c r="E619" s="4" t="n">
-        <v>4000000</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" s="2" t="inlineStr">
         <is>
-          <t>Fighting disinformation and effectively communicating on climate change</t>
+          <t>MSCA COFUND 2026</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2026-07-D1-04</t>
+          <t>HORIZON-MSCA-2026-COFUND-01-01</t>
         </is>
       </c>
       <c r="C620" s="3" t="n">
-        <v>46009</v>
+        <v>46007</v>
       </c>
       <c r="D620" s="3" t="n">
-        <v>46127</v>
-      </c>
-      <c r="E620" s="4" t="n">
-        <v>4000000</v>
+        <v>46120</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" s="2" t="inlineStr">
         <is>
-          <t>Energy-efficient software-defined EVs (2ZERO Partnership)</t>
+          <t>ERDERA Joint Transnational Call 2026: "Resolving unsolved cases in rare genetic and non-genetic diseases”</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2026-05-D5-02</t>
+          <t>HORIZON-HLTH-2023-DISEASE-07-01</t>
         </is>
       </c>
       <c r="C621" s="3" t="n">
-        <v>46009</v>
+        <v>46002</v>
       </c>
       <c r="D621" s="3" t="n">
-        <v>46126</v>
+        <v>46211.58333333334</v>
       </c>
       <c r="E621" s="4" t="n">
-        <v>16000000</v>
+        <v>31186922</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" s="2" t="inlineStr">
         <is>
-          <t>Large-scale demonstration of Heavy-Duty Battery Electric Vehicles (HD BEV) towards long-haul logistics operations (2ZERO Partnership)</t>
+          <t>A European Benchmarking Framework for hybrid quantum-classical computing</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2026-05-D5-01</t>
+          <t>HORIZON-EUROHPC-JU-2024-BENCHMARK-05-03</t>
         </is>
       </c>
       <c r="C622" s="3" t="n">
-        <v>46009</v>
+        <v>46002</v>
       </c>
       <c r="D622" s="3" t="n">
         <v>46126</v>
       </c>
       <c r="E622" s="4" t="n">
-        <v>34000000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" s="2" t="inlineStr">
         <is>
-          <t>AI-assisted digital aircraft design, manufacturing and MRO, towards a competitive aviation</t>
+          <t>A European HPC-centric Benchmark Framework</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2026-05-D5-07</t>
+          <t>HORIZON-EUROHPC-JU-2024-BENCHMARK-05</t>
         </is>
       </c>
       <c r="C623" s="3" t="n">
-        <v>46009</v>
+        <v>46002</v>
       </c>
       <c r="D623" s="3" t="n">
         <v>46126</v>
       </c>
       <c r="E623" s="4" t="n">
-        <v>5000000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" s="2" t="inlineStr">
         <is>
-          <t>Safety of renewable low and zero-carbon waterborne fuels in port areas: risk assessment, regulatory framework, and guidelines for safe bunkering, handling and storage (ZEWT partnership)</t>
+          <t xml:space="preserve">2nd ARISE Open Call </t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2026-05-D5-13</t>
+          <t>HORIZON-CL4-2023-DIGITAL-EMERGING-01-02</t>
         </is>
       </c>
       <c r="C624" s="3" t="n">
-        <v>46009</v>
+        <v>45994</v>
       </c>
       <c r="D624" s="3" t="n">
-        <v>46126</v>
+        <v>46057.70833333334</v>
       </c>
       <c r="E624" s="4" t="n">
-        <v>2000000</v>
+        <v>2600000</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" s="2" t="inlineStr">
         <is>
-          <t>Ports of the future (ZEWT Partnership)</t>
+          <t>Accelerating Food Sustainability - through Household Dietary Shifts, Trust and Transparency, and Innovations in Circular Food Processing Systems</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2026-05-D5-11</t>
+          <t>HORIZON-CL6-2023-FARM2FORK-01-9</t>
         </is>
       </c>
       <c r="C625" s="3" t="n">
-        <v>46009</v>
+        <v>45994</v>
       </c>
       <c r="D625" s="3" t="n">
-        <v>46126</v>
+        <v>46230.54166666666</v>
       </c>
       <c r="E625" s="4" t="n">
-        <v>10500000</v>
+        <v>39000000</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" s="2" t="inlineStr">
         <is>
-          <t>Shipyards of the future (ZEWT Partnership)</t>
+          <t>BlueActionBANOS Open Call for Community-Led Actions</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2026-05-D5-12</t>
+          <t>HORIZON-MISS-2024-OCEAN-02-01</t>
         </is>
       </c>
       <c r="C626" s="3" t="n">
-        <v>46009</v>
+        <v>45989</v>
       </c>
       <c r="D626" s="3" t="n">
-        <v>46126</v>
+        <v>46171.58333333334</v>
       </c>
       <c r="E626" s="4" t="n">
-        <v>10500000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" s="2" t="inlineStr">
         <is>
-          <t>MSCA Staff Exchanges 2026</t>
+          <t>BlueActionBANOS 1st Open Call for Transition Agendas</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>HORIZON-MSCA-2026-SE-01-01</t>
+          <t>HORIZON-MISS-2024-OCEAN-02-01</t>
         </is>
       </c>
       <c r="C627" s="3" t="n">
-        <v>46007</v>
+        <v>45989</v>
       </c>
       <c r="D627" s="3" t="n">
-        <v>46128</v>
+        <v>46171.58333333334</v>
+      </c>
+      <c r="E627" s="4" t="n">
+        <v>1000000</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" s="2" t="inlineStr">
         <is>
-          <t>MSCA COFUND 2026</t>
+          <t>BlueActionAA – Community Led-Pilot Action Call (BAAC-01)</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>HORIZON-MSCA-2026-COFUND-01-01</t>
+          <t>HORIZON-MISS-2024-OCEAN-02-01</t>
         </is>
       </c>
       <c r="C628" s="3" t="n">
-        <v>46007</v>
+        <v>45989</v>
       </c>
       <c r="D628" s="3" t="n">
-        <v>46120</v>
+        <v>46171.58333333334</v>
+      </c>
+      <c r="E628" s="4" t="n">
+        <v>7000000</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" s="2" t="inlineStr">
         <is>
-          <t>ERDERA Joint Transnational Call 2026: "Resolving unsolved cases in rare genetic and non-genetic diseases”</t>
+          <t xml:space="preserve">TASC-RestoreMed Open Call Type B: Transition Agenda Development (TAD) </t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2023-DISEASE-07-01</t>
+          <t>HORIZON-MISS-2024-OCEAN-02-01</t>
         </is>
       </c>
       <c r="C629" s="3" t="n">
-        <v>46002</v>
+        <v>45988</v>
       </c>
       <c r="D629" s="3" t="n">
-        <v>46211.58333333334</v>
+        <v>46169.70833333334</v>
       </c>
       <c r="E629" s="4" t="n">
-        <v>31186922</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" s="2" t="inlineStr">
         <is>
-          <t>A European Benchmarking Framework for hybrid quantum-classical computing</t>
+          <t xml:space="preserve">TASC-RestoreMed Open Call Type A: Community-Led Actions (CLA) </t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>HORIZON-EUROHPC-JU-2024-BENCHMARK-05-03</t>
+          <t>HORIZON-MISS-2024-OCEAN-02-01</t>
         </is>
       </c>
       <c r="C630" s="3" t="n">
-        <v>46002</v>
+        <v>45988</v>
       </c>
       <c r="D630" s="3" t="n">
-        <v>46126</v>
+        <v>46169.70833333334</v>
       </c>
       <c r="E630" s="4" t="n">
-        <v>500000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" s="2" t="inlineStr">
         <is>
-          <t>A European HPC-centric Benchmark Framework</t>
+          <t>Call for MRV providers to test solutions under the LILAS4SOILS Project</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>HORIZON-EUROHPC-JU-2024-BENCHMARK-05</t>
+          <t>HORIZON-MISS-2023-SOIL-01-09</t>
         </is>
       </c>
       <c r="C631" s="3" t="n">
-        <v>46002</v>
+        <v>45985</v>
       </c>
       <c r="D631" s="3" t="n">
-        <v>46126</v>
+        <v>46046.99930555555</v>
       </c>
       <c r="E631" s="4" t="n">
-        <v>500000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" s="2" t="inlineStr">
         <is>
-          <t>Understanding and overcoming barriers to the scale-up of innovations supporting EU Missions</t>
+          <t>Europe-Africa Research and Innovation call on Sustainable Energy - 2026</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-07-CROSS-02</t>
+          <t>HORIZON-CL5-2024-D3-01-09</t>
         </is>
       </c>
       <c r="C632" s="3" t="n">
-        <v>46000</v>
+        <v>45980</v>
       </c>
       <c r="D632" s="3" t="n">
-        <v>46112</v>
+        <v>46197.66666666666</v>
       </c>
       <c r="E632" s="4" t="n">
-        <v>2000000</v>
+        <v>14529000</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" s="2" t="inlineStr">
         <is>
-          <t>Strengthening skills and capacity for the deployment of EU Missions</t>
+          <t>Treatments and Adherence to Treatment protocols</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-07-CROSS-01</t>
+          <t>HORIZON-HLTH-2024-DISEASE-09-01</t>
         </is>
       </c>
       <c r="C633" s="3" t="n">
-        <v>46000</v>
+        <v>45979</v>
       </c>
       <c r="D633" s="3" t="n">
-        <v>46112</v>
+        <v>46190.54166666666</v>
       </c>
       <c r="E633" s="4" t="n">
-        <v>1000000</v>
+        <v>31000000</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" s="2" t="inlineStr">
         <is>
-          <t>Advancing lead markets and proof-of-concept for deep tech solutions contributing to EU Missions</t>
+          <t>Understanding and Preventing Overweight and Obesity: Mechanisms of their onset and progression, neglected determinants and novel strategies for critical transitional periods in life - PREVENT-OO</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-07-CROSS-03</t>
+          <t>HORIZON-HLTH-2022-DISEASE-03-01</t>
         </is>
       </c>
       <c r="C634" s="3" t="n">
-        <v>46000</v>
+        <v>45974</v>
       </c>
       <c r="D634" s="3" t="n">
-        <v>46112</v>
+        <v>46184.5</v>
       </c>
       <c r="E634" s="4" t="n">
-        <v>4000000</v>
+        <v>18940000</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2nd ARISE Open Call </t>
+          <t>Multi-country Investigator-Initiated Clinical Trials in Cardiovascular, Autoimmune and Metabolic diseases (Trials4Health) JTC2026</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2023-DIGITAL-EMERGING-01-02</t>
+          <t>HORIZON-HLTH-2022-DISEASE-03-01</t>
         </is>
       </c>
       <c r="C635" s="3" t="n">
-        <v>45994</v>
+        <v>45967</v>
       </c>
       <c r="D635" s="3" t="n">
-        <v>46057.70833333334</v>
+        <v>46190.66666666666</v>
       </c>
       <c r="E635" s="4" t="n">
-        <v>2600000</v>
+        <v>32190000</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" s="2" t="inlineStr">
         <is>
-          <t>Accelerating Food Sustainability - through Household Dietary Shifts, Trust and Transparency, and Innovations in Circular Food Processing Systems</t>
+          <t>EIC Accelerator 2026 - Short proposal</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2023-FARM2FORK-01-9</t>
+          <t>HORIZON-EIC-2026-ACCELERATOR-01</t>
         </is>
       </c>
       <c r="C636" s="3" t="n">
-        <v>45994</v>
+        <v>45967</v>
       </c>
       <c r="D636" s="3" t="n">
-        <v>46230.54166666666</v>
-      </c>
-      <c r="E636" s="4" t="n">
-        <v>39000000</v>
+        <v>46373</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" s="2" t="inlineStr">
         <is>
-          <t>ScaleDem Scaling Grounds: Piloting Programme</t>
+          <t>EIC STEP Scale Up</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>HORIZON-CL2-2024-DEMOCRACY-01-12</t>
+          <t>HORIZON-EIC-2026-STEP</t>
         </is>
       </c>
       <c r="C637" s="3" t="n">
-        <v>45992</v>
+        <v>45967</v>
       </c>
       <c r="D637" s="3" t="n">
-        <v>46112.99930555555</v>
+        <v>46351</v>
       </c>
       <c r="E637" s="4" t="n">
-        <v>500000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" s="2" t="inlineStr">
         <is>
-          <t>ScaleDem Scaling Grounds: Twinning Programme</t>
+          <t>InnoMatch project - Open call 1 EIC Awardee + Buyer (wave 2)</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>HORIZON-CL2-2024-DEMOCRACY-01-12</t>
+          <t>HORIZON-EIC-2023-INNOVPRO-01-01</t>
         </is>
       </c>
       <c r="C638" s="3" t="n">
-        <v>45992</v>
+        <v>45964</v>
       </c>
       <c r="D638" s="3" t="n">
-        <v>46112.99930555555</v>
-      </c>
-      <c r="E638" s="4" t="n">
-        <v>500000</v>
+        <v>46057.70833333334</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" s="2" t="inlineStr">
         <is>
-          <t>BlueActionBANOS Open Call for Community-Led Actions</t>
+          <t>SYNAPSE OPEN CALL</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-OCEAN-02-01</t>
+          <t>HORIZON-CL3-2022-CS-01-01</t>
         </is>
       </c>
       <c r="C639" s="3" t="n">
-        <v>45989</v>
+        <v>45957</v>
       </c>
       <c r="D639" s="3" t="n">
-        <v>46171.58333333334</v>
+        <v>46010.70833333334</v>
       </c>
       <c r="E639" s="4" t="n">
-        <v>7000000</v>
+        <v>700000</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" s="2" t="inlineStr">
         <is>
-          <t>BlueActionBANOS 1st Open Call for Transition Agendas</t>
+          <t>Open Call for the selection of EEN organisations delivering IRS Awareness and Support Services</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-OCEAN-02-01</t>
+          <t>HORIZON-EIC-2021-EEN-01-01</t>
         </is>
       </c>
       <c r="C640" s="3" t="n">
-        <v>45989</v>
+        <v>45917</v>
       </c>
       <c r="D640" s="3" t="n">
-        <v>46171.58333333334</v>
+        <v>46203.70833333334</v>
       </c>
       <c r="E640" s="4" t="n">
-        <v>1000000</v>
+        <v>4413480</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" s="2" t="inlineStr">
         <is>
-          <t>BlueActionAA – Community Led-Pilot Action Call (BAAC-01)</t>
+          <t>Digitalisation and Innovation for Resilient Marine Ecosystems Businesses, and Communities to Strengthen the EU Blue Economy’s Competitiveness</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-OCEAN-02-01</t>
+          <t>HORIZON-CL6-2022-GOVERNANCE-01-02</t>
         </is>
       </c>
       <c r="C641" s="3" t="n">
-        <v>45989</v>
+        <v>45915</v>
       </c>
       <c r="D641" s="3" t="n">
-        <v>46171.58333333334</v>
+        <v>46190.625</v>
       </c>
       <c r="E641" s="4" t="n">
-        <v>7000000</v>
+        <v>43495835</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TASC-RestoreMed Open Call Type B: Transition Agenda Development (TAD) </t>
+          <t>Water4All 2025 Joint Transnational Call “Water and health”</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-OCEAN-02-01</t>
+          <t>HORIZON-CL6-2021-CLIMATE-01-02</t>
         </is>
       </c>
       <c r="C642" s="3" t="n">
-        <v>45988</v>
+        <v>45912</v>
       </c>
       <c r="D642" s="3" t="n">
-        <v>46169.70833333334</v>
+        <v>46125.08333333334</v>
       </c>
       <c r="E642" s="4" t="n">
-        <v>1000000</v>
+        <v>35642584</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" s="2" t="inlineStr">
         <is>
-          <t>SoS2LearnDBS’s Open call for Community-Led Actions to restore Danube-Black Sea Waters (OC-CLed-SoS2LearnDBS-2025)</t>
+          <t>Restoration of ecosystem functioning, integrity and connectivity</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-OCEAN-02-01</t>
+          <t>HORIZON-CL6-2021-BIODIV-02-01</t>
         </is>
       </c>
       <c r="C643" s="3" t="n">
-        <v>45988</v>
+        <v>45909</v>
       </c>
       <c r="D643" s="3" t="n">
-        <v>46111.5</v>
+        <v>46126.5</v>
       </c>
       <c r="E643" s="4" t="n">
-        <v>7000000</v>
+        <v>40000000</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TASC-RestoreMed Open Call Type A: Community-Led Actions (CLA) </t>
+          <t>Open Call: Textile and clothing industry organisations in Athens and Rotterdam</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-OCEAN-02-01</t>
+          <t>HORIZON-CL4-2023-HUMAN-01-53</t>
         </is>
       </c>
       <c r="C644" s="3" t="n">
-        <v>45988</v>
+        <v>45904</v>
       </c>
       <c r="D644" s="3" t="n">
-        <v>46169.70833333334</v>
+        <v>45964</v>
       </c>
       <c r="E644" s="4" t="n">
-        <v>7000000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" s="2" t="inlineStr">
         <is>
-          <t>Call for MRV providers to test solutions under the LILAS4SOILS Project</t>
+          <t>Driving Urban Transitions (DUT) Call 2025</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2023-SOIL-01-09</t>
+          <t>HORIZON-CL5-2021-D2-01-16</t>
         </is>
       </c>
       <c r="C645" s="3" t="n">
-        <v>45985</v>
+        <v>45901</v>
       </c>
       <c r="D645" s="3" t="n">
-        <v>46046.99930555555</v>
+        <v>46135.54166666666</v>
       </c>
       <c r="E645" s="4" t="n">
-        <v>60000</v>
+        <v>80000000</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" s="2" t="inlineStr">
         <is>
-          <t>Europe-Africa Research and Innovation call on Sustainable Energy - 2026</t>
+          <t>dAIEDGE 3rd Open Call - Collaborative Projects</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2024-D3-01-09</t>
+          <t>HORIZON-CL4-2022-HUMAN-02-02</t>
         </is>
       </c>
       <c r="C646" s="3" t="n">
-        <v>45980</v>
+        <v>45883</v>
       </c>
       <c r="D646" s="3" t="n">
-        <v>46197.66666666666</v>
+        <v>45947.70869212963</v>
       </c>
       <c r="E646" s="4" t="n">
-        <v>14529000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" s="2" t="inlineStr">
         <is>
-          <t>Treatments and Adherence to Treatment protocols</t>
+          <t>Urban Mobility Explained (UMX) Open Call (Multi-cut-off)</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2024-DISEASE-09-01</t>
+          <t>HORIZON-EIT-2023-25-KIC-EITURBANMOBILITY</t>
         </is>
       </c>
       <c r="C647" s="3" t="n">
-        <v>45979</v>
+        <v>45840</v>
       </c>
       <c r="D647" s="3" t="n">
-        <v>46190.54166666666</v>
+        <v>46294.70833333334</v>
       </c>
       <c r="E647" s="4" t="n">
-        <v>31000000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" s="2" t="inlineStr">
         <is>
-          <t>Understanding and Preventing Overweight and Obesity: Mechanisms of their onset and progression, neglected determinants and novel strategies for critical transitional periods in life - PREVENT-OO</t>
+          <t>Bridges</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2022-DISEASE-03-01</t>
+          <t>HORIZON-EIT-2023-25-Cross-KIC-Strategic-Outreach</t>
         </is>
       </c>
       <c r="C648" s="3" t="n">
-        <v>45974</v>
+        <v>45834</v>
       </c>
       <c r="D648" s="3" t="n">
-        <v>46184.5</v>
+        <v>45912.99930555555</v>
       </c>
       <c r="E648" s="4" t="n">
-        <v>18940000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" s="2" t="inlineStr">
         <is>
-          <t>Multi-country Investigator-Initiated Clinical Trials in Cardiovascular, Autoimmune and Metabolic diseases (Trials4Health) JTC2026</t>
+          <t>Strategic Innovation Open call</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2022-DISEASE-03-01</t>
+          <t>HORIZON-EIT-2023-25-KIC-EITURBANMOBILITY</t>
         </is>
       </c>
       <c r="C649" s="3" t="n">
-        <v>45967</v>
+        <v>45827</v>
       </c>
       <c r="D649" s="3" t="n">
-        <v>46190.66666666666</v>
+        <v>46191.70833333334</v>
       </c>
       <c r="E649" s="4" t="n">
-        <v>32190000</v>
+        <v>60000000</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" s="2" t="inlineStr">
         <is>
-          <t>EIC Accelerator 2026 - Short proposal</t>
+          <t>InnoNext - Next Generation Innovation Talents' Initiative</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>HORIZON-EIC-2026-ACCELERATOR-01</t>
+          <t>HORIZON-EIC-2023-TALENTS-01-01</t>
         </is>
       </c>
       <c r="C650" s="3" t="n">
-        <v>45967</v>
+        <v>45733</v>
       </c>
       <c r="D650" s="3" t="n">
-        <v>46373</v>
+        <v>46234.99930555555</v>
+      </c>
+      <c r="E650" s="4" t="n">
+        <v>15900</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" s="2" t="inlineStr">
         <is>
-          <t>EIC STEP Scale Up</t>
+          <t>BOOST Call for Proposals</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>HORIZON-EIC-2026-STEP</t>
+          <t>HORIZON-EIC-2024-BOOSTER</t>
         </is>
       </c>
       <c r="C651" s="3" t="n">
-        <v>45967</v>
+        <v>45722</v>
       </c>
       <c r="D651" s="3" t="n">
-        <v>46351</v>
+        <v>46181.70833333334</v>
       </c>
       <c r="E651" s="4" t="n">
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" s="2" t="inlineStr">
         <is>
-          <t>InnoMatch project - Open call 1 EIC Awardee + Buyer (wave 2)</t>
+          <t>Low power Edge AI Chips</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>HORIZON-EIC-2023-INNOVPRO-01-01</t>
+          <t>HORIZON-JU-CHIPS-2025-IA-LEAI-two-stage</t>
         </is>
       </c>
       <c r="C652" s="3" t="n">
-        <v>45964</v>
+        <v>45720</v>
       </c>
       <c r="D652" s="3" t="n">
-        <v>46057.70833333334</v>
+        <v>45917</v>
+      </c>
+      <c r="E652" s="4" t="n">
+        <v>1000000</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" s="2" t="inlineStr">
         <is>
-          <t>SYNAPSE OPEN CALL</t>
+          <t>EIT RawMaterials – ERMA Booster Call</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>HORIZON-CL3-2022-CS-01-01</t>
+          <t>HORIZON-EIT-2023-25-KIC-EITRAWMATERIALS</t>
         </is>
       </c>
       <c r="C653" s="3" t="n">
-        <v>45957</v>
+        <v>45684</v>
       </c>
       <c r="D653" s="3" t="n">
-        <v>46010.70833333334</v>
+        <v>45908.99930555555</v>
       </c>
       <c r="E653" s="4" t="n">
-        <v>700000</v>
+        <v>24000000</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" s="2" t="inlineStr">
         <is>
-          <t>Open Call for the selection of EEN organisations delivering IRS Awareness and Support Services</t>
+          <t>Call for marine biodiversity (monitoring) data</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>HORIZON-EIC-2021-EEN-01-01</t>
+          <t>HORIZON-MISS-2022-OCEAN-01-07</t>
         </is>
       </c>
       <c r="C654" s="3" t="n">
-        <v>45917</v>
+        <v>45644</v>
       </c>
       <c r="D654" s="3" t="n">
-        <v>46203.70833333334</v>
-      </c>
-      <c r="E654" s="4" t="n">
-        <v>4413480</v>
+        <v>45716.99930555555</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" s="2" t="inlineStr">
         <is>
-          <t>Digitalisation and Innovation for Resilient Marine Ecosystems Businesses, and Communities to Strengthen the EU Blue Economy’s Competitiveness</t>
+          <t>Open Call: Textile and clothing industry facilitators in Athens and Rotterdam</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2022-GOVERNANCE-01-02</t>
+          <t>HORIZON-CL4-2023-HUMAN-01-53</t>
         </is>
       </c>
       <c r="C655" s="3" t="n">
-        <v>45915</v>
+        <v>45631</v>
       </c>
       <c r="D655" s="3" t="n">
-        <v>46190.625</v>
+        <v>45707</v>
       </c>
       <c r="E655" s="4" t="n">
-        <v>43495835</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" s="2" t="inlineStr">
         <is>
-          <t>Water4All 2025 Joint Transnational Call “Water and health”</t>
+          <t>EIT RawMaterials KAVA CALL 13 - UPSCALING</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2021-CLIMATE-01-02</t>
+          <t>HORIZON-EIT-2023-25-KIC-EITRAWMATERIALS</t>
         </is>
       </c>
       <c r="C656" s="3" t="n">
-        <v>45912</v>
+        <v>45572</v>
       </c>
       <c r="D656" s="3" t="n">
-        <v>46125.08333333334</v>
+        <v>45989.54166666666</v>
       </c>
       <c r="E656" s="4" t="n">
-        <v>35642584</v>
+        <v>18000000</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" s="2" t="inlineStr">
         <is>
-          <t>Restoration of ecosystem functioning, integrity and connectivity</t>
+          <t>UP-RISE Open call for fermented food processors</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2021-BIODIV-02-01</t>
+          <t>HORIZON-CL6-2023-FARM2FORK-01-20</t>
         </is>
       </c>
       <c r="C657" s="3" t="n">
-        <v>45909</v>
+        <v>45572</v>
       </c>
       <c r="D657" s="3" t="n">
-        <v>46126.5</v>
+        <v>45632.99930555555</v>
       </c>
       <c r="E657" s="4" t="n">
-        <v>40000000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" s="2" t="inlineStr">
         <is>
-          <t>Open Call: Textile and clothing industry organisations in Athens and Rotterdam</t>
+          <t>STAGE Financial Grant Programme Call 4</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2023-HUMAN-01-53</t>
+          <t>HORIZON-CL4-2021-RESILIENCE-01-29</t>
         </is>
       </c>
       <c r="C658" s="3" t="n">
-        <v>45904</v>
+        <v>45488</v>
       </c>
       <c r="D658" s="3" t="n">
-        <v>45964</v>
+        <v>45657.99930555555</v>
       </c>
       <c r="E658" s="4" t="n">
-        <v>100000</v>
+        <v>2350000</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" s="2" t="inlineStr">
         <is>
-          <t>Driving Urban Transitions (DUT) Call 2025</t>
+          <t>EIT Food Impact Funding Framework</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2021-D2-01-16</t>
+          <t>HORIZON-EIT-2023-25-KIC-EITFOOD</t>
         </is>
       </c>
       <c r="C659" s="3" t="n">
-        <v>45901</v>
+        <v>45464</v>
       </c>
       <c r="D659" s="3" t="n">
-        <v>46135.54166666666</v>
+        <v>45974.5</v>
       </c>
       <c r="E659" s="4" t="n">
-        <v>80000000</v>
+        <v>30000000</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" s="2" t="inlineStr">
         <is>
-          <t>dAIEDGE 3rd Open Call - Collaborative Projects</t>
+          <t>EIT RawMaterials Booster Call 2024-2025 for Startups and SMEs</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2022-HUMAN-02-02</t>
+          <t>HORIZON-EIT-2023-25-KIC-EITRAWMATERIALS</t>
         </is>
       </c>
       <c r="C660" s="3" t="n">
-        <v>45883</v>
+        <v>45376</v>
       </c>
       <c r="D660" s="3" t="n">
-        <v>45947.70869212963</v>
+        <v>45782.99930555555</v>
       </c>
       <c r="E660" s="4" t="n">
-        <v>600000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" s="2" t="inlineStr">
         <is>
-          <t>Urban Mobility Explained (UMX) Open Call (Multi-cut-off)</t>
+          <t>INDUSAC OPEN CALL FOR STUDENTS AND RESEARCHERS</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>HORIZON-EIT-2023-25-KIC-EITURBANMOBILITY</t>
+          <t>HORIZON-CL4-2021-HUMAN-01-20</t>
         </is>
       </c>
       <c r="C661" s="3" t="n">
-        <v>45840</v>
+        <v>45278</v>
       </c>
       <c r="D661" s="3" t="n">
-        <v>46294.70833333334</v>
+        <v>45762.99930555555</v>
       </c>
       <c r="E661" s="4" t="n">
-        <v>4000000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" s="2" t="inlineStr">
         <is>
-          <t>Bridges</t>
+          <t>Permanently Open Call for Targeted Innovation Projects</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>HORIZON-EIT-2023-25-Cross-KIC-Strategic-Outreach</t>
+          <t>HORIZON-EIT-2023-25-KIC-EITURBANMOBILITY</t>
         </is>
       </c>
       <c r="C662" s="3" t="n">
-        <v>45834</v>
+        <v>45274</v>
       </c>
       <c r="D662" s="3" t="n">
-        <v>45912.99930555555</v>
+        <v>46022.70833333334</v>
       </c>
       <c r="E662" s="4" t="n">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="663">
-      <c r="A663" s="2" t="inlineStr">
-        <is>
-          <t>Strategic Innovation Open call</t>
-        </is>
-      </c>
-      <c r="B663" t="inlineStr">
-        <is>
-          <t>HORIZON-EIT-2023-25-KIC-EITURBANMOBILITY</t>
-        </is>
-      </c>
-      <c r="C663" s="3" t="n">
-        <v>45827</v>
-      </c>
-      <c r="D663" s="3" t="n">
-        <v>46191.70833333334</v>
-      </c>
-      <c r="E663" s="4" t="n">
-        <v>60000000</v>
-      </c>
-    </row>
-    <row r="664">
-      <c r="A664" s="2" t="inlineStr">
-        <is>
-          <t>InnoNext - Next Generation Innovation Talents' Initiative</t>
-        </is>
-      </c>
-      <c r="B664" t="inlineStr">
-        <is>
-          <t>HORIZON-EIC-2023-TALENTS-01-01</t>
-        </is>
-      </c>
-      <c r="C664" s="3" t="n">
-        <v>45733</v>
-      </c>
-      <c r="D664" s="3" t="n">
-        <v>46234.99930555555</v>
-      </c>
-      <c r="E664" s="4" t="n">
-        <v>15900</v>
-      </c>
-    </row>
-    <row r="665">
-      <c r="A665" s="2" t="inlineStr">
-        <is>
-          <t>BOOST Call for Proposals</t>
-        </is>
-      </c>
-      <c r="B665" t="inlineStr">
-        <is>
-          <t>HORIZON-EIC-2024-BOOSTER</t>
-        </is>
-      </c>
-      <c r="C665" s="3" t="n">
-        <v>45722</v>
-      </c>
-      <c r="D665" s="3" t="n">
-        <v>46181.70833333334</v>
-      </c>
-      <c r="E665" s="4" t="n">
-        <v>5000000</v>
-      </c>
-    </row>
-    <row r="666">
-      <c r="A666" s="2" t="inlineStr">
-        <is>
-          <t>Low power Edge AI Chips</t>
-        </is>
-      </c>
-      <c r="B666" t="inlineStr">
-        <is>
-          <t>HORIZON-JU-CHIPS-2025-IA-LEAI-two-stage</t>
-        </is>
-      </c>
-      <c r="C666" s="3" t="n">
-        <v>45720</v>
-      </c>
-      <c r="D666" s="3" t="n">
-        <v>45917</v>
-      </c>
-      <c r="E666" s="4" t="n">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="667">
-      <c r="A667" s="2" t="inlineStr">
-        <is>
-          <t>EIT RawMaterials – ERMA Booster Call</t>
-        </is>
-      </c>
-      <c r="B667" t="inlineStr">
-        <is>
-          <t>HORIZON-EIT-2023-25-KIC-EITRAWMATERIALS</t>
-        </is>
-      </c>
-      <c r="C667" s="3" t="n">
-        <v>45684</v>
-      </c>
-      <c r="D667" s="3" t="n">
-        <v>45908.99930555555</v>
-      </c>
-      <c r="E667" s="4" t="n">
-        <v>24000000</v>
-      </c>
-    </row>
-    <row r="668">
-      <c r="A668" s="2" t="inlineStr">
-        <is>
-          <t>Call for marine biodiversity (monitoring) data</t>
-        </is>
-      </c>
-      <c r="B668" t="inlineStr">
-        <is>
-          <t>HORIZON-MISS-2022-OCEAN-01-07</t>
-        </is>
-      </c>
-      <c r="C668" s="3" t="n">
-        <v>45644</v>
-      </c>
-      <c r="D668" s="3" t="n">
-        <v>45716.99930555555</v>
-      </c>
-    </row>
-    <row r="669">
-      <c r="A669" s="2" t="inlineStr">
-        <is>
-          <t>Open Call: Textile and clothing industry facilitators in Athens and Rotterdam</t>
-        </is>
-      </c>
-      <c r="B669" t="inlineStr">
-        <is>
-          <t>HORIZON-CL4-2023-HUMAN-01-53</t>
-        </is>
-      </c>
-      <c r="C669" s="3" t="n">
-        <v>45631</v>
-      </c>
-      <c r="D669" s="3" t="n">
-        <v>45707</v>
-      </c>
-      <c r="E669" s="4" t="n">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="670">
-      <c r="A670" s="2" t="inlineStr">
-        <is>
-          <t>EIT RawMaterials KAVA CALL 13 - UPSCALING</t>
-        </is>
-      </c>
-      <c r="B670" t="inlineStr">
-        <is>
-          <t>HORIZON-EIT-2023-25-KIC-EITRAWMATERIALS</t>
-        </is>
-      </c>
-      <c r="C670" s="3" t="n">
-        <v>45572</v>
-      </c>
-      <c r="D670" s="3" t="n">
-        <v>45989.54166666666</v>
-      </c>
-      <c r="E670" s="4" t="n">
-        <v>18000000</v>
-      </c>
-    </row>
-    <row r="671">
-      <c r="A671" s="2" t="inlineStr">
-        <is>
-          <t>UP-RISE Open call for fermented food processors</t>
-        </is>
-      </c>
-      <c r="B671" t="inlineStr">
-        <is>
-          <t>HORIZON-CL6-2023-FARM2FORK-01-20</t>
-        </is>
-      </c>
-      <c r="C671" s="3" t="n">
-        <v>45572</v>
-      </c>
-      <c r="D671" s="3" t="n">
-        <v>45632.99930555555</v>
-      </c>
-      <c r="E671" s="4" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="672">
-      <c r="A672" s="2" t="inlineStr">
-        <is>
-          <t>STAGE Financial Grant Programme Call 4</t>
-        </is>
-      </c>
-      <c r="B672" t="inlineStr">
-        <is>
-          <t>HORIZON-CL4-2021-RESILIENCE-01-29</t>
-        </is>
-      </c>
-      <c r="C672" s="3" t="n">
-        <v>45488</v>
-      </c>
-      <c r="D672" s="3" t="n">
-        <v>45657.99930555555</v>
-      </c>
-      <c r="E672" s="4" t="n">
-        <v>2350000</v>
-      </c>
-    </row>
-    <row r="673">
-      <c r="A673" s="2" t="inlineStr">
-        <is>
-          <t>EIT Food Impact Funding Framework</t>
-        </is>
-      </c>
-      <c r="B673" t="inlineStr">
-        <is>
-          <t>HORIZON-EIT-2023-25-KIC-EITFOOD</t>
-        </is>
-      </c>
-      <c r="C673" s="3" t="n">
-        <v>45464</v>
-      </c>
-      <c r="D673" s="3" t="n">
-        <v>45974.5</v>
-      </c>
-      <c r="E673" s="4" t="n">
-        <v>30000000</v>
-      </c>
-    </row>
-    <row r="674">
-      <c r="A674" s="2" t="inlineStr">
-        <is>
-          <t>EIT RawMaterials Booster Call 2024-2025 for Startups and SMEs</t>
-        </is>
-      </c>
-      <c r="B674" t="inlineStr">
-        <is>
-          <t>HORIZON-EIT-2023-25-KIC-EITRAWMATERIALS</t>
-        </is>
-      </c>
-      <c r="C674" s="3" t="n">
-        <v>45376</v>
-      </c>
-      <c r="D674" s="3" t="n">
-        <v>45782.99930555555</v>
-      </c>
-      <c r="E674" s="4" t="n">
-        <v>10000000</v>
-      </c>
-    </row>
-    <row r="675">
-      <c r="A675" s="2" t="inlineStr">
-        <is>
-          <t>INDUSAC OPEN CALL FOR STUDENTS AND RESEARCHERS</t>
-        </is>
-      </c>
-      <c r="B675" t="inlineStr">
-        <is>
-          <t>HORIZON-CL4-2021-HUMAN-01-20</t>
-        </is>
-      </c>
-      <c r="C675" s="3" t="n">
-        <v>45278</v>
-      </c>
-      <c r="D675" s="3" t="n">
-        <v>45762.99930555555</v>
-      </c>
-      <c r="E675" s="4" t="n">
-        <v>900000</v>
-      </c>
-    </row>
-    <row r="676">
-      <c r="A676" s="2" t="inlineStr">
-        <is>
-          <t>Permanently Open Call for Targeted Innovation Projects</t>
-        </is>
-      </c>
-      <c r="B676" t="inlineStr">
-        <is>
-          <t>HORIZON-EIT-2023-25-KIC-EITURBANMOBILITY</t>
-        </is>
-      </c>
-      <c r="C676" s="3" t="n">
-        <v>45274</v>
-      </c>
-      <c r="D676" s="3" t="n">
-        <v>46022.70833333334</v>
-      </c>
-      <c r="E676" s="4" t="n">
         <v>4200000</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E676"/>
+  <autoFilter ref="A1:E662"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId2"/>
@@ -16936,20 +16491,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A660" r:id="rId659"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A661" r:id="rId660"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A662" r:id="rId661"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A663" r:id="rId662"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A664" r:id="rId663"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A665" r:id="rId664"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A666" r:id="rId665"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A667" r:id="rId666"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A668" r:id="rId667"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A669" r:id="rId668"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A670" r:id="rId669"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A671" r:id="rId670"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A672" r:id="rId671"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A673" r:id="rId672"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A674" r:id="rId673"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A675" r:id="rId674"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A676" r:id="rId675"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/horizon-reports/horizon_rapor_latest.xlsx
+++ b/horizon-reports/horizon_rapor_latest.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Yeni Açılan Çağrılar'!$A$1:$E$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tüm Misyon Çağrıları'!$A$1:$E$67</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tüm Açık Çağrılar'!$A$1:$E$662</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tüm Açık Çağrılar'!$A$1:$E$661</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -481,22 +481,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ODEON Open Call</t>
+          <t>CIRCULOOS Open Call #3.2: Value-Chain Extension &amp; Enhance</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2023-D3-01-15</t>
+          <t>HORIZON-CL4-2022-TWIN-TRANSITION-01-06</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
         <v>46120</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>46212.70833333334</v>
+        <v>46183.75</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>1200000</v>
+        <v>600000</v>
       </c>
     </row>
   </sheetData>
@@ -2014,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E662"/>
+  <dimension ref="A1:E661"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -9755,12 +9755,12 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>MSCA Postdoctoral Fellowships 2026</t>
+          <t>ERA Fellowships</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>HORIZON-MSCA-2026-PF-01-01</t>
+          <t>HORIZON-WIDERA-2026-05-WIDENING-01</t>
         </is>
       </c>
       <c r="C370" s="3" t="n">
@@ -9769,16 +9769,19 @@
       <c r="D370" s="3" t="n">
         <v>46274</v>
       </c>
+      <c r="E370" s="4" t="n">
+        <v>100000</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>ERA Fellowships</t>
+          <t>MSCA Postdoctoral Fellowships 2026</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>HORIZON-WIDERA-2026-05-WIDENING-01</t>
+          <t>HORIZON-MSCA-2026-PF-01-01</t>
         </is>
       </c>
       <c r="C371" s="3" t="n">
@@ -9787,9 +9790,6 @@
       <c r="D371" s="3" t="n">
         <v>46274</v>
       </c>
-      <c r="E371" s="4" t="n">
-        <v>100000</v>
-      </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
@@ -9815,91 +9815,91 @@
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>JARVIS Open Call #2 - Co-development Track</t>
+          <t>CIRCULOOS Open Call #3.2: Value-Chain Extension &amp; Enhance</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2023-DIGITAL-EMERGING-01-02</t>
+          <t>HORIZON-CL4-2022-TWIN-TRANSITION-01-06</t>
         </is>
       </c>
       <c r="C373" s="3" t="n">
-        <v>46113</v>
+        <v>46120</v>
       </c>
       <c r="D373" s="3" t="n">
-        <v>46174.875</v>
+        <v>46183.75</v>
       </c>
       <c r="E373" s="4" t="n">
-        <v>800000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>JARVIS Open Call #2 - External Pilots Track</t>
+          <t>Open Call 1 addressed to research and technology stakeholders</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2023-DIGITAL-EMERGING-01-02</t>
+          <t>HORIZON-CL6-2024-FARM2FORK-01-11</t>
         </is>
       </c>
       <c r="C374" s="3" t="n">
-        <v>46113</v>
+        <v>46119</v>
       </c>
       <c r="D374" s="3" t="n">
-        <v>46213.875</v>
+        <v>46203.75</v>
       </c>
       <c r="E374" s="4" t="n">
-        <v>650000</v>
+        <v>400000</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>NGI Fediversity open call (2026-06F)</t>
+          <t>JARVIS Open Call #2 - Co-development Track</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2023-HUMAN-01-12</t>
+          <t>HORIZON-CL4-2023-DIGITAL-EMERGING-01-02</t>
         </is>
       </c>
       <c r="C375" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="D375" s="3" t="n">
-        <v>46174.5</v>
+        <v>46174.875</v>
       </c>
       <c r="E375" s="4" t="n">
-        <v>365000</v>
+        <v>800000</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>NGI Zero Commons Fund (2026-06Z)</t>
+          <t>JARVIS Open Call #2 - External Pilots Track</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2023-HUMAN-01-11</t>
+          <t>HORIZON-CL4-2023-DIGITAL-EMERGING-01-02</t>
         </is>
       </c>
       <c r="C376" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="D376" s="3" t="n">
-        <v>46174.5</v>
+        <v>46213.875</v>
       </c>
       <c r="E376" s="4" t="n">
-        <v>6100000</v>
+        <v>650000</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>NGI TALER open call (2026-06T)</t>
+          <t>NGI Fediversity open call (2026-06F)</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -9914,54 +9914,60 @@
         <v>46174.5</v>
       </c>
       <c r="E377" s="4" t="n">
-        <v>269173</v>
+        <v>365000</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>Demonstration of low power Ice Protection System technology</t>
+          <t>NGI Zero Commons Fund (2026-06Z)</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-FTA-01</t>
+          <t>HORIZON-CL4-2023-HUMAN-01-11</t>
         </is>
       </c>
       <c r="C378" s="3" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="D378" s="3" t="n">
-        <v>46161</v>
+        <v>46174.5</v>
+      </c>
+      <c r="E378" s="4" t="n">
+        <v>6100000</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>Demonstration of an Ultra-Efficient Rear Fuselage and Empennage and Its Integrated Industrial System enabling EIS2035 for the SMR Aircraft</t>
+          <t>NGI TALER open call (2026-06T)</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-SMR-02</t>
+          <t>HORIZON-CL4-2023-HUMAN-01-12</t>
         </is>
       </c>
       <c r="C379" s="3" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="D379" s="3" t="n">
-        <v>46161</v>
+        <v>46174.5</v>
+      </c>
+      <c r="E379" s="4" t="n">
+        <v>269173</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>Demonstration and Validation of icing Certification Methodologies compatible with EIS2035 for the SMR and REG Aircraft</t>
+          <t>Demonstration of an Ultra-Efficient Rear Fuselage and Empennage and Its Integrated Industrial System enabling EIS2035 for the SMR Aircraft</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-TRA-01</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-SMR-02</t>
         </is>
       </c>
       <c r="C380" s="3" t="n">
@@ -9974,12 +9980,12 @@
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>Demonstration of an Optimized System Platform for Ultra-efficient SMR Aircraft</t>
+          <t>Demonstration of a hydrogen distribution system for a direct hydrogen combustion propulsion aircraft</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-SMR-01</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-HPA-04</t>
         </is>
       </c>
       <c r="C381" s="3" t="n">
@@ -9992,12 +9998,12 @@
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>Demonstration of an integrated hydrogen fuel system for a fully electric hydrogen fuel cell powered aircraft</t>
+          <t>Innovative light weight and reliable liquid hydrogen tank</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-HPA-02</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-FTA-07</t>
         </is>
       </c>
       <c r="C382" s="3" t="n">
@@ -10010,12 +10016,12 @@
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>Demonstration of a hydrogen distribution system for a direct hydrogen combustion propulsion aircraft</t>
+          <t>Ground Demonstration of Hybrid-Electric Propulsion Architectures for the Ultra-efficient SMR aircraft</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-HPA-04</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-SMR-03</t>
         </is>
       </c>
       <c r="C383" s="3" t="n">
@@ -10028,12 +10034,12 @@
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>Demonstration of Advanced Low NOx H2C Propulsion System for a direct hydrogen combustion aircraft</t>
+          <t>Demonstration of an Optimized System Platform for Ultra-efficient SMR Aircraft</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-HPA-03</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-SMR-01</t>
         </is>
       </c>
       <c r="C384" s="3" t="n">
@@ -10046,12 +10052,12 @@
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>Advanced noise-reducing technologies for propulsion systems of next generation Ultra-efficient SMR aircraft</t>
+          <t>Cryo-cooled power electronics for a fully electric hydrogen fuel cell powered aircraft</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-FTA-03</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-FTA-05</t>
         </is>
       </c>
       <c r="C385" s="3" t="n">
@@ -10064,12 +10070,12 @@
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>Demonstration of cabin acoustic optimization technology</t>
+          <t>Demonstration of advanced airframe for ultra-efficient regional aircraft</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-FTA-02</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-REG-01</t>
         </is>
       </c>
       <c r="C386" s="3" t="n">
@@ -10082,12 +10088,12 @@
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>Hydrogen powered aircraft concepts and key technologies integration and impact assessment</t>
+          <t>Operational stakeholders’ group to support the deployment of Clean Aviation aircraft concepts and technologies</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-ACI-01</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-CSA-01</t>
         </is>
       </c>
       <c r="C387" s="3" t="n">
@@ -10100,12 +10106,12 @@
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>Superconducting motor windings for a fully electric hydrogen fuel cell powered aircraft</t>
+          <t>Demonstration of advanced FC propulsion techno-bricks for a fully electric hydrogen fuel cell powered aircraft</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-FTA-06</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-HPA-01</t>
         </is>
       </c>
       <c r="C388" s="3" t="n">
@@ -10118,12 +10124,12 @@
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>Demonstration of advanced FC propulsion techno-bricks for a fully electric hydrogen fuel cell powered aircraft</t>
+          <t xml:space="preserve">Key Technologies for Loads Control Lidar for Ultra-efficient SMR aircraft </t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-HPA-01</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-FTA-04</t>
         </is>
       </c>
       <c r="C389" s="3" t="n">
@@ -10136,12 +10142,12 @@
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Key Technologies for Loads Control Lidar for Ultra-efficient SMR aircraft </t>
+          <t>Advanced noise-reducing technologies for propulsion systems of next generation Ultra-efficient SMR aircraft</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-FTA-04</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-FTA-03</t>
         </is>
       </c>
       <c r="C390" s="3" t="n">
@@ -10154,12 +10160,12 @@
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>Demonstration of advanced airframe for ultra-efficient regional aircraft</t>
+          <t>Superconducting motor windings for a fully electric hydrogen fuel cell powered aircraft</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-REG-01</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-FTA-06</t>
         </is>
       </c>
       <c r="C391" s="3" t="n">
@@ -10172,12 +10178,12 @@
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>Operational stakeholders’ group to support the deployment of Clean Aviation aircraft concepts and technologies</t>
+          <t>Hydrogen powered aircraft concepts and key technologies integration and impact assessment</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-CSA-01</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-ACI-01</t>
         </is>
       </c>
       <c r="C392" s="3" t="n">
@@ -10190,12 +10196,12 @@
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>Cryo-cooled power electronics for a fully electric hydrogen fuel cell powered aircraft</t>
+          <t>Demonstration of cabin acoustic optimization technology</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-FTA-05</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-FTA-02</t>
         </is>
       </c>
       <c r="C393" s="3" t="n">
@@ -10208,12 +10214,12 @@
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>Innovative light weight and reliable liquid hydrogen tank</t>
+          <t>Demonstration of low power Ice Protection System technology</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-FTA-07</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-FTA-01</t>
         </is>
       </c>
       <c r="C394" s="3" t="n">
@@ -10226,12 +10232,12 @@
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>Ground Demonstration of Hybrid-Electric Propulsion Architectures for the Ultra-efficient SMR aircraft</t>
+          <t>Demonstration and Validation of icing Certification Methodologies compatible with EIS2035 for the SMR and REG Aircraft</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-SMR-03</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-TRA-01</t>
         </is>
       </c>
       <c r="C395" s="3" t="n">
@@ -10244,138 +10250,132 @@
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>Student Entrepreneur Grant Scheme (SEGS)</t>
+          <t>Demonstration of an integrated hydrogen fuel system for a fully electric hydrogen fuel cell powered aircraft</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>HORIZON-EIT-2025-KIC-IBA-UM</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-HPA-02</t>
         </is>
       </c>
       <c r="C396" s="3" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="D396" s="3" t="n">
-        <v>46307.70833333334</v>
-      </c>
-      <c r="E396" s="4" t="n">
-        <v>90000</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>Scaleups Promotion Open Call</t>
+          <t>Demonstration of Advanced Low NOx H2C Propulsion System for a direct hydrogen combustion aircraft</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>HORIZON-EIT-2025-KIC-IBA-UM</t>
+          <t>HORIZON-JU-CLEAN-AVIATION-2026-04-HPA-03</t>
         </is>
       </c>
       <c r="C397" s="3" t="n">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="D397" s="3" t="n">
-        <v>46169.70833333334</v>
-      </c>
-      <c r="E397" s="4" t="n">
-        <v>415000</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>Ignite NEB Open call for hosts</t>
+          <t>Student Entrepreneur Grant Scheme (SEGS)</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>HORIZON-EIT-2025-KIC-IBA-INBC</t>
+          <t>HORIZON-EIT-2025-KIC-IBA-UM</t>
         </is>
       </c>
       <c r="C398" s="3" t="n">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="D398" s="3" t="n">
-        <v>46149.70833333334</v>
+        <v>46307.70833333334</v>
       </c>
       <c r="E398" s="4" t="n">
-        <v>208000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>PERIFORMANCE OPEN CALL FOR BOTTOM-UP STAKEHOLDER ENGAGEMENT INITIATIVES IN CANCER RESEARCH &amp; CARE</t>
+          <t>Scaleups Promotion Open Call</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-CROSS-02-01</t>
+          <t>HORIZON-EIT-2025-KIC-IBA-UM</t>
         </is>
       </c>
       <c r="C399" s="3" t="n">
-        <v>46103</v>
+        <v>46108</v>
       </c>
       <c r="D399" s="3" t="n">
-        <v>46173.70833333334</v>
+        <v>46169.70833333334</v>
       </c>
       <c r="E399" s="4" t="n">
-        <v>150000</v>
+        <v>415000</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>Risk management, mitigation and contingency for ESFRI/ERIC and other world-class research infrastructures</t>
+          <t>Ignite NEB Open call for hosts</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>HORIZON-INFRA-2026-DEV-01-07</t>
+          <t>HORIZON-EIT-2025-KIC-IBA-INBC</t>
         </is>
       </c>
       <c r="C400" s="3" t="n">
-        <v>46091</v>
+        <v>46104</v>
       </c>
       <c r="D400" s="3" t="n">
-        <v>46189</v>
+        <v>46149.70833333334</v>
       </c>
       <c r="E400" s="4" t="n">
-        <v>1000000</v>
+        <v>208000</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>R&amp;D for the next generation of scientific instrumentation, tools, methods, digitalisation and solutions for research infrastructure upgrades</t>
+          <t>PERIFORMANCE OPEN CALL FOR BOTTOM-UP STAKEHOLDER ENGAGEMENT INITIATIVES IN CANCER RESEARCH &amp; CARE</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>HORIZON-INFRA-2026-TECH-01-01</t>
+          <t>HORIZON-MISS-2024-CROSS-02-01</t>
         </is>
       </c>
       <c r="C401" s="3" t="n">
-        <v>46091</v>
+        <v>46103</v>
       </c>
       <c r="D401" s="3" t="n">
-        <v>46189</v>
+        <v>46173.70833333334</v>
       </c>
       <c r="E401" s="4" t="n">
-        <v>5000000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>Uptake of FAIR data management practices and of EOSC by research communities and research infrastructures (EOSC Partnership)</t>
+          <t>Risk management, mitigation and contingency for ESFRI/ERIC and other world-class research infrastructures</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>HORIZON-INFRA-2026-01-EOSC-01</t>
+          <t>HORIZON-INFRA-2026-DEV-01-07</t>
         </is>
       </c>
       <c r="C402" s="3" t="n">
@@ -10385,18 +10385,18 @@
         <v>46189</v>
       </c>
       <c r="E402" s="4" t="n">
-        <v>40000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>Implementing digital services to empower neuroscience research for health and brain inspired technology via EBRAINS</t>
+          <t>R&amp;D for the next generation of scientific instrumentation, tools, methods, digitalisation and solutions for research infrastructure upgrades</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>HORIZON-INFRA-2026-SERV-01-01</t>
+          <t>HORIZON-INFRA-2026-TECH-01-01</t>
         </is>
       </c>
       <c r="C403" s="3" t="n">
@@ -10406,18 +10406,18 @@
         <v>46189</v>
       </c>
       <c r="E403" s="4" t="n">
-        <v>32000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>Strengthening the human capital managing research infrastructures, including in international context</t>
+          <t>Uptake of FAIR data management practices and of EOSC by research communities and research infrastructures (EOSC Partnership)</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>HORIZON-INFRA-2026-DEV-01-04</t>
+          <t>HORIZON-INFRA-2026-01-EOSC-01</t>
         </is>
       </c>
       <c r="C404" s="3" t="n">
@@ -10427,18 +10427,18 @@
         <v>46189</v>
       </c>
       <c r="E404" s="4" t="n">
-        <v>2000000</v>
+        <v>40000000</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>Consolidation of the research infrastructure landscape – pilots for strategic coordination, synergies and simplified access pathways, by large thematic clusters of pan-European research infrastructures</t>
+          <t>Implementing digital services to empower neuroscience research for health and brain inspired technology via EBRAINS</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>HORIZON-INFRA-2026-DEV-01-02</t>
+          <t>HORIZON-INFRA-2026-SERV-01-01</t>
         </is>
       </c>
       <c r="C405" s="3" t="n">
@@ -10448,18 +10448,18 @@
         <v>46189</v>
       </c>
       <c r="E405" s="4" t="n">
-        <v>4000000</v>
+        <v>32000000</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>Digital twins and/or their major components for environment, climate and security</t>
+          <t>Strengthening the human capital managing research infrastructures, including in international context</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>HORIZON-INFRA-2026-TECH-01-02</t>
+          <t>HORIZON-INFRA-2026-DEV-01-04</t>
         </is>
       </c>
       <c r="C406" s="3" t="n">
@@ -10469,18 +10469,18 @@
         <v>46189</v>
       </c>
       <c r="E406" s="4" t="n">
-        <v>5000000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>Strengthening the international dimension of ESFRI and/or ERIC research infrastructures</t>
+          <t>Consolidation of the research infrastructure landscape – pilots for strategic coordination, synergies and simplified access pathways, by large thematic clusters of pan-European research infrastructures</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>HORIZON-INFRA-2026-DEV-01-06</t>
+          <t>HORIZON-INFRA-2026-DEV-01-02</t>
         </is>
       </c>
       <c r="C407" s="3" t="n">
@@ -10490,18 +10490,18 @@
         <v>46189</v>
       </c>
       <c r="E407" s="4" t="n">
-        <v>1000000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>Research infrastructures as accelerators of the integration of Ukraine in the European Research Area</t>
+          <t>Digital twins and/or their major components for environment, climate and security</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>HORIZON-INFRA-2026-DEV-01-05</t>
+          <t>HORIZON-INFRA-2026-TECH-01-02</t>
         </is>
       </c>
       <c r="C408" s="3" t="n">
@@ -10511,18 +10511,18 @@
         <v>46189</v>
       </c>
       <c r="E408" s="4" t="n">
-        <v>8000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>Trusted frameworks for secure and efficient data sharing in EOSC (EOSC Partnership)</t>
+          <t>Strengthening the international dimension of ESFRI and/or ERIC research infrastructures</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>HORIZON-INFRA-2026-01-EOSC-02</t>
+          <t>HORIZON-INFRA-2026-DEV-01-06</t>
         </is>
       </c>
       <c r="C409" s="3" t="n">
@@ -10532,18 +10532,18 @@
         <v>46189</v>
       </c>
       <c r="E409" s="4" t="n">
-        <v>3000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>Consolidation of the research infrastructure landscape – individual support for evolution, long-term sustainability and emerging needs of pan-European research infrastructures</t>
+          <t>Research infrastructures as accelerators of the integration of Ukraine in the European Research Area</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>HORIZON-INFRA-2026-DEV-01-03</t>
+          <t>HORIZON-INFRA-2026-DEV-01-05</t>
         </is>
       </c>
       <c r="C410" s="3" t="n">
@@ -10553,18 +10553,18 @@
         <v>46189</v>
       </c>
       <c r="E410" s="4" t="n">
-        <v>3000000</v>
+        <v>8000000</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>Research infrastructure concept development including major upgrades or extensions of existing infrastructures</t>
+          <t>Trusted frameworks for secure and efficient data sharing in EOSC (EOSC Partnership)</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>HORIZON-INFRA-2026-DEV-01-01</t>
+          <t>HORIZON-INFRA-2026-01-EOSC-02</t>
         </is>
       </c>
       <c r="C411" s="3" t="n">
@@ -10574,60 +10574,60 @@
         <v>46189</v>
       </c>
       <c r="E411" s="4" t="n">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>Preparing demonstration missions for Earth Observation and Satellite telecommunication for Space solutions (Space Partnership)</t>
+          <t>Consolidation of the research infrastructure landscape – individual support for evolution, long-term sustainability and emerging needs of pan-European research infrastructures</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-SPACE-03-32</t>
+          <t>HORIZON-INFRA-2026-DEV-01-03</t>
         </is>
       </c>
       <c r="C412" s="3" t="n">
         <v>46091</v>
       </c>
       <c r="D412" s="3" t="n">
-        <v>46268</v>
+        <v>46189</v>
       </c>
       <c r="E412" s="4" t="n">
-        <v>5000000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>Digital enablers and building-blocks for Earth Observation and Satellite telecommunication for Space solutions (Space Partnership)</t>
+          <t>Research infrastructure concept development including major upgrades or extensions of existing infrastructures</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-SPACE-03-31</t>
+          <t>HORIZON-INFRA-2026-DEV-01-01</t>
         </is>
       </c>
       <c r="C413" s="3" t="n">
         <v>46091</v>
       </c>
       <c r="D413" s="3" t="n">
-        <v>46268</v>
+        <v>46189</v>
       </c>
       <c r="E413" s="4" t="n">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>Space critical EEE components for EU non-dependence – GaN MMICs mm-Wave Foundations (Phase A): Development and Industrialization of Semi-insulating SiC Substrate Capabilities</t>
+          <t>Preparing demonstration missions for Earth Observation and Satellite telecommunication for Space solutions (Space Partnership)</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-SPACE-03-82</t>
+          <t>HORIZON-CL4-2026-SPACE-03-32</t>
         </is>
       </c>
       <c r="C414" s="3" t="n">
@@ -10637,18 +10637,18 @@
         <v>46268</v>
       </c>
       <c r="E414" s="4" t="n">
-        <v>6000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>Reinforcing EU autonomous access to space through EU-based spaceports</t>
+          <t>Digital enablers and building-blocks for Earth Observation and Satellite telecommunication for Space solutions (Space Partnership)</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-SPACE-03-11</t>
+          <t>HORIZON-CL4-2026-SPACE-03-31</t>
         </is>
       </c>
       <c r="C415" s="3" t="n">
@@ -10658,18 +10658,18 @@
         <v>46268</v>
       </c>
       <c r="E415" s="4" t="n">
-        <v>10000000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>Space critical EEE components for EU non-dependence – Radiation Hard FPGA on 7nm</t>
+          <t>Space critical EEE components for EU non-dependence – GaN MMICs mm-Wave Foundations (Phase A): Development and Industrialization of Semi-insulating SiC Substrate Capabilities</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-SPACE-03-81</t>
+          <t>HORIZON-CL4-2026-SPACE-03-82</t>
         </is>
       </c>
       <c r="C416" s="3" t="n">
@@ -10679,18 +10679,18 @@
         <v>46268</v>
       </c>
       <c r="E416" s="4" t="n">
-        <v>12000000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>Space critical Equipment for EU non-dependence – Space Refuelling Interface</t>
+          <t>Reinforcing EU autonomous access to space through EU-based spaceports</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-SPACE-03-86</t>
+          <t>HORIZON-CL4-2026-SPACE-03-11</t>
         </is>
       </c>
       <c r="C417" s="3" t="n">
@@ -10700,18 +10700,18 @@
         <v>46268</v>
       </c>
       <c r="E417" s="4" t="n">
-        <v>2000000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>Critical Facilities Serving Space EEE components for EU non-dependence – High and Very High Energy Irradiation Test Facility Market Deployment</t>
+          <t>Space critical EEE components for EU non-dependence – Radiation Hard FPGA on 7nm</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-SPACE-03-85</t>
+          <t>HORIZON-CL4-2026-SPACE-03-81</t>
         </is>
       </c>
       <c r="C418" s="3" t="n">
@@ -10721,18 +10721,18 @@
         <v>46268</v>
       </c>
       <c r="E418" s="4" t="n">
-        <v>3000000</v>
+        <v>12000000</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
         <is>
-          <t>Scientific analysis and exploitation of space data</t>
+          <t>Space critical Equipment for EU non-dependence – Space Refuelling Interface</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-SPACE-03-61</t>
+          <t>HORIZON-CL4-2026-SPACE-03-86</t>
         </is>
       </c>
       <c r="C419" s="3" t="n">
@@ -10742,123 +10742,123 @@
         <v>46268</v>
       </c>
       <c r="E419" s="4" t="n">
-        <v>1500000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">INTEGRATION OF EXISTING APPLICATIONS, MODELS AND DATA INTO EDITO </t>
+          <t>Critical Facilities Serving Space EEE components for EU non-dependence – High and Very High Energy Irradiation Test Facility Market Deployment</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-OCEAN-IBA</t>
+          <t>HORIZON-CL4-2026-SPACE-03-85</t>
         </is>
       </c>
       <c r="C420" s="3" t="n">
         <v>46091</v>
       </c>
       <c r="D420" s="3" t="n">
-        <v>46148.5</v>
+        <v>46268</v>
       </c>
       <c r="E420" s="4" t="n">
-        <v>600000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>Open Call for Financial Support to Third parties as a mechanism to test, promote, validate, replicate PRIMARY business model blueprints and develop new value chains</t>
+          <t>Scientific analysis and exploitation of space data</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2024-CircBio-02-6-two-stage</t>
+          <t>HORIZON-CL4-2026-SPACE-03-61</t>
         </is>
       </c>
       <c r="C421" s="3" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="D421" s="3" t="n">
-        <v>46181.70833333334</v>
+        <v>46268</v>
       </c>
       <c r="E421" s="4" t="n">
-        <v>900000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">COP-PILOT Open Call 1 </t>
+          <t xml:space="preserve">INTEGRATION OF EXISTING APPLICATIONS, MODELS AND DATA INTO EDITO </t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2024-DATA-01-03</t>
+          <t>HORIZON-MISS-2024-OCEAN-IBA</t>
         </is>
       </c>
       <c r="C422" s="3" t="n">
-        <v>46084</v>
+        <v>46091</v>
       </c>
       <c r="D422" s="3" t="n">
-        <v>46146.91666666666</v>
+        <v>46148.5</v>
       </c>
       <c r="E422" s="4" t="n">
-        <v>1600000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
         <is>
-          <t>Approaches and tools for security in software and hardware development and assessment</t>
+          <t>Open Call for Financial Support to Third parties as a mechanism to test, promote, validate, replicate PRIMARY business model blueprints and develop new value chains</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>HORIZON-CL3-2026-02-CS-ECCC-01</t>
+          <t>HORIZON-CL6-2024-CircBio-02-6-two-stage</t>
         </is>
       </c>
       <c r="C423" s="3" t="n">
-        <v>46084</v>
+        <v>46090</v>
       </c>
       <c r="D423" s="3" t="n">
-        <v>46280</v>
+        <v>46181.70833333334</v>
       </c>
       <c r="E423" s="4" t="n">
-        <v>3000000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>Advanced cryptographic schemes and High-Assurance high-speed cryptographic implementations</t>
+          <t xml:space="preserve">COP-PILOT Open Call 1 </t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>HORIZON-CL3-2026-02-CS-ECCC-03</t>
+          <t>HORIZON-CL4-2024-DATA-01-03</t>
         </is>
       </c>
       <c r="C424" s="3" t="n">
         <v>46084</v>
       </c>
       <c r="D424" s="3" t="n">
-        <v>46280</v>
+        <v>46146.91666666666</v>
       </c>
       <c r="E424" s="4" t="n">
-        <v>2000000</v>
+        <v>1600000</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
         <is>
-          <t>Enhancing the Security, Privacy and Robustness of AI Models and Systems (SecureAI)</t>
+          <t>Approaches and tools for security in software and hardware development and assessment</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>HORIZON-CL3-2026-02-CS-ECCC-02</t>
+          <t>HORIZON-CL3-2026-02-CS-ECCC-01</t>
         </is>
       </c>
       <c r="C425" s="3" t="n">
@@ -10874,219 +10874,219 @@
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>HORIZON-EIC-2026-BAS-02-SCLATEUP</t>
+          <t>Advanced cryptographic schemes and High-Assurance high-speed cryptographic implementations</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>HORIZON-EIC-2026-BAS-02-SCALEUP</t>
+          <t>HORIZON-CL3-2026-02-CS-ECCC-03</t>
         </is>
       </c>
       <c r="C426" s="3" t="n">
         <v>46084</v>
       </c>
       <c r="D426" s="3" t="n">
-        <v>46198</v>
+        <v>46280</v>
       </c>
       <c r="E426" s="4" t="n">
-        <v>4000000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>AUTOASSESS Open Call #2 for Tech Innovators</t>
+          <t>Enhancing the Security, Privacy and Robustness of AI Models and Systems (SecureAI)</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2022-DIGITAL-EMERGING-02-07</t>
+          <t>HORIZON-CL3-2026-02-CS-ECCC-02</t>
         </is>
       </c>
       <c r="C427" s="3" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="D427" s="3" t="n">
-        <v>46147.70833333334</v>
+        <v>46280</v>
       </c>
       <c r="E427" s="4" t="n">
-        <v>1350000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>Open Horizons Open Call #3</t>
+          <t>HORIZON-EIC-2026-BAS-02-SCLATEUP</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>HORIZON-EIE-2024-CONNECT-01-02</t>
+          <t>HORIZON-EIC-2026-BAS-02-SCALEUP</t>
         </is>
       </c>
       <c r="C428" s="3" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="D428" s="3" t="n">
-        <v>46161.70833333334</v>
+        <v>46198</v>
       </c>
       <c r="E428" s="4" t="n">
-        <v>475000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>First FIDELIS Open Call for Mentors and Peer-to-Peer Support Programme</t>
+          <t>AUTOASSESS Open Call #2 for Tech Innovators</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>HORIZON-INFRA-2024-EOSC-01-03</t>
+          <t>HORIZON-CL4-2022-DIGITAL-EMERGING-02-07</t>
         </is>
       </c>
       <c r="C429" s="3" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="D429" s="3" t="n">
-        <v>46142.70833333334</v>
+        <v>46147.70833333334</v>
       </c>
       <c r="E429" s="4" t="n">
-        <v>120000</v>
+        <v>1350000</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>Call for applications: FRONTIERS Science Journalism Residency Program (Call 4)</t>
+          <t>Open Horizons Open Call #3</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>ERC-2023-SJI-1</t>
+          <t>HORIZON-EIE-2024-CONNECT-01-02</t>
         </is>
       </c>
       <c r="C430" s="3" t="n">
-        <v>46078</v>
+        <v>46083</v>
       </c>
       <c r="D430" s="3" t="n">
-        <v>46167.79166666666</v>
+        <v>46161.70833333334</v>
       </c>
       <c r="E430" s="4" t="n">
-        <v>600000</v>
+        <v>475000</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>Open Call 2 - Short Term and Long Term Funding to support ICT standardisation</t>
+          <t>First FIDELIS Open Call for Mentors and Peer-to-Peer Support Programme</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2024-HUMAN-03-04</t>
+          <t>HORIZON-INFRA-2024-EOSC-01-03</t>
         </is>
       </c>
       <c r="C431" s="3" t="n">
-        <v>46076</v>
+        <v>46080</v>
       </c>
       <c r="D431" s="3" t="n">
-        <v>46136.70833333334</v>
+        <v>46142.70833333334</v>
       </c>
       <c r="E431" s="4" t="n">
-        <v>650000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>InnoMatch project - Open call 2 for EIC Awardees</t>
+          <t>Call for applications: FRONTIERS Science Journalism Residency Program (Call 4)</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>HORIZON-EIC-2023-INNOVPRO-01-01</t>
+          <t>ERC-2023-SJI-1</t>
         </is>
       </c>
       <c r="C432" s="3" t="n">
-        <v>46069</v>
+        <v>46078</v>
       </c>
       <c r="D432" s="3" t="n">
-        <v>46129.70833333334</v>
+        <v>46167.79166666666</v>
+      </c>
+      <c r="E432" s="4" t="n">
+        <v>600000</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
         <is>
-          <t>Living labs to enhance soil health in managed forests and in natural/semi-natural lands</t>
+          <t>Open Call 2 - Short Term and Long Term Funding to support ICT standardisation</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-05-SOIL-02-two-stage</t>
+          <t>HORIZON-CL4-2024-HUMAN-03-04</t>
         </is>
       </c>
       <c r="C433" s="3" t="n">
-        <v>46065</v>
+        <v>46076</v>
       </c>
       <c r="D433" s="3" t="n">
-        <v>46280</v>
+        <v>46136.70833333334</v>
       </c>
       <c r="E433" s="4" t="n">
-        <v>12000000</v>
+        <v>650000</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>Open topic: Uncovering the causes of specific species’ rapid decline and exploring actionable solutions</t>
+          <t>InnoMatch project - Open call 2 for EIC Awardees</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-01-BIODIV-02-two-stage</t>
+          <t>HORIZON-EIC-2023-INNOVPRO-01-01</t>
         </is>
       </c>
       <c r="C434" s="3" t="n">
-        <v>46065</v>
+        <v>46069</v>
       </c>
       <c r="D434" s="3" t="n">
-        <v>46288</v>
-      </c>
-      <c r="E434" s="4" t="n">
-        <v>3000000</v>
+        <v>46129.70833333334</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
         <is>
-          <t>Open topic: Using the Circular Cities and Regions Initiative to strengthen urban manufacturing in support of the Clean Industrial Deal</t>
+          <t>Living labs to enhance soil health in managed forests and in natural/semi-natural lands</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-01-CIRCBIO-02-two-stage</t>
+          <t>HORIZON-MISS-2026-05-SOIL-02-two-stage</t>
         </is>
       </c>
       <c r="C435" s="3" t="n">
         <v>46065</v>
       </c>
       <c r="D435" s="3" t="n">
-        <v>46288</v>
+        <v>46280</v>
       </c>
       <c r="E435" s="4" t="n">
-        <v>6000000</v>
+        <v>12000000</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>Deploying circular systemic solutions through living labs in cities and regions (Circular Cities and Regions Initiative topic)</t>
+          <t>Open topic: Uncovering the causes of specific species’ rapid decline and exploring actionable solutions</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-01-CIRCBIO-01-two-stage</t>
+          <t>HORIZON-CL6-2026-01-BIODIV-02-two-stage</t>
         </is>
       </c>
       <c r="C436" s="3" t="n">
@@ -11096,18 +11096,18 @@
         <v>46288</v>
       </c>
       <c r="E436" s="4" t="n">
-        <v>5000000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
         <is>
-          <t>Unlocking the potential of citizen action for nature protection and restoration</t>
+          <t>Open topic: Using the Circular Cities and Regions Initiative to strengthen urban manufacturing in support of the Clean Industrial Deal</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-01-BIODIV-03-two-stage</t>
+          <t>HORIZON-CL6-2026-01-CIRCBIO-02-two-stage</t>
         </is>
       </c>
       <c r="C437" s="3" t="n">
@@ -11117,18 +11117,18 @@
         <v>46288</v>
       </c>
       <c r="E437" s="4" t="n">
-        <v>5000000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>Living labs for co-creating solutions for the restoration of ecosystems</t>
+          <t>Deploying circular systemic solutions through living labs in cities and regions (Circular Cities and Regions Initiative topic)</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-01-BIODIV-01-two-stage</t>
+          <t>HORIZON-CL6-2026-01-CIRCBIO-01-two-stage</t>
         </is>
       </c>
       <c r="C438" s="3" t="n">
@@ -11138,18 +11138,18 @@
         <v>46288</v>
       </c>
       <c r="E438" s="4" t="n">
-        <v>7000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
         <is>
-          <t>Decontaminate and bioremediate aquatic pollution</t>
+          <t>Unlocking the potential of citizen action for nature protection and restoration</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-01-ZEROPOLLUTION-01-two-stage</t>
+          <t>HORIZON-CL6-2026-01-BIODIV-03-two-stage</t>
         </is>
       </c>
       <c r="C439" s="3" t="n">
@@ -11159,18 +11159,18 @@
         <v>46288</v>
       </c>
       <c r="E439" s="4" t="n">
-        <v>7000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>Mainstreaming and scaling-up evidence-based Nature-Based Solutions towards a nature positive and climate-resilient economy</t>
+          <t>Living labs for co-creating solutions for the restoration of ecosystems</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-01-BIODIV-04-two-stage</t>
+          <t>HORIZON-CL6-2026-01-BIODIV-01-two-stage</t>
         </is>
       </c>
       <c r="C440" s="3" t="n">
@@ -11180,46 +11180,46 @@
         <v>46288</v>
       </c>
       <c r="E440" s="4" t="n">
-        <v>6000000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
         <is>
-          <t>Open topic: Improving the competitiveness of the agricultural sector by enhancing the efficient and sustainable use of agricultural production factors</t>
+          <t>Decontaminate and bioremediate aquatic pollution</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-FARM2FORK-01-two-stage</t>
+          <t>HORIZON-CL6-2026-01-ZEROPOLLUTION-01-two-stage</t>
         </is>
       </c>
       <c r="C441" s="3" t="n">
         <v>46065</v>
       </c>
       <c r="D441" s="3" t="n">
-        <v>46280</v>
+        <v>46288</v>
       </c>
       <c r="E441" s="4" t="n">
-        <v>4500000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>Open topic: Develop Earth Intelligence solutions using environmental observations and state-of-the-art AI for sustainable competitiveness and policy making</t>
+          <t>Mainstreaming and scaling-up evidence-based Nature-Based Solutions towards a nature positive and climate-resilient economy</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-03-GOVERNANCE-01-two-stage</t>
+          <t>HORIZON-CL6-2026-01-BIODIV-04-two-stage</t>
         </is>
       </c>
       <c r="C442" s="3" t="n">
         <v>46065</v>
       </c>
       <c r="D442" s="3" t="n">
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="E442" s="4" t="n">
         <v>6000000</v>
@@ -11228,12 +11228,12 @@
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
         <is>
-          <t>Living labs to enhance soil health in Alpine and Atlantic biogeographical regions</t>
+          <t>Open topic: Improving the competitiveness of the agricultural sector by enhancing the efficient and sustainable use of agricultural production factors</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-05-SOIL-01-two-stage</t>
+          <t>HORIZON-CL6-2026-02-FARM2FORK-01-two-stage</t>
         </is>
       </c>
       <c r="C443" s="3" t="n">
@@ -11243,25 +11243,25 @@
         <v>46280</v>
       </c>
       <c r="E443" s="4" t="n">
-        <v>12000000</v>
+        <v>4500000</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>Open topic: Boosting organic farming for a competitive, sustainable and resilient farming sector</t>
+          <t>Open topic: Develop Earth Intelligence solutions using environmental observations and state-of-the-art AI for sustainable competitiveness and policy making</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-FARM2FORK-02-two-stage</t>
+          <t>HORIZON-CL6-2026-03-GOVERNANCE-01-two-stage</t>
         </is>
       </c>
       <c r="C444" s="3" t="n">
         <v>46065</v>
       </c>
       <c r="D444" s="3" t="n">
-        <v>46280</v>
+        <v>46295</v>
       </c>
       <c r="E444" s="4" t="n">
         <v>6000000</v>
@@ -11270,40 +11270,40 @@
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
         <is>
-          <t>Innovative interventions to prevent the harmful effects of using digital technologies on the mental health of children and young adults</t>
+          <t>Living labs to enhance soil health in Alpine and Atlantic biogeographical regions</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-DISEASE-02</t>
+          <t>HORIZON-MISS-2026-05-SOIL-01-two-stage</t>
         </is>
       </c>
       <c r="C445" s="3" t="n">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="D445" s="3" t="n">
-        <v>46128</v>
+        <v>46280</v>
       </c>
       <c r="E445" s="4" t="n">
-        <v>8000000</v>
+        <v>12000000</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>Advancing research on the prevention, diagnosis, and management of post-infection long-term conditions</t>
+          <t>Open topic: Boosting organic farming for a competitive, sustainable and resilient farming sector</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-DISEASE-03</t>
+          <t>HORIZON-CL6-2026-02-FARM2FORK-02-two-stage</t>
         </is>
       </c>
       <c r="C446" s="3" t="n">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="D446" s="3" t="n">
-        <v>46128</v>
+        <v>46280</v>
       </c>
       <c r="E446" s="4" t="n">
         <v>6000000</v>
@@ -11312,12 +11312,12 @@
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
         <is>
-          <t>Identifying and addressing low-value care in health and care systems</t>
+          <t>Innovative interventions to prevent the harmful effects of using digital technologies on the mental health of children and young adults</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-CARE-03</t>
+          <t>HORIZON-HLTH-2026-01-DISEASE-02</t>
         </is>
       </c>
       <c r="C447" s="3" t="n">
@@ -11327,18 +11327,18 @@
         <v>46128</v>
       </c>
       <c r="E447" s="4" t="n">
-        <v>10000000</v>
+        <v>8000000</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
         <is>
-          <t>Regulatory science to support translational development of patient-centred health technologies</t>
+          <t>Advancing research on the prevention, diagnosis, and management of post-infection long-term conditions</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-IND-03</t>
+          <t>HORIZON-HLTH-2026-01-DISEASE-03</t>
         </is>
       </c>
       <c r="C448" s="3" t="n">
@@ -11348,18 +11348,18 @@
         <v>46128</v>
       </c>
       <c r="E448" s="4" t="n">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
         <is>
-          <t>Towards a better understanding and anticipation of the impacts of climate change on health</t>
+          <t>Identifying and addressing low-value care in health and care systems</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-ENVHLTH-01</t>
+          <t>HORIZON-HLTH-2026-01-CARE-03</t>
         </is>
       </c>
       <c r="C449" s="3" t="n">
@@ -11369,18 +11369,18 @@
         <v>46128</v>
       </c>
       <c r="E449" s="4" t="n">
-        <v>7000000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>Public procurement of innovative solutions for improving citizens' access to healthcare through integrated or personalised approaches</t>
+          <t>Regulatory science to support translational development of patient-centred health technologies</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-CARE-01</t>
+          <t>HORIZON-HLTH-2026-01-IND-03</t>
         </is>
       </c>
       <c r="C450" s="3" t="n">
@@ -11390,18 +11390,18 @@
         <v>46128</v>
       </c>
       <c r="E450" s="4" t="n">
-        <v>3000000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
         <is>
-          <t>Establishing a European network of Centres of Excellence (CoEs) for Advanced Therapies Medicinal Products (ATMPs)</t>
+          <t>Towards a better understanding and anticipation of the impacts of climate change on health</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-TOOL-07</t>
+          <t>HORIZON-HLTH-2026-01-ENVHLTH-01</t>
         </is>
       </c>
       <c r="C451" s="3" t="n">
@@ -11411,18 +11411,18 @@
         <v>46128</v>
       </c>
       <c r="E451" s="4" t="n">
-        <v>3900000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
         <is>
-          <t>Development of novel vaccines for viral pathogens with epidemic potential</t>
+          <t>Public procurement of innovative solutions for improving citizens' access to healthcare through integrated or personalised approaches</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-DISEASE-04</t>
+          <t>HORIZON-HLTH-2026-01-CARE-01</t>
         </is>
       </c>
       <c r="C452" s="3" t="n">
@@ -11432,18 +11432,18 @@
         <v>46128</v>
       </c>
       <c r="E452" s="4" t="n">
-        <v>9000000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
         <is>
-          <t>Towards climate resilient, prepared and carbon neutral populations and healthcare systems</t>
+          <t>Establishing a European network of Centres of Excellence (CoEs) for Advanced Therapies Medicinal Products (ATMPs)</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-ENVHLTH-04</t>
+          <t>HORIZON-HLTH-2026-01-TOOL-07</t>
         </is>
       </c>
       <c r="C453" s="3" t="n">
@@ -11453,18 +11453,18 @@
         <v>46128</v>
       </c>
       <c r="E453" s="4" t="n">
-        <v>7000000</v>
+        <v>3900000</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>Support for a multilateral initiative on climate change and health research</t>
+          <t>Development of novel vaccines for viral pathogens with epidemic potential</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-ENVHLTH-05</t>
+          <t>HORIZON-HLTH-2026-01-DISEASE-04</t>
         </is>
       </c>
       <c r="C454" s="3" t="n">
@@ -11474,18 +11474,18 @@
         <v>46128</v>
       </c>
       <c r="E454" s="4" t="n">
-        <v>3000000</v>
+        <v>9000000</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
         <is>
-          <t>Enhancing and enlarging the European Partnership on Personalised Medicine (EP PerMEd) (Top-up)</t>
+          <t>Towards climate resilient, prepared and carbon neutral populations and healthcare systems</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-04-CARE-04</t>
+          <t>HORIZON-HLTH-2026-01-ENVHLTH-04</t>
         </is>
       </c>
       <c r="C455" s="3" t="n">
@@ -11495,18 +11495,18 @@
         <v>46128</v>
       </c>
       <c r="E455" s="4" t="n">
-        <v>9800000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
         <is>
-          <t>Multisectoral approach to tackle chronic non-communicable diseases: implementation research maximising collaboration and coordination with sectors and in settings beyond the healthcare system (GACD)</t>
+          <t>Support for a multilateral initiative on climate change and health research</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-DISEASE-09</t>
+          <t>HORIZON-HLTH-2026-01-ENVHLTH-05</t>
         </is>
       </c>
       <c r="C456" s="3" t="n">
@@ -11522,12 +11522,12 @@
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
         <is>
-          <t>Scaling up innovation in cardiovascular health</t>
+          <t>Enhancing and enlarging the European Partnership on Personalised Medicine (EP PerMEd) (Top-up)</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-DISEASE-15</t>
+          <t>HORIZON-HLTH-2026-04-CARE-04</t>
         </is>
       </c>
       <c r="C457" s="3" t="n">
@@ -11537,18 +11537,18 @@
         <v>46128</v>
       </c>
       <c r="E457" s="4" t="n">
-        <v>1900000</v>
+        <v>9800000</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
         <is>
-          <t>Understanding of sex and/or gender-specific mechanisms of cardiovascular diseases: determinants, risk factors and pathways</t>
+          <t>Multisectoral approach to tackle chronic non-communicable diseases: implementation research maximising collaboration and coordination with sectors and in settings beyond the healthcare system (GACD)</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-DISEASE-11</t>
+          <t>HORIZON-HLTH-2026-01-DISEASE-09</t>
         </is>
       </c>
       <c r="C458" s="3" t="n">
@@ -11558,39 +11558,39 @@
         <v>46128</v>
       </c>
       <c r="E458" s="4" t="n">
-        <v>6000000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
         <is>
-          <t>European Partnership on Rare Diseases (ERDERA) (Phase 2)</t>
+          <t>Scaling up innovation in cardiovascular health</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-02-DISEASE-12</t>
+          <t>HORIZON-HLTH-2026-01-DISEASE-15</t>
         </is>
       </c>
       <c r="C459" s="3" t="n">
         <v>46063</v>
       </c>
       <c r="D459" s="3" t="n">
-        <v>46280</v>
+        <v>46128</v>
       </c>
       <c r="E459" s="4" t="n">
-        <v>91300000</v>
+        <v>1900000</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
         <is>
-          <t>Support to European Research Area (ERA) action on accelerating New Approach Methodologies (NAMs) to advance biomedical research and testing of medicinal products and medical devices</t>
+          <t>Understanding of sex and/or gender-specific mechanisms of cardiovascular diseases: determinants, risk factors and pathways</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-TOOL-06</t>
+          <t>HORIZON-HLTH-2026-01-DISEASE-11</t>
         </is>
       </c>
       <c r="C460" s="3" t="n">
@@ -11600,39 +11600,39 @@
         <v>46128</v>
       </c>
       <c r="E460" s="4" t="n">
-        <v>2900000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
         <is>
-          <t>Building public trust and outreach in the life sciences</t>
+          <t>European Partnership on Rare Diseases (ERDERA) (Phase 2)</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-STAYHLTH-03</t>
+          <t>HORIZON-HLTH-2026-02-DISEASE-12</t>
         </is>
       </c>
       <c r="C461" s="3" t="n">
         <v>46063</v>
       </c>
       <c r="D461" s="3" t="n">
-        <v>46128</v>
+        <v>46280</v>
       </c>
       <c r="E461" s="4" t="n">
-        <v>1500000</v>
+        <v>91300000</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
         <is>
-          <t>Behavioural interventions as primary prevention for Non-Communicable Diseases (NCDs) among young people</t>
+          <t>Support to European Research Area (ERA) action on accelerating New Approach Methodologies (NAMs) to advance biomedical research and testing of medicinal products and medical devices</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-STAYHLTH-02</t>
+          <t>HORIZON-HLTH-2026-01-TOOL-06</t>
         </is>
       </c>
       <c r="C462" s="3" t="n">
@@ -11642,18 +11642,18 @@
         <v>46128</v>
       </c>
       <c r="E462" s="4" t="n">
-        <v>9000000</v>
+        <v>2900000</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
         <is>
-          <t>Integrating New Approach Methodologies (NAMs) to advance biomedical research and regulatory testing</t>
+          <t>Building public trust and outreach in the life sciences</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-TOOL-03</t>
+          <t>HORIZON-HLTH-2026-01-STAYHLTH-03</t>
         </is>
       </c>
       <c r="C463" s="3" t="n">
@@ -11663,60 +11663,60 @@
         <v>46128</v>
       </c>
       <c r="E463" s="4" t="n">
-        <v>5000000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
         <is>
-          <t>Earlier and more precise palliative care</t>
+          <t>Behavioural interventions as primary prevention for Non-Communicable Diseases (NCDs) among young people</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-02-CANCER-04</t>
+          <t>HORIZON-HLTH-2026-01-STAYHLTH-02</t>
         </is>
       </c>
       <c r="C464" s="3" t="n">
         <v>46063</v>
       </c>
       <c r="D464" s="3" t="n">
-        <v>46280</v>
+        <v>46128</v>
       </c>
       <c r="E464" s="4" t="n">
-        <v>5000000</v>
+        <v>9000000</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
         <is>
-          <t>Virtual Human Twin (VHT) Models for Cancer Research</t>
+          <t>Integrating New Approach Methodologies (NAMs) to advance biomedical research and regulatory testing</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-02-CANCER-01</t>
+          <t>HORIZON-HLTH-2026-01-TOOL-03</t>
         </is>
       </c>
       <c r="C465" s="3" t="n">
         <v>46063</v>
       </c>
       <c r="D465" s="3" t="n">
-        <v>46280</v>
+        <v>46128</v>
       </c>
       <c r="E465" s="4" t="n">
-        <v>8000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
         <is>
-          <t>Improve the Quality of Life of older cancer patients</t>
+          <t>Earlier and more precise palliative care</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-02-CANCER-07</t>
+          <t>HORIZON-MISS-2026-02-CANCER-04</t>
         </is>
       </c>
       <c r="C466" s="3" t="n">
@@ -11732,12 +11732,12 @@
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
         <is>
-          <t>Pragmatic clinical trials to optimise immunotherapeutic interventions for patients with refractory cancers</t>
+          <t>Virtual Human Twin (VHT) Models for Cancer Research</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-02-CANCER-03</t>
+          <t>HORIZON-MISS-2026-02-CANCER-01</t>
         </is>
       </c>
       <c r="C467" s="3" t="n">
@@ -11747,18 +11747,18 @@
         <v>46280</v>
       </c>
       <c r="E467" s="4" t="n">
-        <v>7000000</v>
+        <v>8000000</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
         <is>
-          <t>Microbiome for early cancer prediction before the onset of disease</t>
+          <t>Improve the Quality of Life of older cancer patients</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-02-CANCER-02</t>
+          <t>HORIZON-MISS-2026-02-CANCER-07</t>
         </is>
       </c>
       <c r="C468" s="3" t="n">
@@ -11768,39 +11768,39 @@
         <v>46280</v>
       </c>
       <c r="E468" s="4" t="n">
-        <v>15000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="inlineStr">
         <is>
-          <t>Pilot actions for follow-on funding: Leveraging EU-funded collaborative research in regenerative medicine</t>
+          <t>Pragmatic clinical trials to optimise immunotherapeutic interventions for patients with refractory cancers</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2026-01-TOOL-05</t>
+          <t>HORIZON-MISS-2026-02-CANCER-03</t>
         </is>
       </c>
       <c r="C469" s="3" t="n">
         <v>46063</v>
       </c>
       <c r="D469" s="3" t="n">
-        <v>46128</v>
+        <v>46280</v>
       </c>
       <c r="E469" s="4" t="n">
-        <v>6000000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
         <is>
-          <t>Boosting mental health of young cancer survivors through the European Cancer Patient Digital Centre (ECPDC)</t>
+          <t>Microbiome for early cancer prediction before the onset of disease</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-02-CANCER-05</t>
+          <t>HORIZON-MISS-2026-02-CANCER-02</t>
         </is>
       </c>
       <c r="C470" s="3" t="n">
@@ -11810,81 +11810,81 @@
         <v>46280</v>
       </c>
       <c r="E470" s="4" t="n">
-        <v>7000000</v>
+        <v>15000000</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
         <is>
-          <t>Development of a research capacity building programme on cancer with and for Ukraine</t>
+          <t>Pilot actions for follow-on funding: Leveraging EU-funded collaborative research in regenerative medicine</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-02-CANCER-06</t>
+          <t>HORIZON-HLTH-2026-01-TOOL-05</t>
         </is>
       </c>
       <c r="C471" s="3" t="n">
         <v>46063</v>
       </c>
       <c r="D471" s="3" t="n">
-        <v>46280</v>
+        <v>46128</v>
       </c>
       <c r="E471" s="4" t="n">
-        <v>5000000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
         <is>
-          <t>Components Development and Experimental Testing for an Onboard Liquid Hydrogen Supply and Conditioning System in High-Power Fuel Cell Aviation Applications</t>
+          <t>Boosting mental health of young cancer survivors through the European Cancer Patient Digital Centre (ECPDC)</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-03-02</t>
+          <t>HORIZON-MISS-2026-02-CANCER-05</t>
         </is>
       </c>
       <c r="C472" s="3" t="n">
         <v>46063</v>
       </c>
       <c r="D472" s="3" t="n">
-        <v>46127</v>
+        <v>46280</v>
       </c>
       <c r="E472" s="4" t="n">
-        <v>8000000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
         <is>
-          <t>Improved components and tools to increase the safety of electrolysers</t>
+          <t>Development of a research capacity building programme on cancer with and for Ukraine</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-01-03</t>
+          <t>HORIZON-MISS-2026-02-CANCER-06</t>
         </is>
       </c>
       <c r="C473" s="3" t="n">
         <v>46063</v>
       </c>
       <c r="D473" s="3" t="n">
-        <v>46127</v>
+        <v>46280</v>
       </c>
       <c r="E473" s="4" t="n">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
         <is>
-          <t>Demonstration of rSOC operation for local grid-connected hydrogen production and utilisation</t>
+          <t>Components Development and Experimental Testing for an Onboard Liquid Hydrogen Supply and Conditioning System in High-Power Fuel Cell Aviation Applications</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-04-02</t>
+          <t>HORIZON-JU-CLEANH2-2026-03-02</t>
         </is>
       </c>
       <c r="C474" s="3" t="n">
@@ -11900,12 +11900,12 @@
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
         <is>
-          <t>Multi-fuel SOFC powertrain for maritime transport</t>
+          <t>Improved components and tools to increase the safety of electrolysers</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-03-04</t>
+          <t>HORIZON-JU-CLEANH2-2026-01-03</t>
         </is>
       </c>
       <c r="C475" s="3" t="n">
@@ -11915,18 +11915,18 @@
         <v>46127</v>
       </c>
       <c r="E475" s="4" t="n">
-        <v>8000000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
         <is>
-          <t>Cost-efficient and reliable designs towards gigawatt-scale electrolytic hydrogen production plants</t>
+          <t>Demonstration of rSOC operation for local grid-connected hydrogen production and utilisation</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-01-02</t>
+          <t>HORIZON-JU-CLEANH2-2026-04-02</t>
         </is>
       </c>
       <c r="C476" s="3" t="n">
@@ -11936,18 +11936,18 @@
         <v>46127</v>
       </c>
       <c r="E476" s="4" t="n">
-        <v>2500000</v>
+        <v>8000000</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="inlineStr">
         <is>
-          <t>Demonstrating in-line inspection (ILI) to monitor cracks assuring compatibility for operation with hydrogen in new and re-purposed offshore natural gas pipelines</t>
+          <t>Multi-fuel SOFC powertrain for maritime transport</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-02-02</t>
+          <t>HORIZON-JU-CLEANH2-2026-03-04</t>
         </is>
       </c>
       <c r="C477" s="3" t="n">
@@ -11957,18 +11957,18 @@
         <v>46127</v>
       </c>
       <c r="E477" s="4" t="n">
-        <v>3500000</v>
+        <v>8000000</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
         <is>
-          <t>Integration of control &amp; monitoring tools and strategies for improved Fuel Cell System durability &amp; reliability</t>
+          <t>Cost-efficient and reliable designs towards gigawatt-scale electrolytic hydrogen production plants</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-03-01</t>
+          <t>HORIZON-JU-CLEANH2-2026-01-02</t>
         </is>
       </c>
       <c r="C478" s="3" t="n">
@@ -11978,18 +11978,18 @@
         <v>46127</v>
       </c>
       <c r="E478" s="4" t="n">
-        <v>4000000</v>
+        <v>2500000</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
         <is>
-          <t>Flexible and standardised hydrogen storage system</t>
+          <t>Demonstrating in-line inspection (ILI) to monitor cracks assuring compatibility for operation with hydrogen in new and re-purposed offshore natural gas pipelines</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-03-03</t>
+          <t>HORIZON-JU-CLEANH2-2026-02-02</t>
         </is>
       </c>
       <c r="C479" s="3" t="n">
@@ -11999,18 +11999,18 @@
         <v>46127</v>
       </c>
       <c r="E479" s="4" t="n">
-        <v>5000000</v>
+        <v>3500000</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
         <is>
-          <t>Pre-Normative Research on hydrogen odorisation: enhancing safety and detection along the hydrogen value chain</t>
+          <t>Integration of control &amp; monitoring tools and strategies for improved Fuel Cell System durability &amp; reliability</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-05-02</t>
+          <t>HORIZON-JU-CLEANH2-2026-03-01</t>
         </is>
       </c>
       <c r="C480" s="3" t="n">
@@ -12020,18 +12020,18 @@
         <v>46127</v>
       </c>
       <c r="E480" s="4" t="n">
-        <v>3000000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
         <is>
-          <t>Next generation of reversible proton conducting ceramic cells and stacks for efficient energy applications at ≥1 kW scale</t>
+          <t>Flexible and standardised hydrogen storage system</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-04-01</t>
+          <t>HORIZON-JU-CLEANH2-2026-03-03</t>
         </is>
       </c>
       <c r="C481" s="3" t="n">
@@ -12041,18 +12041,18 @@
         <v>46127</v>
       </c>
       <c r="E481" s="4" t="n">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
         <is>
-          <t>Innovative business models advancing renewable electrolysis integration in industry</t>
+          <t>Pre-Normative Research on hydrogen odorisation: enhancing safety and detection along the hydrogen value chain</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-01-04</t>
+          <t>HORIZON-JU-CLEANH2-2026-05-02</t>
         </is>
       </c>
       <c r="C482" s="3" t="n">
@@ -12062,18 +12062,18 @@
         <v>46127</v>
       </c>
       <c r="E482" s="4" t="n">
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
         <is>
-          <t>Affordable, Safe and Sustainable aboveground medium to large GH2 storage</t>
+          <t>Next generation of reversible proton conducting ceramic cells and stacks for efficient energy applications at ≥1 kW scale</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-02-01</t>
+          <t>HORIZON-JU-CLEANH2-2026-04-01</t>
         </is>
       </c>
       <c r="C483" s="3" t="n">
@@ -12083,18 +12083,18 @@
         <v>46127</v>
       </c>
       <c r="E483" s="4" t="n">
-        <v>4000000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
         <is>
-          <t>New thermal insulation concepts for bulk liquid hydrogen shipping</t>
+          <t>Innovative business models advancing renewable electrolysis integration in industry</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-02-03</t>
+          <t>HORIZON-JU-CLEANH2-2026-01-04</t>
         </is>
       </c>
       <c r="C484" s="3" t="n">
@@ -12104,18 +12104,18 @@
         <v>46127</v>
       </c>
       <c r="E484" s="4" t="n">
-        <v>4000000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
         <is>
-          <t>Fuel-flexible gas turbine combustion technology for clean and efficient ammonia firing</t>
+          <t>Affordable, Safe and Sustainable aboveground medium to large GH2 storage</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-04-03</t>
+          <t>HORIZON-JU-CLEANH2-2026-02-01</t>
         </is>
       </c>
       <c r="C485" s="3" t="n">
@@ -12125,18 +12125,18 @@
         <v>46127</v>
       </c>
       <c r="E485" s="4" t="n">
-        <v>5000000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
         <is>
-          <t>Scalable and high efficiency materials and reactors for direct solar hydrogen production</t>
+          <t>New thermal insulation concepts for bulk liquid hydrogen shipping</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-01-06</t>
+          <t>HORIZON-JU-CLEANH2-2026-02-03</t>
         </is>
       </c>
       <c r="C486" s="3" t="n">
@@ -12146,18 +12146,18 @@
         <v>46127</v>
       </c>
       <c r="E486" s="4" t="n">
-        <v>3000000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
         <is>
-          <t>Small-scale Hydrogen Valley</t>
+          <t>Fuel-flexible gas turbine combustion technology for clean and efficient ammonia firing</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-06-02</t>
+          <t>HORIZON-JU-CLEANH2-2026-04-03</t>
         </is>
       </c>
       <c r="C487" s="3" t="n">
@@ -12167,18 +12167,18 @@
         <v>46127</v>
       </c>
       <c r="E487" s="4" t="n">
-        <v>8000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
         <is>
-          <t>Public datasets of technologies along the hydrogen value chain for life cycle (sustainability) assessment</t>
+          <t>Scalable and high efficiency materials and reactors for direct solar hydrogen production</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-05-01</t>
+          <t>HORIZON-JU-CLEANH2-2026-01-06</t>
         </is>
       </c>
       <c r="C488" s="3" t="n">
@@ -12188,18 +12188,18 @@
         <v>46127</v>
       </c>
       <c r="E488" s="4" t="n">
-        <v>2500000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
         <is>
-          <t>Development and validation of innovative approaches, catalysts, electrolytes and components for electrolysis technologies based on low-quality water</t>
+          <t>Small-scale Hydrogen Valley</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-01-01</t>
+          <t>HORIZON-JU-CLEANH2-2026-06-02</t>
         </is>
       </c>
       <c r="C489" s="3" t="n">
@@ -12209,18 +12209,18 @@
         <v>46127</v>
       </c>
       <c r="E489" s="4" t="n">
-        <v>3000000</v>
+        <v>8000000</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
         <is>
-          <t>Cost-efficient small scale hydrogen liquefaction</t>
+          <t>Public datasets of technologies along the hydrogen value chain for life cycle (sustainability) assessment</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-02-04</t>
+          <t>HORIZON-JU-CLEANH2-2026-05-01</t>
         </is>
       </c>
       <c r="C490" s="3" t="n">
@@ -12230,18 +12230,18 @@
         <v>46127</v>
       </c>
       <c r="E490" s="4" t="n">
-        <v>6000000</v>
+        <v>2500000</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
         <is>
-          <t>Large-scale Hydrogen Valley</t>
+          <t>Development and validation of innovative approaches, catalysts, electrolytes and components for electrolysis technologies based on low-quality water</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-06-01</t>
+          <t>HORIZON-JU-CLEANH2-2026-01-01</t>
         </is>
       </c>
       <c r="C491" s="3" t="n">
@@ -12251,18 +12251,18 @@
         <v>46127</v>
       </c>
       <c r="E491" s="4" t="n">
-        <v>17000000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
         <is>
-          <t>Sustainable hydrogen production from renewable gases and biogenic waste sources through innovative modular reactor design, process intensification and integration</t>
+          <t>Cost-efficient small scale hydrogen liquefaction</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CLEANH2-2026-01-05</t>
+          <t>HORIZON-JU-CLEANH2-2026-02-04</t>
         </is>
       </c>
       <c r="C492" s="3" t="n">
@@ -12272,81 +12272,81 @@
         <v>46127</v>
       </c>
       <c r="E492" s="4" t="n">
-        <v>3000000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
         <is>
-          <t>EIC 2026 Pathfinder Open</t>
+          <t>Large-scale Hydrogen Valley</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>HORIZON-EIC-2026-PATHFINDEROPEN</t>
+          <t>HORIZON-JU-CLEANH2-2026-06-01</t>
         </is>
       </c>
       <c r="C493" s="3" t="n">
-        <v>46058</v>
+        <v>46063</v>
       </c>
       <c r="D493" s="3" t="n">
-        <v>46154</v>
+        <v>46127</v>
       </c>
       <c r="E493" s="4" t="n">
-        <v>1000000</v>
+        <v>17000000</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
         <is>
-          <t>ROB4GREEN Open Call #1</t>
+          <t>Sustainable hydrogen production from renewable gases and biogenic waste sources through innovative modular reactor design, process intensification and integration</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2024-DIGITAL-EMERGING-01-04</t>
+          <t>HORIZON-JU-CLEANH2-2026-01-05</t>
         </is>
       </c>
       <c r="C494" s="3" t="n">
-        <v>46057</v>
+        <v>46063</v>
       </c>
       <c r="D494" s="3" t="n">
-        <v>46120.70833333334</v>
+        <v>46127</v>
       </c>
       <c r="E494" s="4" t="n">
-        <v>2400000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="inlineStr">
         <is>
-          <t>Standardising and supporting climate services for  climate adaptation</t>
+          <t>EIC 2026 Pathfinder Open</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-01-CLIMA-03</t>
+          <t>HORIZON-EIC-2026-PATHFINDEROPEN</t>
         </is>
       </c>
       <c r="C495" s="3" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="D495" s="3" t="n">
-        <v>46288</v>
+        <v>46154</v>
       </c>
       <c r="E495" s="4" t="n">
-        <v>9000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
         <is>
-          <t>National Adaptation Hubs - Bringing together the national level with the engaged regional and local levels (multi-level governance)</t>
+          <t>Standardising and supporting climate services for  climate adaptation</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-01-CLIMA-01</t>
+          <t>HORIZON-MISS-2026-01-CLIMA-03</t>
         </is>
       </c>
       <c r="C496" s="3" t="n">
@@ -12356,18 +12356,18 @@
         <v>46288</v>
       </c>
       <c r="E496" s="4" t="n">
-        <v>10000000</v>
+        <v>9000000</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="2" t="inlineStr">
         <is>
-          <t>Bridging the gap between disaster risk management and climate adaptation</t>
+          <t>National Adaptation Hubs - Bringing together the national level with the engaged regional and local levels (multi-level governance)</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-01-CLIMA-04</t>
+          <t>HORIZON-MISS-2026-01-CLIMA-01</t>
         </is>
       </c>
       <c r="C497" s="3" t="n">
@@ -12377,18 +12377,18 @@
         <v>46288</v>
       </c>
       <c r="E497" s="4" t="n">
-        <v>5000000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
         <is>
-          <t>Supporting financing of local adaptation actions with combination of public funding and private financing</t>
+          <t>Bridging the gap between disaster risk management and climate adaptation</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-01-CLIMA-07</t>
+          <t>HORIZON-MISS-2026-01-CLIMA-04</t>
         </is>
       </c>
       <c r="C498" s="3" t="n">
@@ -12398,18 +12398,18 @@
         <v>46288</v>
       </c>
       <c r="E498" s="4" t="n">
-        <v>20000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="inlineStr">
         <is>
-          <t>Demonstrating solutions to protect and preserve cultural heritage from the impacts of climate change</t>
+          <t>Supporting financing of local adaptation actions with combination of public funding and private financing</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-01-CLIMA-05</t>
+          <t>HORIZON-MISS-2026-01-CLIMA-07</t>
         </is>
       </c>
       <c r="C499" s="3" t="n">
@@ -12419,18 +12419,18 @@
         <v>46288</v>
       </c>
       <c r="E499" s="4" t="n">
-        <v>7000000</v>
+        <v>20000000</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joint demonstration of solutions to build soil resilience to extreme weather events and support food security </t>
+          <t>Demonstrating solutions to protect and preserve cultural heritage from the impacts of climate change</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-06-CLIMA-SOIL</t>
+          <t>HORIZON-MISS-2026-01-CLIMA-05</t>
         </is>
       </c>
       <c r="C500" s="3" t="n">
@@ -12440,18 +12440,18 @@
         <v>46288</v>
       </c>
       <c r="E500" s="4" t="n">
-        <v>10000000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="inlineStr">
         <is>
-          <t>Improving climate resilience of navigable inland waterways, their surroundings and related water infrastructure</t>
+          <t xml:space="preserve">Joint demonstration of solutions to build soil resilience to extreme weather events and support food security </t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-01-CLIMA-06</t>
+          <t>HORIZON-MISS-2026-06-CLIMA-SOIL</t>
         </is>
       </c>
       <c r="C501" s="3" t="n">
@@ -12461,18 +12461,18 @@
         <v>46288</v>
       </c>
       <c r="E501" s="4" t="n">
-        <v>6000000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
         <is>
-          <t>Facilitating implementation of actionable solutions for climate adaptation of regions and local authorities</t>
+          <t>Improving climate resilience of navigable inland waterways, their surroundings and related water infrastructure</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-01-CLIMA-02</t>
+          <t>HORIZON-MISS-2026-01-CLIMA-06</t>
         </is>
       </c>
       <c r="C502" s="3" t="n">
@@ -12482,18 +12482,18 @@
         <v>46288</v>
       </c>
       <c r="E502" s="4" t="n">
-        <v>5000000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="2" t="inlineStr">
         <is>
-          <t>Leveraging long-term field experiments and other datasets to develop AI-ready decision support systems for sustainable soil management</t>
+          <t>Facilitating implementation of actionable solutions for climate adaptation of regions and local authorities</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-05-SOIL-04</t>
+          <t>HORIZON-MISS-2026-01-CLIMA-02</t>
         </is>
       </c>
       <c r="C503" s="3" t="n">
@@ -12503,18 +12503,18 @@
         <v>46288</v>
       </c>
       <c r="E503" s="4" t="n">
-        <v>9000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
         <is>
-          <t>Antimicrobial resistance and antibiotic biosynthesis in soils: developing key understanding and counteractive strategies using a One-Health approach</t>
+          <t>Leveraging long-term field experiments and other datasets to develop AI-ready decision support systems for sustainable soil management</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-05-SOIL-02</t>
+          <t>HORIZON-MISS-2026-05-SOIL-04</t>
         </is>
       </c>
       <c r="C504" s="3" t="n">
@@ -12524,18 +12524,18 @@
         <v>46288</v>
       </c>
       <c r="E504" s="4" t="n">
-        <v>7000000</v>
+        <v>9000000</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="2" t="inlineStr">
         <is>
-          <t>Monitoring soil health in practice: equipping stakeholders to sample, analyse, and interpret soil health indicators</t>
+          <t>Antimicrobial resistance and antibiotic biosynthesis in soils: developing key understanding and counteractive strategies using a One-Health approach</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-05-SOIL-01</t>
+          <t>HORIZON-MISS-2026-05-SOIL-02</t>
         </is>
       </c>
       <c r="C505" s="3" t="n">
@@ -12545,18 +12545,18 @@
         <v>46288</v>
       </c>
       <c r="E505" s="4" t="n">
-        <v>5000000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
         <is>
-          <t>Enabling user-centred and open innovation initiatives to enhance soil health in Ukraine</t>
+          <t>Monitoring soil health in practice: equipping stakeholders to sample, analyse, and interpret soil health indicators</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-05-SOIL-03</t>
+          <t>HORIZON-MISS-2026-05-SOIL-01</t>
         </is>
       </c>
       <c r="C506" s="3" t="n">
@@ -12572,33 +12572,33 @@
     <row r="507">
       <c r="A507" s="2" t="inlineStr">
         <is>
-          <t>Introducing circular economy models in the construction sector, from buildings to city scale</t>
+          <t>Enabling user-centred and open innovation initiatives to enhance soil health in Ukraine</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-04-CIT-NEB-B4P-CCRI-03</t>
+          <t>HORIZON-MISS-2026-05-SOIL-03</t>
         </is>
       </c>
       <c r="C507" s="3" t="n">
         <v>46057</v>
       </c>
       <c r="D507" s="3" t="n">
-        <v>46303</v>
+        <v>46288</v>
       </c>
       <c r="E507" s="4" t="n">
-        <v>9500000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
         <is>
-          <t>Energy efficient urban and sub-urban public transport, complemented by shared mobility</t>
+          <t>Introducing circular economy models in the construction sector, from buildings to city scale</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-04-CIT-01</t>
+          <t>HORIZON-MISS-2026-04-CIT-NEB-B4P-CCRI-03</t>
         </is>
       </c>
       <c r="C508" s="3" t="n">
@@ -12608,18 +12608,18 @@
         <v>46303</v>
       </c>
       <c r="E508" s="4" t="n">
-        <v>10000000</v>
+        <v>9500000</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" s="2" t="inlineStr">
         <is>
-          <t>Transition to low-temperature heating solutions in multi-apartment buildings</t>
+          <t>Energy efficient urban and sub-urban public transport, complemented by shared mobility</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-04-CIT-02</t>
+          <t>HORIZON-MISS-2026-04-CIT-01</t>
         </is>
       </c>
       <c r="C509" s="3" t="n">
@@ -12629,39 +12629,39 @@
         <v>46303</v>
       </c>
       <c r="E509" s="4" t="n">
-        <v>6000000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="2" t="inlineStr">
         <is>
-          <t>Regional  (sea-basins) components of the EU Digital Twin Ocean</t>
+          <t>Transition to low-temperature heating solutions in multi-apartment buildings</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-03-OCEAN-05</t>
+          <t>HORIZON-MISS-2026-04-CIT-02</t>
         </is>
       </c>
       <c r="C510" s="3" t="n">
         <v>46057</v>
       </c>
       <c r="D510" s="3" t="n">
-        <v>46288</v>
+        <v>46303</v>
       </c>
       <c r="E510" s="4" t="n">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" s="2" t="inlineStr">
         <is>
-          <t>By fishers, for fishers: co-management of marine and freshwaters ecosystems and resources</t>
+          <t>Regional  (sea-basins) components of the EU Digital Twin Ocean</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-03-OCEAN-03</t>
+          <t>HORIZON-MISS-2026-03-OCEAN-05</t>
         </is>
       </c>
       <c r="C511" s="3" t="n">
@@ -12671,18 +12671,18 @@
         <v>46288</v>
       </c>
       <c r="E511" s="4" t="n">
-        <v>7000000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" s="2" t="inlineStr">
         <is>
-          <t>Large-scale demonstration for mapping the distribution and condition of marine habitats to implement the Nature Restoration Regulation</t>
+          <t>By fishers, for fishers: co-management of marine and freshwaters ecosystems and resources</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-03-OCEAN-01</t>
+          <t>HORIZON-MISS-2026-03-OCEAN-03</t>
         </is>
       </c>
       <c r="C512" s="3" t="n">
@@ -12698,12 +12698,12 @@
     <row r="513">
       <c r="A513" s="2" t="inlineStr">
         <is>
-          <t>Towards a European network of ocean technology testing sites</t>
+          <t>Large-scale demonstration for mapping the distribution and condition of marine habitats to implement the Nature Restoration Regulation</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-03-OCEAN-04</t>
+          <t>HORIZON-MISS-2026-03-OCEAN-01</t>
         </is>
       </c>
       <c r="C513" s="3" t="n">
@@ -12713,18 +12713,18 @@
         <v>46288</v>
       </c>
       <c r="E513" s="4" t="n">
-        <v>2500000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" s="2" t="inlineStr">
         <is>
-          <t>Addressing aquatic pollution and biodiversity loss through nature positive solutions from source to sea</t>
+          <t>Towards a European network of ocean technology testing sites</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2026-03-OCEAN-02</t>
+          <t>HORIZON-MISS-2026-03-OCEAN-04</t>
         </is>
       </c>
       <c r="C514" s="3" t="n">
@@ -12734,39 +12734,39 @@
         <v>46288</v>
       </c>
       <c r="E514" s="4" t="n">
-        <v>7000000</v>
+        <v>2500000</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" s="2" t="inlineStr">
         <is>
-          <t>Innovation for regional rail services and new guided transport systems</t>
+          <t>Addressing aquatic pollution and biodiversity loss through nature positive solutions from source to sea</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>HORIZON-JU-ER-2026-FA6FA7-01</t>
+          <t>HORIZON-MISS-2026-03-OCEAN-02</t>
         </is>
       </c>
       <c r="C515" s="3" t="n">
         <v>46057</v>
       </c>
       <c r="D515" s="3" t="n">
-        <v>46149</v>
+        <v>46288</v>
       </c>
       <c r="E515" s="4" t="n">
-        <v>3100000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" s="2" t="inlineStr">
         <is>
-          <t>Safety and certification guidelines and demonstration of safety components for hyperloop</t>
+          <t>Innovation for regional rail services and new guided transport systems</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>HORIZON-JU-ER-2026-FA7-01</t>
+          <t>HORIZON-JU-ER-2026-FA6FA7-01</t>
         </is>
       </c>
       <c r="C516" s="3" t="n">
@@ -12776,39 +12776,39 @@
         <v>46149</v>
       </c>
       <c r="E516" s="4" t="n">
-        <v>3000000</v>
+        <v>3100000</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" s="2" t="inlineStr">
         <is>
-          <t>RIA Global call according to SRIA 2026</t>
+          <t>Safety and certification guidelines and demonstration of safety components for hyperloop</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CHIPS-2026-1-RIA</t>
+          <t>HORIZON-JU-ER-2026-FA7-01</t>
         </is>
       </c>
       <c r="C517" s="3" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="D517" s="3" t="n">
-        <v>46282</v>
+        <v>46149</v>
       </c>
       <c r="E517" s="4" t="n">
-        <v>1000000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" s="2" t="inlineStr">
         <is>
-          <t>IA Global call according to SRIA 2026</t>
+          <t>RIA Global call according to SRIA 2026</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CHIPS-2026-1-IA</t>
+          <t>HORIZON-JU-CHIPS-2026-1-RIA</t>
         </is>
       </c>
       <c r="C518" s="3" t="n">
@@ -12824,19 +12824,19 @@
     <row r="519">
       <c r="A519" s="2" t="inlineStr">
         <is>
-          <t>BlueActionAA – Transition Agenda Call (BAAT-01)</t>
+          <t>IA Global call according to SRIA 2026</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-OCEAN-02-01</t>
+          <t>HORIZON-JU-CHIPS-2026-1-IA</t>
         </is>
       </c>
       <c r="C519" s="3" t="n">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="D519" s="3" t="n">
-        <v>46171.58333333334</v>
+        <v>46282</v>
       </c>
       <c r="E519" s="4" t="n">
         <v>1000000</v>
@@ -12845,33 +12845,33 @@
     <row r="520">
       <c r="A520" s="2" t="inlineStr">
         <is>
-          <t>SNS Operations and Output optimisation</t>
+          <t>BlueActionAA – Transition Agenda Call (BAAT-01)</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>HORIZON-JU-SNS-2026-STREAM-CSA-01</t>
+          <t>HORIZON-MISS-2024-OCEAN-02-01</t>
         </is>
       </c>
       <c r="C520" s="3" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="D520" s="3" t="n">
-        <v>46141</v>
+        <v>46171.58333333334</v>
       </c>
       <c r="E520" s="4" t="n">
-        <v>3000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" s="2" t="inlineStr">
         <is>
-          <t>6G Devices</t>
+          <t>SNS Operations and Output optimisation</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>HORIZON-JU-SNS-2026-STREAM-CSA-02</t>
+          <t>HORIZON-JU-SNS-2026-STREAM-CSA-01</t>
         </is>
       </c>
       <c r="C521" s="3" t="n">
@@ -12881,18 +12881,18 @@
         <v>46141</v>
       </c>
       <c r="E521" s="4" t="n">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" s="2" t="inlineStr">
         <is>
-          <t>Collection, Generation and Validation of Datasets  suitable for training AI Models for 6G Networks and for AIaaS</t>
+          <t>6G Devices</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>HORIZON-JU-SNS-2026-STREAM-B-01</t>
+          <t>HORIZON-JU-SNS-2026-STREAM-CSA-02</t>
         </is>
       </c>
       <c r="C522" s="3" t="n">
@@ -12902,18 +12902,18 @@
         <v>46141</v>
       </c>
       <c r="E522" s="4" t="n">
-        <v>8000000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" s="2" t="inlineStr">
         <is>
-          <t>EU-India International Collaboration</t>
+          <t>Collection, Generation and Validation of Datasets  suitable for training AI Models for 6G Networks and for AIaaS</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>HORIZON-JU-SNS-2026-STREAM-CSA-03</t>
+          <t>HORIZON-JU-SNS-2026-STREAM-B-01</t>
         </is>
       </c>
       <c r="C523" s="3" t="n">
@@ -12923,18 +12923,18 @@
         <v>46141</v>
       </c>
       <c r="E523" s="4" t="n">
-        <v>1000000</v>
+        <v>8000000</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" s="2" t="inlineStr">
         <is>
-          <t>SNS experimental infrastructure</t>
+          <t>EU-India International Collaboration</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>HORIZON-JU-SNS-2026-STREAM-C-01</t>
+          <t>HORIZON-JU-SNS-2026-STREAM-CSA-03</t>
         </is>
       </c>
       <c r="C524" s="3" t="n">
@@ -12944,204 +12944,204 @@
         <v>46141</v>
       </c>
       <c r="E524" s="4" t="n">
-        <v>8000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="2" t="inlineStr">
         <is>
-          <t>Excel4Pro Open Call</t>
+          <t>SNS experimental infrastructure</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>HORIZON-WIDERA-2023-ACCESS-07-01</t>
+          <t>HORIZON-JU-SNS-2026-STREAM-C-01</t>
         </is>
       </c>
       <c r="C525" s="3" t="n">
-        <v>46048</v>
+        <v>46051</v>
       </c>
       <c r="D525" s="3" t="n">
-        <v>46139.70833333334</v>
+        <v>46141</v>
       </c>
       <c r="E525" s="4" t="n">
-        <v>360000</v>
+        <v>8000000</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" s="2" t="inlineStr">
         <is>
-          <t>Renewable energy technology (RET) solutions in energy communities</t>
+          <t>Excel4Pro Open Call</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2026-2-PRIZE</t>
+          <t>HORIZON-WIDERA-2023-ACCESS-07-01</t>
         </is>
       </c>
       <c r="C526" s="3" t="n">
-        <v>46042</v>
+        <v>46048</v>
       </c>
       <c r="D526" s="3" t="n">
-        <v>46198</v>
+        <v>46139.70833333334</v>
+      </c>
+      <c r="E526" s="4" t="n">
+        <v>360000</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" s="2" t="inlineStr">
         <is>
-          <t>ERC PROOF OF CONCEPT GRANTS</t>
+          <t>Renewable energy technology (RET) solutions in energy communities</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>ERC-2026-POC</t>
+          <t>HORIZON-CL5-2026-2-PRIZE</t>
         </is>
       </c>
       <c r="C527" s="3" t="n">
         <v>46042</v>
       </c>
       <c r="D527" s="3" t="n">
-        <v>46282</v>
-      </c>
-      <c r="E527" s="4" t="n">
-        <v>150000</v>
+        <v>46198</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" s="2" t="inlineStr">
         <is>
-          <t>Joint Transnational Call 2026 for the BE READY Partnership: Advancing knowledge of host and pathogens dynamics to better combat emerging diseases</t>
+          <t>ERC PROOF OF CONCEPT GRANTS</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2024-DISEASE-12-01</t>
+          <t>ERC-2026-POC</t>
         </is>
       </c>
       <c r="C528" s="3" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="D528" s="3" t="n">
-        <v>46254.54166666666</v>
+        <v>46282</v>
       </c>
       <c r="E528" s="4" t="n">
-        <v>16400000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" s="2" t="inlineStr">
         <is>
-          <t>Developing and demonstrating core technologies for Virtual Worlds and Web 4.0 (IA) (Virtual worlds Partnership)</t>
+          <t>Joint Transnational Call 2026 for the BE READY Partnership: Advancing knowledge of host and pathogens dynamics to better combat emerging diseases</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-04-HUMAN-01</t>
+          <t>HORIZON-HLTH-2024-DISEASE-12-01</t>
         </is>
       </c>
       <c r="C529" s="3" t="n">
-        <v>46037</v>
+        <v>46041</v>
       </c>
       <c r="D529" s="3" t="n">
-        <v>46127</v>
+        <v>46254.54166666666</v>
       </c>
       <c r="E529" s="4" t="n">
-        <v>4000000</v>
+        <v>16400000</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="2" t="inlineStr">
         <is>
-          <t>Networking and Future Photonics Strategy  (CSA) (Photonics Partnership)</t>
+          <t>Boosting innovation for a better understanding of the determinants of health</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-14</t>
+          <t>HORIZON-JU-IHI-2026-12-SINGLE-STAGE-01</t>
         </is>
       </c>
       <c r="C530" s="3" t="n">
         <v>46037</v>
       </c>
       <c r="D530" s="3" t="n">
-        <v>46127</v>
+        <v>46133</v>
       </c>
       <c r="E530" s="4" t="n">
-        <v>3000000</v>
+        <v>8000000</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" s="2" t="inlineStr">
         <is>
-          <t>Fostering 2-Dimensional Materials (2DM) based emerging and enabling technologies (CSA)</t>
+          <t>Boosting innovation through better integration of fragmented health R&amp;I efforts</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-17</t>
+          <t>HORIZON-JU-IHI-2026-12-SINGLE-STAGE-02</t>
         </is>
       </c>
       <c r="C531" s="3" t="n">
         <v>46037</v>
       </c>
       <c r="D531" s="3" t="n">
-        <v>46127</v>
+        <v>46133</v>
       </c>
       <c r="E531" s="4" t="n">
-        <v>1000000</v>
+        <v>15000000</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" s="2" t="inlineStr">
         <is>
-          <t>Apply AI: Robotics for Manufacturing: Advancing Core Skills through Technical Challenges (RIA) (Partnership in AI, Data and Robotics)</t>
+          <t>Boosting innovation through exploitation of digitalisation and data exchange in healthcare</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-08</t>
+          <t>HORIZON-JU-IHI-2026-12-SINGLE-STAGE-04</t>
         </is>
       </c>
       <c r="C532" s="3" t="n">
         <v>46037</v>
       </c>
       <c r="D532" s="3" t="n">
-        <v>46127</v>
+        <v>46133</v>
       </c>
       <c r="E532" s="4" t="n">
-        <v>18000000</v>
+        <v>8000000</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" s="2" t="inlineStr">
         <is>
-          <t>Strengthening the cooperation of semiconductor-intensive EU regions (CSA)</t>
+          <t>Boosting innovation for better assessment of the added value of innovative integrated healthcare solutions</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-15</t>
+          <t>HORIZON-JU-IHI-2026-12-SINGLE-STAGE-05</t>
         </is>
       </c>
       <c r="C533" s="3" t="n">
         <v>46037</v>
       </c>
       <c r="D533" s="3" t="n">
-        <v>46127</v>
+        <v>46133</v>
       </c>
       <c r="E533" s="4" t="n">
-        <v>1000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" s="2" t="inlineStr">
         <is>
-          <t>Boosting innovation for a better understanding of the determinants of health</t>
+          <t>Boosting innovation for people-centred integrated healthcare solutions</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>HORIZON-JU-IHI-2026-12-SINGLE-STAGE-01</t>
+          <t>HORIZON-JU-IHI-2026-12-SINGLE-STAGE-03</t>
         </is>
       </c>
       <c r="C534" s="3" t="n">
@@ -13157,12 +13157,12 @@
     <row r="535">
       <c r="A535" s="2" t="inlineStr">
         <is>
-          <t>Advanced Local Digital Twins using AI for Early Warning and Preparedness (IA)</t>
+          <t>New or enhanced Innovative Advanced Materials (IAM) enabled sensing functionality (RIA)</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-09</t>
+          <t>HORIZON-CL4-2026-05-MAT-PROD-25</t>
         </is>
       </c>
       <c r="C535" s="3" t="n">
@@ -13172,18 +13172,18 @@
         <v>46127</v>
       </c>
       <c r="E535" s="4" t="n">
-        <v>6000000</v>
+        <v>7500000</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" s="2" t="inlineStr">
         <is>
-          <t>Apply AI: Pilot of the “Science for AI” Pillar of RAISE (“Resource for AI science in Europe”) (RIA)</t>
+          <t>Apply AI: Next-Generation Agile and Intelligent Robotics Platforms for Industrial and Service Applications (Partnership in AI, Data and Robotics) (RIA)</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-01</t>
+          <t>HORIZON-CL4-2026-05-DIGITAL-EMERGING-03</t>
         </is>
       </c>
       <c r="C536" s="3" t="n">
@@ -13193,18 +13193,18 @@
         <v>46127</v>
       </c>
       <c r="E536" s="4" t="n">
-        <v>17000000</v>
+        <v>12000000</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" s="2" t="inlineStr">
         <is>
-          <t>Grand Challenge on Quantum Sensors for Inertial Navigation</t>
+          <t>Next-Generation AI Agents for Real-World Applications in the Apply AI sectors (RIA) (Partnership in AI, Data and Robotics)</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-11</t>
+          <t>HORIZON-CL4-2026-05-DIGITAL-EMERGING-02</t>
         </is>
       </c>
       <c r="C537" s="3" t="n">
@@ -13214,102 +13214,102 @@
         <v>46127</v>
       </c>
       <c r="E537" s="4" t="n">
-        <v>500000</v>
+        <v>19000000</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" s="2" t="inlineStr">
         <is>
-          <t>Boosting innovation through better integration of fragmented health R&amp;I efforts</t>
+          <t>Open Internet Stack Support for Scale (CSA)</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>HORIZON-JU-IHI-2026-12-SINGLE-STAGE-02</t>
+          <t>HORIZON-CL4-2026-04-DATA-03</t>
         </is>
       </c>
       <c r="C538" s="3" t="n">
         <v>46037</v>
       </c>
       <c r="D538" s="3" t="n">
-        <v>46133</v>
+        <v>46127</v>
       </c>
       <c r="E538" s="4" t="n">
-        <v>15000000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" s="2" t="inlineStr">
         <is>
-          <t>Boosting innovation through exploitation of digitalisation and data exchange in healthcare</t>
+          <t>Efficient and compliant access to and use of data (IA) (AI, Data and Robotics partnership)</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>HORIZON-JU-IHI-2026-12-SINGLE-STAGE-04</t>
+          <t>HORIZON-CL4-2026-04-DATA-06</t>
         </is>
       </c>
       <c r="C539" s="3" t="n">
         <v>46037</v>
       </c>
       <c r="D539" s="3" t="n">
-        <v>46133</v>
+        <v>46127</v>
       </c>
       <c r="E539" s="4" t="n">
-        <v>8000000</v>
+        <v>11500000</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" s="2" t="inlineStr">
         <is>
-          <t>Boosting innovation for better assessment of the added value of innovative integrated healthcare solutions</t>
+          <t>Open Internet Stack Sovereign Solutions (RIA)</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>HORIZON-JU-IHI-2026-12-SINGLE-STAGE-05</t>
+          <t>HORIZON-CL4-2026-04-DATA-02</t>
         </is>
       </c>
       <c r="C540" s="3" t="n">
         <v>46037</v>
       </c>
       <c r="D540" s="3" t="n">
-        <v>46133</v>
+        <v>46127</v>
       </c>
       <c r="E540" s="4" t="n">
-        <v>5000000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" s="2" t="inlineStr">
         <is>
-          <t>Boosting innovation for people-centred integrated healthcare solutions</t>
+          <t>Standards for Quantum Technologies – Coordination and Support Action (CSA)</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>HORIZON-JU-IHI-2026-12-SINGLE-STAGE-03</t>
+          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-12</t>
         </is>
       </c>
       <c r="C541" s="3" t="n">
         <v>46037</v>
       </c>
       <c r="D541" s="3" t="n">
-        <v>46133</v>
+        <v>46127</v>
       </c>
       <c r="E541" s="4" t="n">
-        <v>8000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" s="2" t="inlineStr">
         <is>
-          <t>Efficient and compliant access to and use of data (IA) (AI, Data and Robotics partnership)</t>
+          <t>Challenge-Driven GenAI4EU Booster in Apply AI prioritised sectors (RIA) (AI/Data/Robotics Partnership)</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-04-DATA-06</t>
+          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-19</t>
         </is>
       </c>
       <c r="C542" s="3" t="n">
@@ -13319,18 +13319,18 @@
         <v>46127</v>
       </c>
       <c r="E542" s="4" t="n">
-        <v>11500000</v>
+        <v>15000000</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" s="2" t="inlineStr">
         <is>
-          <t>Large-Scale Photonic Quantum Computing Platform Technologies (RIA)</t>
+          <t>Apply AI: Robotics for Manufacturing: Advancing Core Skills through Technical Challenges (RIA) (Partnership in AI, Data and Robotics)</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-18</t>
+          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-08</t>
         </is>
       </c>
       <c r="C543" s="3" t="n">
@@ -13340,18 +13340,18 @@
         <v>46127</v>
       </c>
       <c r="E543" s="4" t="n">
-        <v>10000000</v>
+        <v>18000000</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" s="2" t="inlineStr">
         <is>
-          <t>Challenge-Driven GenAI4EU Booster in Apply AI prioritised sectors (RIA) (AI/Data/Robotics Partnership)</t>
+          <t>Web 4.0 architectural framework and Open Internet Stack applications for virtual worlds (RIA)</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-19</t>
+          <t>HORIZON-CL4-2026-04-HUMAN-02</t>
         </is>
       </c>
       <c r="C544" s="3" t="n">
@@ -13361,18 +13361,18 @@
         <v>46127</v>
       </c>
       <c r="E544" s="4" t="n">
-        <v>15000000</v>
+        <v>2800000</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" s="2" t="inlineStr">
         <is>
-          <t>Web 4.0 architectural framework and Open Internet Stack applications for virtual worlds (RIA)</t>
+          <t>Advanced Local Digital Twins using AI for Early Warning and Preparedness (IA)</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-04-HUMAN-02</t>
+          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-09</t>
         </is>
       </c>
       <c r="C545" s="3" t="n">
@@ -13382,18 +13382,18 @@
         <v>46127</v>
       </c>
       <c r="E545" s="4" t="n">
-        <v>2800000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" s="2" t="inlineStr">
         <is>
-          <t>Open Internet Stack Sovereign Solutions (RIA)</t>
+          <t>Large-Scale Photonic Quantum Computing Platform Technologies (RIA)</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-04-DATA-02</t>
+          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-18</t>
         </is>
       </c>
       <c r="C546" s="3" t="n">
@@ -13403,18 +13403,18 @@
         <v>46127</v>
       </c>
       <c r="E546" s="4" t="n">
-        <v>7000000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" s="2" t="inlineStr">
         <is>
-          <t>Open Internet Stack Support for Scale (CSA)</t>
+          <t>Grand Challenge on Quantum Sensors for Inertial Navigation</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-04-DATA-03</t>
+          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-11</t>
         </is>
       </c>
       <c r="C547" s="3" t="n">
@@ -13424,18 +13424,18 @@
         <v>46127</v>
       </c>
       <c r="E547" s="4" t="n">
-        <v>4000000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" s="2" t="inlineStr">
         <is>
-          <t>Standards for Quantum Technologies – Coordination and Support Action (CSA)</t>
+          <t>Developing and demonstrating core technologies for Virtual Worlds and Web 4.0 (IA) (Virtual worlds Partnership)</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-12</t>
+          <t>HORIZON-CL4-2026-04-HUMAN-01</t>
         </is>
       </c>
       <c r="C548" s="3" t="n">
@@ -13445,18 +13445,18 @@
         <v>46127</v>
       </c>
       <c r="E548" s="4" t="n">
-        <v>1000000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" s="2" t="inlineStr">
         <is>
-          <t>New or enhanced Innovative Advanced Materials (IAM) enabled sensing functionality (RIA)</t>
+          <t>Apply AI: Pilot of the “Science for AI” Pillar of RAISE (“Resource for AI science in Europe”) (RIA)</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-05-MAT-PROD-25</t>
+          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-01</t>
         </is>
       </c>
       <c r="C549" s="3" t="n">
@@ -13466,18 +13466,18 @@
         <v>46127</v>
       </c>
       <c r="E549" s="4" t="n">
-        <v>7500000</v>
+        <v>17000000</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" s="2" t="inlineStr">
         <is>
-          <t>Apply AI: Next-Generation Agile and Intelligent Robotics Platforms for Industrial and Service Applications (Partnership in AI, Data and Robotics) (RIA)</t>
+          <t>Networking and Future Photonics Strategy  (CSA) (Photonics Partnership)</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-05-DIGITAL-EMERGING-03</t>
+          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-14</t>
         </is>
       </c>
       <c r="C550" s="3" t="n">
@@ -13487,18 +13487,18 @@
         <v>46127</v>
       </c>
       <c r="E550" s="4" t="n">
-        <v>12000000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" s="2" t="inlineStr">
         <is>
-          <t>Next-Generation AI Agents for Real-World Applications in the Apply AI sectors (RIA) (Partnership in AI, Data and Robotics)</t>
+          <t>Strengthening the cooperation of semiconductor-intensive EU regions (CSA)</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2026-05-DIGITAL-EMERGING-02</t>
+          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-15</t>
         </is>
       </c>
       <c r="C551" s="3" t="n">
@@ -13508,39 +13508,39 @@
         <v>46127</v>
       </c>
       <c r="E551" s="4" t="n">
-        <v>19000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" s="2" t="inlineStr">
         <is>
-          <t>Enhancing integrated research and healthcare in sub-Saharan Africa through digital innovation and Artificial Intelligence</t>
+          <t>Fostering 2-Dimensional Materials (2DM) based emerging and enabling technologies (CSA)</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>HORIZON-JU-GH-EDCTP3-2026-03-DIGIT-02</t>
+          <t>HORIZON-CL4-2026-04-DIGITAL-EMERGING-17</t>
         </is>
       </c>
       <c r="C552" s="3" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="D552" s="3" t="n">
-        <v>46267</v>
+        <v>46127</v>
       </c>
       <c r="E552" s="4" t="n">
-        <v>2250000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" s="2" t="inlineStr">
         <is>
-          <t>Training and innovation networks for sustained capacity development related to ethics, regulatory, pharmacovigilance, and related digital regulatory platforms</t>
+          <t>Enhancing integrated research and healthcare in sub-Saharan Africa through digital innovation and Artificial Intelligence</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>HORIZON-JU-GH-EDCTP3-2026-03-SERP-01</t>
+          <t>HORIZON-JU-GH-EDCTP3-2026-03-DIGIT-02</t>
         </is>
       </c>
       <c r="C553" s="3" t="n">
@@ -13550,39 +13550,39 @@
         <v>46267</v>
       </c>
       <c r="E553" s="4" t="n">
-        <v>1500000</v>
+        <v>2250000</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" s="2" t="inlineStr">
         <is>
-          <t>Strengthening the EU plant protection ecosystem for a future-proof agriculture</t>
+          <t>Training and innovation networks for sustained capacity development related to ethics, regulatory, pharmacovigilance, and related digital regulatory platforms</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-FARM2FORK-07</t>
+          <t>HORIZON-JU-GH-EDCTP3-2026-03-SERP-01</t>
         </is>
       </c>
       <c r="C554" s="3" t="n">
         <v>46036</v>
       </c>
       <c r="D554" s="3" t="n">
-        <v>46126</v>
+        <v>46267</v>
       </c>
       <c r="E554" s="4" t="n">
-        <v>3000000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" s="2" t="inlineStr">
         <is>
-          <t>Developing innovative phytosanitary treatments for regulated plant pests to support safe international trade</t>
+          <t>Strengthening the EU plant protection ecosystem for a future-proof agriculture</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-FARM2FORK-01</t>
+          <t>HORIZON-CL6-2026-02-FARM2FORK-07</t>
         </is>
       </c>
       <c r="C555" s="3" t="n">
@@ -13592,18 +13592,18 @@
         <v>46126</v>
       </c>
       <c r="E555" s="4" t="n">
-        <v>5900000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" s="2" t="inlineStr">
         <is>
-          <t>Leveraging R&amp;I knowledge on microbiome</t>
+          <t>Developing innovative phytosanitary treatments for regulated plant pests to support safe international trade</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-FARM2FORK-12</t>
+          <t>HORIZON-CL6-2026-02-FARM2FORK-01</t>
         </is>
       </c>
       <c r="C556" s="3" t="n">
@@ -13613,18 +13613,18 @@
         <v>46126</v>
       </c>
       <c r="E556" s="4" t="n">
-        <v>2000000</v>
+        <v>5900000</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" s="2" t="inlineStr">
         <is>
-          <t>Advancing basic knowledge and developing tools for sustainable management of key migratory fish species</t>
+          <t>Leveraging R&amp;I knowledge on microbiome</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-FARM2FORK-08</t>
+          <t>HORIZON-CL6-2026-02-FARM2FORK-12</t>
         </is>
       </c>
       <c r="C557" s="3" t="n">
@@ -13634,18 +13634,18 @@
         <v>46126</v>
       </c>
       <c r="E557" s="4" t="n">
-        <v>7000000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" s="2" t="inlineStr">
         <is>
-          <t>Boosting sustainable competitiveness in rural areas through innovation</t>
+          <t>Advancing basic knowledge and developing tools for sustainable management of key migratory fish species</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-COMMUNITIES-01</t>
+          <t>HORIZON-CL6-2026-02-FARM2FORK-08</t>
         </is>
       </c>
       <c r="C558" s="3" t="n">
@@ -13655,18 +13655,18 @@
         <v>46126</v>
       </c>
       <c r="E558" s="4" t="n">
-        <v>5000000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" s="2" t="inlineStr">
         <is>
-          <t>Boosting the competitiveness of protein crops in Europe</t>
+          <t>Boosting sustainable competitiveness in rural areas through innovation</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-FARM2FORK-03</t>
+          <t>HORIZON-CL6-2026-02-COMMUNITIES-01</t>
         </is>
       </c>
       <c r="C559" s="3" t="n">
@@ -13676,18 +13676,18 @@
         <v>46126</v>
       </c>
       <c r="E559" s="4" t="n">
-        <v>6000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" s="2" t="inlineStr">
         <is>
-          <t>Integrating a holistic perspective in microbiome research for resilient, competitive and sustainable food systems</t>
+          <t>Boosting the competitiveness of protein crops in Europe</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-FARM2FORK-11</t>
+          <t>HORIZON-CL6-2026-02-FARM2FORK-03</t>
         </is>
       </c>
       <c r="C560" s="3" t="n">
@@ -13697,18 +13697,18 @@
         <v>46126</v>
       </c>
       <c r="E560" s="4" t="n">
-        <v>5000000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" s="2" t="inlineStr">
         <is>
-          <t>Tackling pesticide resistance: early detection, management strategies, and foresight</t>
+          <t>Integrating a holistic perspective in microbiome research for resilient, competitive and sustainable food systems</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-FARM2FORK-02</t>
+          <t>HORIZON-CL6-2026-02-FARM2FORK-11</t>
         </is>
       </c>
       <c r="C561" s="3" t="n">
@@ -13718,18 +13718,18 @@
         <v>46126</v>
       </c>
       <c r="E561" s="4" t="n">
-        <v>6000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" s="2" t="inlineStr">
         <is>
-          <t>Boosting plant health and reducing losses on farm and during storage for sustainable growth in Africa (FNSSA)</t>
+          <t>Tackling pesticide resistance: early detection, management strategies, and foresight</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-FARM2FORK-13</t>
+          <t>HORIZON-CL6-2026-02-FARM2FORK-02</t>
         </is>
       </c>
       <c r="C562" s="3" t="n">
@@ -13745,12 +13745,12 @@
     <row r="563">
       <c r="A563" s="2" t="inlineStr">
         <is>
-          <t>Advanced innovative solutions for improved competitiveness and sustainability in controlled environment agriculture (CEA)</t>
+          <t>Boosting plant health and reducing losses on farm and during storage for sustainable growth in Africa (FNSSA)</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-FARM2FORK-06</t>
+          <t>HORIZON-CL6-2026-02-FARM2FORK-13</t>
         </is>
       </c>
       <c r="C563" s="3" t="n">
@@ -13766,33 +13766,33 @@
     <row r="564">
       <c r="A564" s="2" t="inlineStr">
         <is>
-          <t>Additional activities for the Sustainable Blue Economy Partnership (SBEP)</t>
+          <t>Advanced innovative solutions for improved competitiveness and sustainability in controlled environment agriculture (CEA)</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-03-GOVERNANCE-01</t>
+          <t>HORIZON-CL6-2026-02-FARM2FORK-06</t>
         </is>
       </c>
       <c r="C564" s="3" t="n">
         <v>46036</v>
       </c>
       <c r="D564" s="3" t="n">
-        <v>46127</v>
+        <v>46126</v>
       </c>
       <c r="E564" s="4" t="n">
-        <v>38000000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" s="2" t="inlineStr">
         <is>
-          <t>Interconnect Earth Observation research for addressing environmental policies</t>
+          <t>Additional activities for the Sustainable Blue Economy Partnership (SBEP)</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-03-GOVERNANCE-07</t>
+          <t>HORIZON-CL6-2026-03-GOVERNANCE-01</t>
         </is>
       </c>
       <c r="C565" s="3" t="n">
@@ -13802,18 +13802,18 @@
         <v>46127</v>
       </c>
       <c r="E565" s="4" t="n">
-        <v>5400000</v>
+        <v>38000000</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" s="2" t="inlineStr">
         <is>
-          <t>Boosting data availability and AI solutions in food for consumers and food service professionals</t>
+          <t>Interconnect Earth Observation research for addressing environmental policies</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-03-GOVERNANCE-08</t>
+          <t>HORIZON-CL6-2026-03-GOVERNANCE-07</t>
         </is>
       </c>
       <c r="C566" s="3" t="n">
@@ -13823,18 +13823,18 @@
         <v>46127</v>
       </c>
       <c r="E566" s="4" t="n">
-        <v>7500000</v>
+        <v>5400000</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" s="2" t="inlineStr">
         <is>
-          <t>A services and business incubator for geospatial open-source developments</t>
+          <t>Boosting data availability and AI solutions in food for consumers and food service professionals</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-03-GOVERNANCE-06</t>
+          <t>HORIZON-CL6-2026-03-GOVERNANCE-08</t>
         </is>
       </c>
       <c r="C567" s="3" t="n">
@@ -13844,25 +13844,25 @@
         <v>46127</v>
       </c>
       <c r="E567" s="4" t="n">
-        <v>6000000</v>
+        <v>7500000</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" s="2" t="inlineStr">
         <is>
-          <t>Towards more effective, fair and coherent policies for climate change mitigation and adaptation in agriculture and forestry</t>
+          <t>A services and business incubator for geospatial open-source developments</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-CLIMATE-01</t>
+          <t>HORIZON-CL6-2026-03-GOVERNANCE-06</t>
         </is>
       </c>
       <c r="C568" s="3" t="n">
         <v>46036</v>
       </c>
       <c r="D568" s="3" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="E568" s="4" t="n">
         <v>6000000</v>
@@ -13871,33 +13871,33 @@
     <row r="569">
       <c r="A569" s="2" t="inlineStr">
         <is>
-          <t>Empowering the UN Decade of Ocean Science for Sustainable Development</t>
+          <t>Towards more effective, fair and coherent policies for climate change mitigation and adaptation in agriculture and forestry</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-03-GOVERNANCE-03</t>
+          <t>HORIZON-CL6-2026-02-CLIMATE-01</t>
         </is>
       </c>
       <c r="C569" s="3" t="n">
         <v>46036</v>
       </c>
       <c r="D569" s="3" t="n">
-        <v>46127</v>
+        <v>46126</v>
       </c>
       <c r="E569" s="4" t="n">
-        <v>3000000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" s="2" t="inlineStr">
         <is>
-          <t>Supporting All-Atlantic Ocean Research and Innovation Alliance</t>
+          <t>Empowering the UN Decade of Ocean Science for Sustainable Development</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-03-GOVERNANCE-04</t>
+          <t>HORIZON-CL6-2026-03-GOVERNANCE-03</t>
         </is>
       </c>
       <c r="C570" s="3" t="n">
@@ -13907,18 +13907,18 @@
         <v>46127</v>
       </c>
       <c r="E570" s="4" t="n">
-        <v>4500000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" s="2" t="inlineStr">
         <is>
-          <t>Coordinated European contribution to the WMO Global Greenhouse Gas Watch and its international governance</t>
+          <t>Supporting All-Atlantic Ocean Research and Innovation Alliance</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-03-GOVERNANCE-05</t>
+          <t>HORIZON-CL6-2026-03-GOVERNANCE-04</t>
         </is>
       </c>
       <c r="C571" s="3" t="n">
@@ -13928,39 +13928,39 @@
         <v>46127</v>
       </c>
       <c r="E571" s="4" t="n">
-        <v>7000000</v>
+        <v>4500000</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" s="2" t="inlineStr">
         <is>
-          <t>Sustainable and healthy diets for cardiovascular diseases prevention with the support of digital applications</t>
+          <t>Coordinated European contribution to the WMO Global Greenhouse Gas Watch and its international governance</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-FARM2FORK-09</t>
+          <t>HORIZON-CL6-2026-03-GOVERNANCE-05</t>
         </is>
       </c>
       <c r="C572" s="3" t="n">
         <v>46036</v>
       </c>
       <c r="D572" s="3" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="E572" s="4" t="n">
-        <v>5000000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" s="2" t="inlineStr">
         <is>
-          <t>Boosting circularity and diversification strategies of terrestrial livestock production systems</t>
+          <t>Sustainable and healthy diets for cardiovascular diseases prevention with the support of digital applications</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-FARM2FORK-05</t>
+          <t>HORIZON-CL6-2026-02-FARM2FORK-09</t>
         </is>
       </c>
       <c r="C573" s="3" t="n">
@@ -13970,39 +13970,39 @@
         <v>46126</v>
       </c>
       <c r="E573" s="4" t="n">
-        <v>6000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" s="2" t="inlineStr">
         <is>
-          <t>Embracing innovation in agriculture by peer-to-peer learning via on farm-demonstrations and cost-benefit analysis</t>
+          <t>Boosting circularity and diversification strategies of terrestrial livestock production systems</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-03-GOVERNANCE-10</t>
+          <t>HORIZON-CL6-2026-02-FARM2FORK-05</t>
         </is>
       </c>
       <c r="C574" s="3" t="n">
         <v>46036</v>
       </c>
       <c r="D574" s="3" t="n">
-        <v>46127</v>
+        <v>46126</v>
       </c>
       <c r="E574" s="4" t="n">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" s="2" t="inlineStr">
         <is>
-          <t>Improving analytical capacity and understanding of social drivers in agriculture to better assess social sustainability in the sector</t>
+          <t>Embracing innovation in agriculture by peer-to-peer learning via on farm-demonstrations and cost-benefit analysis</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-03-GOVERNANCE-02</t>
+          <t>HORIZON-CL6-2026-03-GOVERNANCE-10</t>
         </is>
       </c>
       <c r="C575" s="3" t="n">
@@ -14012,39 +14012,39 @@
         <v>46127</v>
       </c>
       <c r="E575" s="4" t="n">
-        <v>5000000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" s="2" t="inlineStr">
         <is>
-          <t>Sustainable and healthy diets based on health status and socio-economic risk factors of ageing population</t>
+          <t>Improving analytical capacity and understanding of social drivers in agriculture to better assess social sustainability in the sector</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-FARM2FORK-10</t>
+          <t>HORIZON-CL6-2026-03-GOVERNANCE-02</t>
         </is>
       </c>
       <c r="C576" s="3" t="n">
         <v>46036</v>
       </c>
       <c r="D576" s="3" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="E576" s="4" t="n">
-        <v>2000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" s="2" t="inlineStr">
         <is>
-          <t>Green Transition Food Processing Africa</t>
+          <t>Sustainable and healthy diets based on health status and socio-economic risk factors of ageing population</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-FARM2FORK-14</t>
+          <t>HORIZON-CL6-2026-02-FARM2FORK-10</t>
         </is>
       </c>
       <c r="C577" s="3" t="n">
@@ -14054,18 +14054,18 @@
         <v>46126</v>
       </c>
       <c r="E577" s="4" t="n">
-        <v>5000000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" s="2" t="inlineStr">
         <is>
-          <t>Accelerating the development of breeding tools for perennial crops, specifically fruits and nuts</t>
+          <t>Green Transition Food Processing Africa</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-FARM2FORK-04</t>
+          <t>HORIZON-CL6-2026-02-FARM2FORK-14</t>
         </is>
       </c>
       <c r="C578" s="3" t="n">
@@ -14075,18 +14075,18 @@
         <v>46126</v>
       </c>
       <c r="E578" s="4" t="n">
-        <v>6000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" s="2" t="inlineStr">
         <is>
-          <t>Towards the water infrastructures of the future</t>
+          <t>Accelerating the development of breeding tools for perennial crops, specifically fruits and nuts</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-02-CLIMATE-02</t>
+          <t>HORIZON-CL6-2026-02-FARM2FORK-04</t>
         </is>
       </c>
       <c r="C579" s="3" t="n">
@@ -14096,76 +14096,76 @@
         <v>46126</v>
       </c>
       <c r="E579" s="4" t="n">
-        <v>5000000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" s="2" t="inlineStr">
         <is>
-          <t>Increasing knowledge flows to practice within AKIS via EU thematic knowledge hubs</t>
+          <t>Towards the water infrastructures of the future</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2026-03-GOVERNANCE-09</t>
+          <t>HORIZON-CL6-2026-02-CLIMATE-02</t>
         </is>
       </c>
       <c r="C580" s="3" t="n">
         <v>46036</v>
       </c>
       <c r="D580" s="3" t="n">
-        <v>46127</v>
+        <v>46126</v>
       </c>
       <c r="E580" s="4" t="n">
-        <v>3500000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" s="2" t="inlineStr">
         <is>
-          <t>Hop-On Facility</t>
+          <t>Increasing knowledge flows to practice within AKIS via EU thematic knowledge hubs</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>HORIZON-WIDERA-2026-03-WIDENING-01</t>
+          <t>HORIZON-CL6-2026-03-GOVERNANCE-09</t>
         </is>
       </c>
       <c r="C581" s="3" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="D581" s="3" t="n">
-        <v>46289</v>
+        <v>46127</v>
       </c>
       <c r="E581" s="4" t="n">
-        <v>200000</v>
+        <v>3500000</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" s="2" t="inlineStr">
         <is>
-          <t>EP BrainHealth Call 1 | Biological, social and environmental factors that impact the trajectory of brain health across the lifespan – in the field of neurological, mental and sensory disorders</t>
+          <t>Hop-On Facility</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2025-02-DISEASE-01</t>
+          <t>HORIZON-WIDERA-2026-03-WIDENING-01</t>
         </is>
       </c>
       <c r="C582" s="3" t="n">
-        <v>46030</v>
+        <v>46035</v>
       </c>
       <c r="D582" s="3" t="n">
-        <v>46203.58333333334</v>
+        <v>46289</v>
       </c>
       <c r="E582" s="4" t="n">
-        <v>26260000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" s="2" t="inlineStr">
         <is>
-          <t>EP BrainHealth Call 2 | Biological, social and environmental factors that impact the trajectory of brain health across the lifespan – in the field of neurodegeneration</t>
+          <t>EP BrainHealth Call 1 | Biological, social and environmental factors that impact the trajectory of brain health across the lifespan – in the field of neurological, mental and sensory disorders</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -14180,28 +14180,28 @@
         <v>46203.58333333334</v>
       </c>
       <c r="E583" s="4" t="n">
-        <v>27540000</v>
+        <v>26260000</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
         <is>
-          <t>Twinning</t>
+          <t>EP BrainHealth Call 2 | Biological, social and environmental factors that impact the trajectory of brain health across the lifespan – in the field of neurodegeneration</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>HORIZON-WIDERA-2026-02-WIDENING-01</t>
+          <t>HORIZON-HLTH-2025-02-DISEASE-01</t>
         </is>
       </c>
       <c r="C584" s="3" t="n">
         <v>46030</v>
       </c>
       <c r="D584" s="3" t="n">
-        <v>46121</v>
+        <v>46203.58333333334</v>
       </c>
       <c r="E584" s="4" t="n">
-        <v>800000</v>
+        <v>27540000</v>
       </c>
     </row>
     <row r="585">
@@ -14939,51 +14939,54 @@
     <row r="620">
       <c r="A620" s="2" t="inlineStr">
         <is>
-          <t>MSCA COFUND 2026</t>
+          <t>ERDERA Joint Transnational Call 2026: "Resolving unsolved cases in rare genetic and non-genetic diseases”</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>HORIZON-MSCA-2026-COFUND-01-01</t>
+          <t>HORIZON-HLTH-2023-DISEASE-07-01</t>
         </is>
       </c>
       <c r="C620" s="3" t="n">
-        <v>46007</v>
+        <v>46002</v>
       </c>
       <c r="D620" s="3" t="n">
-        <v>46120</v>
+        <v>46211.58333333334</v>
+      </c>
+      <c r="E620" s="4" t="n">
+        <v>31186922</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" s="2" t="inlineStr">
         <is>
-          <t>ERDERA Joint Transnational Call 2026: "Resolving unsolved cases in rare genetic and non-genetic diseases”</t>
+          <t>A European Benchmarking Framework for hybrid quantum-classical computing</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2023-DISEASE-07-01</t>
+          <t>HORIZON-EUROHPC-JU-2024-BENCHMARK-05-03</t>
         </is>
       </c>
       <c r="C621" s="3" t="n">
         <v>46002</v>
       </c>
       <c r="D621" s="3" t="n">
-        <v>46211.58333333334</v>
+        <v>46126</v>
       </c>
       <c r="E621" s="4" t="n">
-        <v>31186922</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" s="2" t="inlineStr">
         <is>
-          <t>A European Benchmarking Framework for hybrid quantum-classical computing</t>
+          <t>A European HPC-centric Benchmark Framework</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>HORIZON-EUROHPC-JU-2024-BENCHMARK-05-03</t>
+          <t>HORIZON-EUROHPC-JU-2024-BENCHMARK-05</t>
         </is>
       </c>
       <c r="C622" s="3" t="n">
@@ -14999,70 +15002,70 @@
     <row r="623">
       <c r="A623" s="2" t="inlineStr">
         <is>
-          <t>A European HPC-centric Benchmark Framework</t>
+          <t xml:space="preserve">2nd ARISE Open Call </t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>HORIZON-EUROHPC-JU-2024-BENCHMARK-05</t>
+          <t>HORIZON-CL4-2023-DIGITAL-EMERGING-01-02</t>
         </is>
       </c>
       <c r="C623" s="3" t="n">
-        <v>46002</v>
+        <v>45994</v>
       </c>
       <c r="D623" s="3" t="n">
-        <v>46126</v>
+        <v>46057.70833333334</v>
       </c>
       <c r="E623" s="4" t="n">
-        <v>500000</v>
+        <v>2600000</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2nd ARISE Open Call </t>
+          <t>Accelerating Food Sustainability - through Household Dietary Shifts, Trust and Transparency, and Innovations in Circular Food Processing Systems</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2023-DIGITAL-EMERGING-01-02</t>
+          <t>HORIZON-CL6-2023-FARM2FORK-01-9</t>
         </is>
       </c>
       <c r="C624" s="3" t="n">
         <v>45994</v>
       </c>
       <c r="D624" s="3" t="n">
-        <v>46057.70833333334</v>
+        <v>46230.54166666666</v>
       </c>
       <c r="E624" s="4" t="n">
-        <v>2600000</v>
+        <v>39000000</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" s="2" t="inlineStr">
         <is>
-          <t>Accelerating Food Sustainability - through Household Dietary Shifts, Trust and Transparency, and Innovations in Circular Food Processing Systems</t>
+          <t>BlueActionBANOS Open Call for Community-Led Actions</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2023-FARM2FORK-01-9</t>
+          <t>HORIZON-MISS-2024-OCEAN-02-01</t>
         </is>
       </c>
       <c r="C625" s="3" t="n">
-        <v>45994</v>
+        <v>45989</v>
       </c>
       <c r="D625" s="3" t="n">
-        <v>46230.54166666666</v>
+        <v>46171.58333333334</v>
       </c>
       <c r="E625" s="4" t="n">
-        <v>39000000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" s="2" t="inlineStr">
         <is>
-          <t>BlueActionBANOS Open Call for Community-Led Actions</t>
+          <t>BlueActionBANOS 1st Open Call for Transition Agendas</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -15077,13 +15080,13 @@
         <v>46171.58333333334</v>
       </c>
       <c r="E626" s="4" t="n">
-        <v>7000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" s="2" t="inlineStr">
         <is>
-          <t>BlueActionBANOS 1st Open Call for Transition Agendas</t>
+          <t>BlueActionAA – Community Led-Pilot Action Call (BAAC-01)</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -15098,13 +15101,13 @@
         <v>46171.58333333334</v>
       </c>
       <c r="E627" s="4" t="n">
-        <v>1000000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" s="2" t="inlineStr">
         <is>
-          <t>BlueActionAA – Community Led-Pilot Action Call (BAAC-01)</t>
+          <t xml:space="preserve">TASC-RestoreMed Open Call Type B: Transition Agenda Development (TAD) </t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -15113,19 +15116,19 @@
         </is>
       </c>
       <c r="C628" s="3" t="n">
-        <v>45989</v>
+        <v>45988</v>
       </c>
       <c r="D628" s="3" t="n">
-        <v>46171.58333333334</v>
+        <v>46169.70833333334</v>
       </c>
       <c r="E628" s="4" t="n">
-        <v>7000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TASC-RestoreMed Open Call Type B: Transition Agenda Development (TAD) </t>
+          <t xml:space="preserve">TASC-RestoreMed Open Call Type A: Community-Led Actions (CLA) </t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -15140,97 +15143,97 @@
         <v>46169.70833333334</v>
       </c>
       <c r="E629" s="4" t="n">
-        <v>1000000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TASC-RestoreMed Open Call Type A: Community-Led Actions (CLA) </t>
+          <t>Call for MRV providers to test solutions under the LILAS4SOILS Project</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2024-OCEAN-02-01</t>
+          <t>HORIZON-MISS-2023-SOIL-01-09</t>
         </is>
       </c>
       <c r="C630" s="3" t="n">
-        <v>45988</v>
+        <v>45985</v>
       </c>
       <c r="D630" s="3" t="n">
-        <v>46169.70833333334</v>
+        <v>46046.99930555555</v>
       </c>
       <c r="E630" s="4" t="n">
-        <v>7000000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" s="2" t="inlineStr">
         <is>
-          <t>Call for MRV providers to test solutions under the LILAS4SOILS Project</t>
+          <t>Europe-Africa Research and Innovation call on Sustainable Energy - 2026</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2023-SOIL-01-09</t>
+          <t>HORIZON-CL5-2024-D3-01-09</t>
         </is>
       </c>
       <c r="C631" s="3" t="n">
-        <v>45985</v>
+        <v>45980</v>
       </c>
       <c r="D631" s="3" t="n">
-        <v>46046.99930555555</v>
+        <v>46197.66666666666</v>
       </c>
       <c r="E631" s="4" t="n">
-        <v>60000</v>
+        <v>14529000</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" s="2" t="inlineStr">
         <is>
-          <t>Europe-Africa Research and Innovation call on Sustainable Energy - 2026</t>
+          <t>Treatments and Adherence to Treatment protocols</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2024-D3-01-09</t>
+          <t>HORIZON-HLTH-2024-DISEASE-09-01</t>
         </is>
       </c>
       <c r="C632" s="3" t="n">
-        <v>45980</v>
+        <v>45979</v>
       </c>
       <c r="D632" s="3" t="n">
-        <v>46197.66666666666</v>
+        <v>46190.54166666666</v>
       </c>
       <c r="E632" s="4" t="n">
-        <v>14529000</v>
+        <v>31000000</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" s="2" t="inlineStr">
         <is>
-          <t>Treatments and Adherence to Treatment protocols</t>
+          <t>Understanding and Preventing Overweight and Obesity: Mechanisms of their onset and progression, neglected determinants and novel strategies for critical transitional periods in life - PREVENT-OO</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2024-DISEASE-09-01</t>
+          <t>HORIZON-HLTH-2022-DISEASE-03-01</t>
         </is>
       </c>
       <c r="C633" s="3" t="n">
-        <v>45979</v>
+        <v>45974</v>
       </c>
       <c r="D633" s="3" t="n">
-        <v>46190.54166666666</v>
+        <v>46184.5</v>
       </c>
       <c r="E633" s="4" t="n">
-        <v>31000000</v>
+        <v>18940000</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" s="2" t="inlineStr">
         <is>
-          <t>Understanding and Preventing Overweight and Obesity: Mechanisms of their onset and progression, neglected determinants and novel strategies for critical transitional periods in life - PREVENT-OO</t>
+          <t>Multi-country Investigator-Initiated Clinical Trials in Cardiovascular, Autoimmune and Metabolic diseases (Trials4Health) JTC2026</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
@@ -15239,596 +15242,575 @@
         </is>
       </c>
       <c r="C634" s="3" t="n">
-        <v>45974</v>
+        <v>45967</v>
       </c>
       <c r="D634" s="3" t="n">
-        <v>46184.5</v>
+        <v>46190.66666666666</v>
       </c>
       <c r="E634" s="4" t="n">
-        <v>18940000</v>
+        <v>32190000</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" s="2" t="inlineStr">
         <is>
-          <t>Multi-country Investigator-Initiated Clinical Trials in Cardiovascular, Autoimmune and Metabolic diseases (Trials4Health) JTC2026</t>
+          <t>EIC Accelerator 2026 - Short proposal</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>HORIZON-HLTH-2022-DISEASE-03-01</t>
+          <t>HORIZON-EIC-2026-ACCELERATOR-01</t>
         </is>
       </c>
       <c r="C635" s="3" t="n">
         <v>45967</v>
       </c>
       <c r="D635" s="3" t="n">
-        <v>46190.66666666666</v>
-      </c>
-      <c r="E635" s="4" t="n">
-        <v>32190000</v>
+        <v>46373</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" s="2" t="inlineStr">
         <is>
-          <t>EIC Accelerator 2026 - Short proposal</t>
+          <t>EIC STEP Scale Up</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>HORIZON-EIC-2026-ACCELERATOR-01</t>
+          <t>HORIZON-EIC-2026-STEP</t>
         </is>
       </c>
       <c r="C636" s="3" t="n">
         <v>45967</v>
       </c>
       <c r="D636" s="3" t="n">
-        <v>46373</v>
+        <v>46351</v>
+      </c>
+      <c r="E636" s="4" t="n">
+        <v>10000000</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" s="2" t="inlineStr">
         <is>
-          <t>EIC STEP Scale Up</t>
+          <t>InnoMatch project - Open call 1 EIC Awardee + Buyer (wave 2)</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>HORIZON-EIC-2026-STEP</t>
+          <t>HORIZON-EIC-2023-INNOVPRO-01-01</t>
         </is>
       </c>
       <c r="C637" s="3" t="n">
-        <v>45967</v>
+        <v>45964</v>
       </c>
       <c r="D637" s="3" t="n">
-        <v>46351</v>
-      </c>
-      <c r="E637" s="4" t="n">
-        <v>10000000</v>
+        <v>46057.70833333334</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" s="2" t="inlineStr">
         <is>
-          <t>InnoMatch project - Open call 1 EIC Awardee + Buyer (wave 2)</t>
+          <t>SYNAPSE OPEN CALL</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>HORIZON-EIC-2023-INNOVPRO-01-01</t>
+          <t>HORIZON-CL3-2022-CS-01-01</t>
         </is>
       </c>
       <c r="C638" s="3" t="n">
-        <v>45964</v>
+        <v>45957</v>
       </c>
       <c r="D638" s="3" t="n">
-        <v>46057.70833333334</v>
+        <v>46010.70833333334</v>
+      </c>
+      <c r="E638" s="4" t="n">
+        <v>700000</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" s="2" t="inlineStr">
         <is>
-          <t>SYNAPSE OPEN CALL</t>
+          <t>Open Call for the selection of EEN organisations delivering IRS Awareness and Support Services</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>HORIZON-CL3-2022-CS-01-01</t>
+          <t>HORIZON-EIC-2021-EEN-01-01</t>
         </is>
       </c>
       <c r="C639" s="3" t="n">
-        <v>45957</v>
+        <v>45917</v>
       </c>
       <c r="D639" s="3" t="n">
-        <v>46010.70833333334</v>
+        <v>46203.70833333334</v>
       </c>
       <c r="E639" s="4" t="n">
-        <v>700000</v>
+        <v>4413480</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" s="2" t="inlineStr">
         <is>
-          <t>Open Call for the selection of EEN organisations delivering IRS Awareness and Support Services</t>
+          <t>Digitalisation and Innovation for Resilient Marine Ecosystems Businesses, and Communities to Strengthen the EU Blue Economy’s Competitiveness</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>HORIZON-EIC-2021-EEN-01-01</t>
+          <t>HORIZON-CL6-2022-GOVERNANCE-01-02</t>
         </is>
       </c>
       <c r="C640" s="3" t="n">
-        <v>45917</v>
+        <v>45915</v>
       </c>
       <c r="D640" s="3" t="n">
-        <v>46203.70833333334</v>
+        <v>46190.625</v>
       </c>
       <c r="E640" s="4" t="n">
-        <v>4413480</v>
+        <v>43495835</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" s="2" t="inlineStr">
         <is>
-          <t>Digitalisation and Innovation for Resilient Marine Ecosystems Businesses, and Communities to Strengthen the EU Blue Economy’s Competitiveness</t>
+          <t>Water4All 2025 Joint Transnational Call “Water and health”</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2022-GOVERNANCE-01-02</t>
+          <t>HORIZON-CL6-2021-CLIMATE-01-02</t>
         </is>
       </c>
       <c r="C641" s="3" t="n">
-        <v>45915</v>
+        <v>45912</v>
       </c>
       <c r="D641" s="3" t="n">
-        <v>46190.625</v>
+        <v>46133.625</v>
       </c>
       <c r="E641" s="4" t="n">
-        <v>43495835</v>
+        <v>35642584</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" s="2" t="inlineStr">
         <is>
-          <t>Water4All 2025 Joint Transnational Call “Water and health”</t>
+          <t>Restoration of ecosystem functioning, integrity and connectivity</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2021-CLIMATE-01-02</t>
+          <t>HORIZON-CL6-2021-BIODIV-02-01</t>
         </is>
       </c>
       <c r="C642" s="3" t="n">
-        <v>45912</v>
+        <v>45909</v>
       </c>
       <c r="D642" s="3" t="n">
-        <v>46125.08333333334</v>
+        <v>46126.5</v>
       </c>
       <c r="E642" s="4" t="n">
-        <v>35642584</v>
+        <v>40000000</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" s="2" t="inlineStr">
         <is>
-          <t>Restoration of ecosystem functioning, integrity and connectivity</t>
+          <t>Open Call: Textile and clothing industry organisations in Athens and Rotterdam</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2021-BIODIV-02-01</t>
+          <t>HORIZON-CL4-2023-HUMAN-01-53</t>
         </is>
       </c>
       <c r="C643" s="3" t="n">
-        <v>45909</v>
+        <v>45904</v>
       </c>
       <c r="D643" s="3" t="n">
-        <v>46126.5</v>
+        <v>45964</v>
       </c>
       <c r="E643" s="4" t="n">
-        <v>40000000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" s="2" t="inlineStr">
         <is>
-          <t>Open Call: Textile and clothing industry organisations in Athens and Rotterdam</t>
+          <t>Driving Urban Transitions (DUT) Call 2025</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2023-HUMAN-01-53</t>
+          <t>HORIZON-CL5-2021-D2-01-16</t>
         </is>
       </c>
       <c r="C644" s="3" t="n">
-        <v>45904</v>
+        <v>45901</v>
       </c>
       <c r="D644" s="3" t="n">
-        <v>45964</v>
+        <v>46135.54166666666</v>
       </c>
       <c r="E644" s="4" t="n">
-        <v>100000</v>
+        <v>80000000</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" s="2" t="inlineStr">
         <is>
-          <t>Driving Urban Transitions (DUT) Call 2025</t>
+          <t>dAIEDGE 3rd Open Call - Collaborative Projects</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>HORIZON-CL5-2021-D2-01-16</t>
+          <t>HORIZON-CL4-2022-HUMAN-02-02</t>
         </is>
       </c>
       <c r="C645" s="3" t="n">
-        <v>45901</v>
+        <v>45883</v>
       </c>
       <c r="D645" s="3" t="n">
-        <v>46135.54166666666</v>
+        <v>45947.70869212963</v>
       </c>
       <c r="E645" s="4" t="n">
-        <v>80000000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" s="2" t="inlineStr">
         <is>
-          <t>dAIEDGE 3rd Open Call - Collaborative Projects</t>
+          <t>Urban Mobility Explained (UMX) Open Call (Multi-cut-off)</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2022-HUMAN-02-02</t>
+          <t>HORIZON-EIT-2023-25-KIC-EITURBANMOBILITY</t>
         </is>
       </c>
       <c r="C646" s="3" t="n">
-        <v>45883</v>
+        <v>45840</v>
       </c>
       <c r="D646" s="3" t="n">
-        <v>45947.70869212963</v>
+        <v>46294.70833333334</v>
       </c>
       <c r="E646" s="4" t="n">
-        <v>600000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" s="2" t="inlineStr">
         <is>
-          <t>Urban Mobility Explained (UMX) Open Call (Multi-cut-off)</t>
+          <t>Bridges</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>HORIZON-EIT-2023-25-KIC-EITURBANMOBILITY</t>
+          <t>HORIZON-EIT-2023-25-Cross-KIC-Strategic-Outreach</t>
         </is>
       </c>
       <c r="C647" s="3" t="n">
-        <v>45840</v>
+        <v>45834</v>
       </c>
       <c r="D647" s="3" t="n">
-        <v>46294.70833333334</v>
+        <v>45912.99930555555</v>
       </c>
       <c r="E647" s="4" t="n">
-        <v>4000000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" s="2" t="inlineStr">
         <is>
-          <t>Bridges</t>
+          <t>Strategic Innovation Open call</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>HORIZON-EIT-2023-25-Cross-KIC-Strategic-Outreach</t>
+          <t>HORIZON-EIT-2023-25-KIC-EITURBANMOBILITY</t>
         </is>
       </c>
       <c r="C648" s="3" t="n">
-        <v>45834</v>
+        <v>45827</v>
       </c>
       <c r="D648" s="3" t="n">
-        <v>45912.99930555555</v>
+        <v>46191.70833333334</v>
       </c>
       <c r="E648" s="4" t="n">
-        <v>12000</v>
+        <v>60000000</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" s="2" t="inlineStr">
         <is>
-          <t>Strategic Innovation Open call</t>
+          <t>InnoNext - Next Generation Innovation Talents' Initiative</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>HORIZON-EIT-2023-25-KIC-EITURBANMOBILITY</t>
+          <t>HORIZON-EIC-2023-TALENTS-01-01</t>
         </is>
       </c>
       <c r="C649" s="3" t="n">
-        <v>45827</v>
+        <v>45733</v>
       </c>
       <c r="D649" s="3" t="n">
-        <v>46191.70833333334</v>
+        <v>46234.99930555555</v>
       </c>
       <c r="E649" s="4" t="n">
-        <v>60000000</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" s="2" t="inlineStr">
         <is>
-          <t>InnoNext - Next Generation Innovation Talents' Initiative</t>
+          <t>BOOST Call for Proposals</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>HORIZON-EIC-2023-TALENTS-01-01</t>
+          <t>HORIZON-EIC-2024-BOOSTER</t>
         </is>
       </c>
       <c r="C650" s="3" t="n">
-        <v>45733</v>
+        <v>45722</v>
       </c>
       <c r="D650" s="3" t="n">
-        <v>46234.99930555555</v>
+        <v>46181.70833333334</v>
       </c>
       <c r="E650" s="4" t="n">
-        <v>15900</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" s="2" t="inlineStr">
         <is>
-          <t>BOOST Call for Proposals</t>
+          <t>Low power Edge AI Chips</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>HORIZON-EIC-2024-BOOSTER</t>
+          <t>HORIZON-JU-CHIPS-2025-IA-LEAI-two-stage</t>
         </is>
       </c>
       <c r="C651" s="3" t="n">
-        <v>45722</v>
+        <v>45720</v>
       </c>
       <c r="D651" s="3" t="n">
-        <v>46181.70833333334</v>
+        <v>45917</v>
       </c>
       <c r="E651" s="4" t="n">
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" s="2" t="inlineStr">
         <is>
-          <t>Low power Edge AI Chips</t>
+          <t>EIT RawMaterials – ERMA Booster Call</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>HORIZON-JU-CHIPS-2025-IA-LEAI-two-stage</t>
+          <t>HORIZON-EIT-2023-25-KIC-EITRAWMATERIALS</t>
         </is>
       </c>
       <c r="C652" s="3" t="n">
-        <v>45720</v>
+        <v>45684</v>
       </c>
       <c r="D652" s="3" t="n">
-        <v>45917</v>
+        <v>45908.99930555555</v>
       </c>
       <c r="E652" s="4" t="n">
-        <v>1000000</v>
+        <v>24000000</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" s="2" t="inlineStr">
         <is>
-          <t>EIT RawMaterials – ERMA Booster Call</t>
+          <t>Call for marine biodiversity (monitoring) data</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>HORIZON-EIT-2023-25-KIC-EITRAWMATERIALS</t>
+          <t>HORIZON-MISS-2022-OCEAN-01-07</t>
         </is>
       </c>
       <c r="C653" s="3" t="n">
-        <v>45684</v>
+        <v>45644</v>
       </c>
       <c r="D653" s="3" t="n">
-        <v>45908.99930555555</v>
-      </c>
-      <c r="E653" s="4" t="n">
-        <v>24000000</v>
+        <v>45716.99930555555</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" s="2" t="inlineStr">
         <is>
-          <t>Call for marine biodiversity (monitoring) data</t>
+          <t>Open Call: Textile and clothing industry facilitators in Athens and Rotterdam</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>HORIZON-MISS-2022-OCEAN-01-07</t>
+          <t>HORIZON-CL4-2023-HUMAN-01-53</t>
         </is>
       </c>
       <c r="C654" s="3" t="n">
-        <v>45644</v>
+        <v>45631</v>
       </c>
       <c r="D654" s="3" t="n">
-        <v>45716.99930555555</v>
+        <v>45707</v>
+      </c>
+      <c r="E654" s="4" t="n">
+        <v>100000</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" s="2" t="inlineStr">
         <is>
-          <t>Open Call: Textile and clothing industry facilitators in Athens and Rotterdam</t>
+          <t>EIT RawMaterials KAVA CALL 13 - UPSCALING</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2023-HUMAN-01-53</t>
+          <t>HORIZON-EIT-2023-25-KIC-EITRAWMATERIALS</t>
         </is>
       </c>
       <c r="C655" s="3" t="n">
-        <v>45631</v>
+        <v>45572</v>
       </c>
       <c r="D655" s="3" t="n">
-        <v>45707</v>
+        <v>45989.54166666666</v>
       </c>
       <c r="E655" s="4" t="n">
-        <v>100000</v>
+        <v>18000000</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" s="2" t="inlineStr">
         <is>
-          <t>EIT RawMaterials KAVA CALL 13 - UPSCALING</t>
+          <t>UP-RISE Open call for fermented food processors</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>HORIZON-EIT-2023-25-KIC-EITRAWMATERIALS</t>
+          <t>HORIZON-CL6-2023-FARM2FORK-01-20</t>
         </is>
       </c>
       <c r="C656" s="3" t="n">
         <v>45572</v>
       </c>
       <c r="D656" s="3" t="n">
-        <v>45989.54166666666</v>
+        <v>45632.99930555555</v>
       </c>
       <c r="E656" s="4" t="n">
-        <v>18000000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" s="2" t="inlineStr">
         <is>
-          <t>UP-RISE Open call for fermented food processors</t>
+          <t>STAGE Financial Grant Programme Call 4</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>HORIZON-CL6-2023-FARM2FORK-01-20</t>
+          <t>HORIZON-CL4-2021-RESILIENCE-01-29</t>
         </is>
       </c>
       <c r="C657" s="3" t="n">
-        <v>45572</v>
+        <v>45488</v>
       </c>
       <c r="D657" s="3" t="n">
-        <v>45632.99930555555</v>
+        <v>45657.99930555555</v>
       </c>
       <c r="E657" s="4" t="n">
-        <v>500000</v>
+        <v>2350000</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" s="2" t="inlineStr">
         <is>
-          <t>STAGE Financial Grant Programme Call 4</t>
+          <t>EIT Food Impact Funding Framework</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2021-RESILIENCE-01-29</t>
+          <t>HORIZON-EIT-2023-25-KIC-EITFOOD</t>
         </is>
       </c>
       <c r="C658" s="3" t="n">
-        <v>45488</v>
+        <v>45464</v>
       </c>
       <c r="D658" s="3" t="n">
-        <v>45657.99930555555</v>
+        <v>45974.5</v>
       </c>
       <c r="E658" s="4" t="n">
-        <v>2350000</v>
+        <v>30000000</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" s="2" t="inlineStr">
         <is>
-          <t>EIT Food Impact Funding Framework</t>
+          <t>EIT RawMaterials Booster Call 2024-2025 for Startups and SMEs</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>HORIZON-EIT-2023-25-KIC-EITFOOD</t>
+          <t>HORIZON-EIT-2023-25-KIC-EITRAWMATERIALS</t>
         </is>
       </c>
       <c r="C659" s="3" t="n">
-        <v>45464</v>
+        <v>45376</v>
       </c>
       <c r="D659" s="3" t="n">
-        <v>45974.5</v>
+        <v>45782.99930555555</v>
       </c>
       <c r="E659" s="4" t="n">
-        <v>30000000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" s="2" t="inlineStr">
         <is>
-          <t>EIT RawMaterials Booster Call 2024-2025 for Startups and SMEs</t>
+          <t>INDUSAC OPEN CALL FOR STUDENTS AND RESEARCHERS</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>HORIZON-EIT-2023-25-KIC-EITRAWMATERIALS</t>
+          <t>HORIZON-CL4-2021-HUMAN-01-20</t>
         </is>
       </c>
       <c r="C660" s="3" t="n">
-        <v>45376</v>
+        <v>45278</v>
       </c>
       <c r="D660" s="3" t="n">
-        <v>45782.99930555555</v>
+        <v>45762.99930555555</v>
       </c>
       <c r="E660" s="4" t="n">
-        <v>10000000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" s="2" t="inlineStr">
         <is>
-          <t>INDUSAC OPEN CALL FOR STUDENTS AND RESEARCHERS</t>
+          <t>Permanently Open Call for Targeted Innovation Projects</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>HORIZON-CL4-2021-HUMAN-01-20</t>
+          <t>HORIZON-EIT-2023-25-KIC-EITURBANMOBILITY</t>
         </is>
       </c>
       <c r="C661" s="3" t="n">
-        <v>45278</v>
+        <v>45274</v>
       </c>
       <c r="D661" s="3" t="n">
-        <v>45762.99930555555</v>
+        <v>46022.70833333334</v>
       </c>
       <c r="E661" s="4" t="n">
-        <v>900000</v>
-      </c>
-    </row>
-    <row r="662">
-      <c r="A662" s="2" t="inlineStr">
-        <is>
-          <t>Permanently Open Call for Targeted Innovation Projects</t>
-        </is>
-      </c>
-      <c r="B662" t="inlineStr">
-        <is>
-          <t>HORIZON-EIT-2023-25-KIC-EITURBANMOBILITY</t>
-        </is>
-      </c>
-      <c r="C662" s="3" t="n">
-        <v>45274</v>
-      </c>
-      <c r="D662" s="3" t="n">
-        <v>46022.70833333334</v>
-      </c>
-      <c r="E662" s="4" t="n">
         <v>4200000</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E662"/>
+  <autoFilter ref="A1:E661"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId2"/>
@@ -16490,7 +16472,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A659" r:id="rId658"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A660" r:id="rId659"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A661" r:id="rId660"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A662" r:id="rId661"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
